--- a/08_submission_package/m5/datasets/tropic/analysis/adam/ADaM_spec.xlsx
+++ b/08_submission_package/m5/datasets/tropic/analysis/adam/ADaM_spec.xlsx
@@ -1349,12 +1349,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SDTM.DM.ETHNIC.</t>
+          <t>Not collected in the public SDTM.DM release; assigned NOT REPORTED with the disposition documented in ADRG §5.1.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Actual treatment assignment from first non-missing SDTM.EX exposure record and config/study_config.yaml treatment map.</t>
+          <t>Actual treatment assignment from SDTM.DM.ARM/ARMCD using the same Path A arm authority as TRT01P; EXTRT is not used because F-028 documents an inconsistent exposure treatment value.</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Numeric actual treatment assignment from first non-missing SDTM.EX exposure record and config/study_config.yaml treatment map.</t>
+          <t>Numeric actual treatment assignment from SDTM.DM.ARM/ARMCD using the same Path A arm authority as TRT01PN; EXTRT is not used because F-028 documents an inconsistent exposure treatment value.</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Baseline albumin from SDTM.LB records.</t>
+          <t>Not collected in the public SDTM.LB release; left missing with a blank imputation flag (ADRG §5.1).</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Baseline lactate dehydrogenase from SDTM.LB records.</t>
+          <t>Not collected in the public SDTM.LB release; left missing with a blank imputation flag (ADRG §5.1).</t>
         </is>
       </c>
     </row>

--- a/08_submission_package/m5/datasets/tropic/analysis/adam/ADaM_spec.xlsx
+++ b/08_submission_package/m5/datasets/tropic/analysis/adam/ADaM_spec.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study" sheetId="1" r:id="R66a21d6e76c84d12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" r:id="R0ac8bf64f0924397"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables" sheetId="3" r:id="Rb720cc42a7854362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValueLevel" sheetId="4" r:id="R8b1a94a98fe745ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WhereClauses" sheetId="5" r:id="R734d5b0907bb41dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelists" sheetId="6" r:id="Rf2bb0a852ca9483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionaries" sheetId="7" r:id="R678fc14596aa4f99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods" sheetId="8" r:id="R6bd8071016c34c3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comments" sheetId="9" r:id="Rfed08770344042dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="10" r:id="R228d4e519b324022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study" sheetId="1" r:id="R8417359375c7412e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" r:id="R157960e7de3e429c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables" sheetId="3" r:id="R7ba54f32b8544e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValueLevel" sheetId="4" r:id="R342ecab52a594eef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WhereClauses" sheetId="5" r:id="Rb6c7b016bfba4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelists" sheetId="6" r:id="R676e14af20e64810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionaries" sheetId="7" r:id="R339fe328673e42a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods" sheetId="8" r:id="R4f84911ab6864d73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comments" sheetId="9" r:id="R260fc5554cf64d02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="10" r:id="Rb45df35fb9364064"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -107,74 +107,80 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -467,8 +473,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="82" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" customWidth="1"/>
+    <x:col min="2" max="2" width="82" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -564,9 +570,9 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="70" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" customWidth="1"/>
+    <x:col min="2" max="2" width="52" customWidth="1"/>
+    <x:col min="3" max="3" width="70" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -595,15 +601,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="58" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" customWidth="1"/>
+    <x:col min="2" max="2" width="58" customWidth="1"/>
+    <x:col min="3" max="3" width="30" customWidth="1"/>
+    <x:col min="4" max="4" width="44" customWidth="1"/>
+    <x:col min="5" max="5" width="14" customWidth="1"/>
+    <x:col min="6" max="6" width="24" customWidth="1"/>
+    <x:col min="7" max="7" width="14" customWidth="1"/>
+    <x:col min="8" max="8" width="16" customWidth="1"/>
+    <x:col min="9" max="9" width="40" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -679,7 +685,9 @@
           <x:t xml:space="preserve">Analysis</x:t>
         </x:is>
       </x:c>
-      <x:c r="F2" s="7"/>
+      <x:c r="F2" s="7" t="str">
+        <x:v>STUDYID, USUBJID</x:v>
+      </x:c>
       <x:c r="G2" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -690,7 +698,7 @@
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="I2" s="7"/>
+      <x:c r="I2" s="7" t="n"/>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="7" t="inlineStr">
@@ -698,10 +706,8 @@
           <x:t xml:space="preserve">ADEX</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cycle-level actual dose performance, cumulative exposure, actual/planned dose intensities, and RDI calculations.</x:t>
-        </x:is>
+      <x:c r="B3" s="7" t="str">
+        <x:v>Primary randomized IV antineoplastic exposure: cycle-level administered dose and adjustments; subject-level source RDI, cumulative exposure, and administered-cycle counts.</x:v>
       </x:c>
       <x:c r="C3" s="7" t="inlineStr">
         <x:is>
@@ -718,7 +724,9 @@
           <x:t xml:space="preserve">Analysis</x:t>
         </x:is>
       </x:c>
-      <x:c r="F3" s="7"/>
+      <x:c r="F3" s="7" t="str">
+        <x:v>STUDYID, USUBJID, PARAMCD, AVISIT</x:v>
+      </x:c>
       <x:c r="G3" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -729,7 +737,7 @@
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="I3" s="7"/>
+      <x:c r="I3" s="7" t="n"/>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="7" t="inlineStr">
@@ -757,7 +765,9 @@
           <x:t xml:space="preserve">Analysis</x:t>
         </x:is>
       </x:c>
-      <x:c r="F4" s="7"/>
+      <x:c r="F4" s="7" t="str">
+        <x:v>STUDYID, USUBJID, CMSEQ</x:v>
+      </x:c>
       <x:c r="G4" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -768,7 +778,7 @@
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="I4" s="7"/>
+      <x:c r="I4" s="7" t="n"/>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="7" t="inlineStr">
@@ -796,7 +806,9 @@
           <x:t xml:space="preserve">Analysis</x:t>
         </x:is>
       </x:c>
-      <x:c r="F5" s="7"/>
+      <x:c r="F5" s="7" t="str">
+        <x:v>STUDYID, USUBJID, AESEQ</x:v>
+      </x:c>
       <x:c r="G5" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -807,7 +819,7 @@
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="I5" s="7"/>
+      <x:c r="I5" s="7" t="n"/>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="7" t="inlineStr">
@@ -815,10 +827,8 @@
           <x:t xml:space="preserve">ADLB</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Longitudinal absolute laboratory measurements, CTCAE grading, Worst-in-window flags (ANL01FL), and continuous nadir models.</x:t>
-        </x:is>
+      <x:c r="B6" s="7" t="str">
+        <x:v>Longitudinal laboratory measurements with source-carried toxicity grades, source-flagged baselines, analysis-window flags (ANL01FL), and ANC nadir/recovery parameters.</x:v>
       </x:c>
       <x:c r="C6" s="7" t="inlineStr">
         <x:is>
@@ -835,7 +845,9 @@
           <x:t xml:space="preserve">Analysis</x:t>
         </x:is>
       </x:c>
-      <x:c r="F6" s="7"/>
+      <x:c r="F6" s="7" t="str">
+        <x:v>STUDYID, USUBJID, PARAMCD, AVISITN, LBDY, LBSEQ</x:v>
+      </x:c>
       <x:c r="G6" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -846,7 +858,7 @@
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="I6" s="7"/>
+      <x:c r="I6" s="7" t="n"/>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="7" t="inlineStr">
@@ -854,10 +866,8 @@
           <x:t xml:space="preserve">ADRS</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RECIST v1.0 soft-tissue assessments, bone-lesion scan progression tracking, objective responses, and PSA progressions.</x:t>
-        </x:is>
+      <x:c r="B7" s="7" t="str">
+        <x:v>Lesion-derived RECIST v1.0 assessments, confirmed objective response, reconstructed PSA endpoints, exploratory bone 2+2 status, and separately typed disposition clinical progression.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="inlineStr">
         <x:is>
@@ -874,7 +884,9 @@
           <x:t xml:space="preserve">Analysis</x:t>
         </x:is>
       </x:c>
-      <x:c r="F7" s="7"/>
+      <x:c r="F7" s="7" t="str">
+        <x:v>STUDYID, USUBJID, PARAMCD, ADT, AVISIT</x:v>
+      </x:c>
       <x:c r="G7" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -885,7 +897,7 @@
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="I7" s="7"/>
+      <x:c r="I7" s="7" t="n"/>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="8" t="inlineStr">
@@ -893,8 +905,10 @@
           <x:t xml:space="preserve">ADTTE</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="8" t="str">
-        <x:v>Time-to-event endpoints including Overall Survival (OS), Progression-Free Survival (PFS), time to PSA progression (TTPSA), time to tumor progression (TTUMOR), time to pain progression (TTPAIN), and time to first serious adverse event (TTSAE).</x:v>
+      <x:c r="B8" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Time-to-event endpoints including Overall Survival (OS), Progression-Free Survival (PFS), time to PSA progression (TTPSA), time to tumor progression (TTUMOR), time to pain progression (TTPAIN), and time to first serious adverse event (TTSAE).</x:t>
+        </x:is>
       </x:c>
       <x:c r="C8" s="8" t="inlineStr">
         <x:is>
@@ -911,7 +925,9 @@
           <x:t xml:space="preserve">Analysis</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="8"/>
+      <x:c r="F8" s="8" t="str">
+        <x:v>STUDYID, USUBJID, PARAMCD</x:v>
+      </x:c>
       <x:c r="G8" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -922,7 +938,7 @@
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="I8" s="8"/>
+      <x:c r="I8" s="8" t="n"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -933,22 +949,22 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="66" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="42" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8" customWidth="1"/>
+    <x:col min="2" max="2" width="10" customWidth="1"/>
+    <x:col min="3" max="3" width="16" customWidth="1"/>
+    <x:col min="4" max="4" width="34" customWidth="1"/>
+    <x:col min="5" max="5" width="12" customWidth="1"/>
+    <x:col min="6" max="6" width="9" customWidth="1"/>
+    <x:col min="7" max="7" width="13" customWidth="1"/>
+    <x:col min="8" max="8" width="12" customWidth="1"/>
+    <x:col min="9" max="9" width="12" customWidth="1"/>
+    <x:col min="10" max="10" width="16" customWidth="1"/>
+    <x:col min="11" max="11" width="14" customWidth="1"/>
+    <x:col min="12" max="12" width="10" customWidth="1"/>
+    <x:col min="13" max="13" width="20" customWidth="1"/>
+    <x:col min="14" max="14" width="66" customWidth="1"/>
+    <x:col min="15" max="15" width="14" customWidth="1"/>
+    <x:col min="16" max="16" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -1060,28 +1076,28 @@
       <x:c r="F2" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
+      <x:c r="G2" s="7" t="n"/>
+      <x:c r="H2" s="7" t="n"/>
       <x:c r="I2" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J2" s="7"/>
+      <x:c r="J2" s="7" t="n"/>
       <x:c r="K2" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol</x:t>
         </x:is>
       </x:c>
-      <x:c r="L2" s="7"/>
-      <x:c r="M2" s="7"/>
+      <x:c r="L2" s="7" t="n"/>
+      <x:c r="M2" s="7" t="n"/>
       <x:c r="N2" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol identifier from config/study_config.yaml and SDTM study domain records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O2" s="7"/>
-      <x:c r="P2" s="7"/>
+      <x:c r="O2" s="7" t="n"/>
+      <x:c r="P2" s="7" t="n"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="7" t="n">
@@ -1110,28 +1126,28 @@
       <x:c r="F3" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G3" s="7"/>
-      <x:c r="H3" s="7"/>
+      <x:c r="G3" s="7" t="n"/>
+      <x:c r="H3" s="7" t="n"/>
       <x:c r="I3" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J3" s="7"/>
+      <x:c r="J3" s="7" t="n"/>
       <x:c r="K3" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L3" s="7"/>
-      <x:c r="M3" s="7"/>
+      <x:c r="L3" s="7" t="n"/>
+      <x:c r="M3" s="7" t="n"/>
       <x:c r="N3" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.USUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O3" s="7"/>
-      <x:c r="P3" s="7"/>
+      <x:c r="O3" s="7" t="n"/>
+      <x:c r="P3" s="7" t="n"/>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="7" t="n">
@@ -1160,28 +1176,28 @@
       <x:c r="F4" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G4" s="7"/>
-      <x:c r="H4" s="7"/>
+      <x:c r="G4" s="7" t="n"/>
+      <x:c r="H4" s="7" t="n"/>
       <x:c r="I4" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J4" s="7"/>
+      <x:c r="J4" s="7" t="n"/>
       <x:c r="K4" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L4" s="7"/>
-      <x:c r="M4" s="7"/>
+      <x:c r="L4" s="7" t="n"/>
+      <x:c r="M4" s="7" t="n"/>
       <x:c r="N4" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.SUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O4" s="7"/>
-      <x:c r="P4" s="7"/>
+      <x:c r="O4" s="7" t="n"/>
+      <x:c r="P4" s="7" t="n"/>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="7" t="n">
@@ -1210,28 +1226,28 @@
       <x:c r="F5" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G5" s="7"/>
-      <x:c r="H5" s="7"/>
+      <x:c r="G5" s="7" t="n"/>
+      <x:c r="H5" s="7" t="n"/>
       <x:c r="I5" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J5" s="7"/>
+      <x:c r="J5" s="7" t="n"/>
       <x:c r="K5" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L5" s="7"/>
-      <x:c r="M5" s="7"/>
+      <x:c r="L5" s="7" t="n"/>
+      <x:c r="M5" s="7" t="n"/>
       <x:c r="N5" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.SITEID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O5" s="7"/>
-      <x:c r="P5" s="7"/>
+      <x:c r="O5" s="7" t="n"/>
+      <x:c r="P5" s="7" t="n"/>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -1260,28 +1276,28 @@
       <x:c r="F6" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G6" s="7"/>
-      <x:c r="H6" s="7"/>
+      <x:c r="G6" s="7" t="n"/>
+      <x:c r="H6" s="7" t="n"/>
       <x:c r="I6" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J6" s="7"/>
+      <x:c r="J6" s="7" t="n"/>
       <x:c r="K6" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L6" s="7"/>
-      <x:c r="M6" s="7"/>
+      <x:c r="L6" s="7" t="n"/>
+      <x:c r="M6" s="7" t="n"/>
       <x:c r="N6" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.AGE.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O6" s="7"/>
-      <x:c r="P6" s="7"/>
+      <x:c r="O6" s="7" t="n"/>
+      <x:c r="P6" s="7" t="n"/>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="7" t="n">
@@ -1310,8 +1326,8 @@
       <x:c r="F7" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G7" s="7"/>
-      <x:c r="H7" s="7"/>
+      <x:c r="G7" s="7" t="n"/>
+      <x:c r="H7" s="7" t="n"/>
       <x:c r="I7" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -1327,15 +1343,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L7" s="7"/>
-      <x:c r="M7" s="7"/>
+      <x:c r="L7" s="7" t="n"/>
+      <x:c r="M7" s="7" t="n"/>
       <x:c r="N7" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived age group from SDTM.DM.AGE and protocol age group definitions.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O7" s="7"/>
-      <x:c r="P7" s="7"/>
+      <x:c r="O7" s="7" t="n"/>
+      <x:c r="P7" s="7" t="n"/>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="7" t="n">
@@ -1364,28 +1380,28 @@
       <x:c r="F8" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G8" s="7"/>
-      <x:c r="H8" s="7"/>
+      <x:c r="G8" s="7" t="n"/>
+      <x:c r="H8" s="7" t="n"/>
       <x:c r="I8" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J8" s="7"/>
+      <x:c r="J8" s="7" t="n"/>
       <x:c r="K8" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L8" s="7"/>
-      <x:c r="M8" s="7"/>
+      <x:c r="L8" s="7" t="n"/>
+      <x:c r="M8" s="7" t="n"/>
       <x:c r="N8" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Numeric age group from AGEGR1.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O8" s="7"/>
-      <x:c r="P8" s="7"/>
+      <x:c r="O8" s="7" t="n"/>
+      <x:c r="P8" s="7" t="n"/>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="7" t="n">
@@ -1414,28 +1430,28 @@
       <x:c r="F9" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G9" s="7"/>
-      <x:c r="H9" s="7"/>
+      <x:c r="G9" s="7" t="n"/>
+      <x:c r="H9" s="7" t="n"/>
       <x:c r="I9" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J9" s="7"/>
+      <x:c r="J9" s="7" t="n"/>
       <x:c r="K9" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L9" s="7"/>
-      <x:c r="M9" s="7"/>
+      <x:c r="L9" s="7" t="n"/>
+      <x:c r="M9" s="7" t="n"/>
       <x:c r="N9" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.RACE.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O9" s="7"/>
-      <x:c r="P9" s="7"/>
+      <x:c r="O9" s="7" t="n"/>
+      <x:c r="P9" s="7" t="n"/>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="7" t="n">
@@ -1464,28 +1480,28 @@
       <x:c r="F10" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G10" s="7"/>
-      <x:c r="H10" s="7"/>
+      <x:c r="G10" s="7" t="n"/>
+      <x:c r="H10" s="7" t="n"/>
       <x:c r="I10" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J10" s="7"/>
+      <x:c r="J10" s="7" t="n"/>
       <x:c r="K10" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L10" s="7"/>
-      <x:c r="M10" s="7"/>
+      <x:c r="L10" s="7" t="n"/>
+      <x:c r="M10" s="7" t="n"/>
       <x:c r="N10" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Not collected in the public SDTM.DM release; assigned NOT REPORTED with the disposition documented in ADRG §5.1.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O10" s="7"/>
-      <x:c r="P10" s="7"/>
+      <x:c r="O10" s="7" t="n"/>
+      <x:c r="P10" s="7" t="n"/>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="7" t="n">
@@ -1514,8 +1530,8 @@
       <x:c r="F11" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7"/>
+      <x:c r="G11" s="7" t="n"/>
+      <x:c r="H11" s="7" t="n"/>
       <x:c r="I11" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -1531,15 +1547,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L11" s="7"/>
-      <x:c r="M11" s="7"/>
+      <x:c r="L11" s="7" t="n"/>
+      <x:c r="M11" s="7" t="n"/>
       <x:c r="N11" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.SEX.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O11" s="7"/>
-      <x:c r="P11" s="7"/>
+      <x:c r="O11" s="7" t="n"/>
+      <x:c r="P11" s="7" t="n"/>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="7" t="n">
@@ -1568,8 +1584,8 @@
       <x:c r="F12" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G12" s="7"/>
-      <x:c r="H12" s="7"/>
+      <x:c r="G12" s="7" t="n"/>
+      <x:c r="H12" s="7" t="n"/>
       <x:c r="I12" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -1585,15 +1601,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L12" s="7"/>
-      <x:c r="M12" s="7"/>
+      <x:c r="L12" s="7" t="n"/>
+      <x:c r="M12" s="7" t="n"/>
       <x:c r="N12" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Randomized/planned treatment assignment from SDTM.DM.ARM and config/study_config.yaml treatment map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O12" s="7"/>
-      <x:c r="P12" s="7"/>
+      <x:c r="O12" s="7" t="n"/>
+      <x:c r="P12" s="7" t="n"/>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="7" t="n">
@@ -1622,8 +1638,8 @@
       <x:c r="F13" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G13" s="7"/>
-      <x:c r="H13" s="7"/>
+      <x:c r="G13" s="7" t="n"/>
+      <x:c r="H13" s="7" t="n"/>
       <x:c r="I13" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -1639,15 +1655,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L13" s="7"/>
-      <x:c r="M13" s="7"/>
+      <x:c r="L13" s="7" t="n"/>
+      <x:c r="M13" s="7" t="n"/>
       <x:c r="N13" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Numeric planned treatment assignment from config/study_config.yaml treatment map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O13" s="7"/>
-      <x:c r="P13" s="7"/>
+      <x:c r="O13" s="7" t="n"/>
+      <x:c r="P13" s="7" t="n"/>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="7" t="n">
@@ -1676,8 +1692,8 @@
       <x:c r="F14" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G14" s="7"/>
-      <x:c r="H14" s="7"/>
+      <x:c r="G14" s="7" t="n"/>
+      <x:c r="H14" s="7" t="n"/>
       <x:c r="I14" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -1688,20 +1704,18 @@
           <x:t xml:space="preserve">CL.TRT</x:t>
         </x:is>
       </x:c>
-      <x:c r="K14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Assigned</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L14" s="7"/>
-      <x:c r="M14" s="7"/>
-      <x:c r="N14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Actual treatment assignment from SDTM.DM.ARM/ARMCD using the same Path A arm authority as TRT01P; EXTRT is not used because F-028 documents an inconsistent exposure treatment value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O14" s="7"/>
-      <x:c r="P14" s="7"/>
+      <x:c r="K14" s="7" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="L14" s="7" t="n"/>
+      <x:c r="M14" s="7" t="str">
+        <x:v>MT.TRT01A</x:v>
+      </x:c>
+      <x:c r="N14" s="7" t="str">
+        <x:v>Actual treatment derived from administered primary IV antineoplastic in SDTM.EX; falls back to planned treatment only when no qualifying IV exposure is present.</x:v>
+      </x:c>
+      <x:c r="O14" s="7" t="n"/>
+      <x:c r="P14" s="7" t="n"/>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="7" t="n">
@@ -1730,8 +1744,8 @@
       <x:c r="F15" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G15" s="7"/>
-      <x:c r="H15" s="7"/>
+      <x:c r="G15" s="7" t="n"/>
+      <x:c r="H15" s="7" t="n"/>
       <x:c r="I15" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -1742,20 +1756,18 @@
           <x:t xml:space="preserve">CL.TRT01PN</x:t>
         </x:is>
       </x:c>
-      <x:c r="K15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Assigned</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L15" s="7"/>
-      <x:c r="M15" s="7"/>
-      <x:c r="N15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Numeric actual treatment assignment from SDTM.DM.ARM/ARMCD using the same Path A arm authority as TRT01PN; EXTRT is not used because F-028 documents an inconsistent exposure treatment value.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O15" s="7"/>
-      <x:c r="P15" s="7"/>
+      <x:c r="K15" s="7" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="L15" s="7" t="n"/>
+      <x:c r="M15" s="7" t="str">
+        <x:v>MT.TRT01A</x:v>
+      </x:c>
+      <x:c r="N15" s="7" t="str">
+        <x:v>Numeric actual-treatment code mapped from ADSL.TRT01A (CbzP=1, MP=2).</x:v>
+      </x:c>
+      <x:c r="O15" s="7" t="n"/>
+      <x:c r="P15" s="7" t="n"/>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="7" t="n">
@@ -1784,28 +1796,28 @@
       <x:c r="F16" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G16" s="7"/>
-      <x:c r="H16" s="7"/>
+      <x:c r="G16" s="7" t="n"/>
+      <x:c r="H16" s="7" t="n"/>
       <x:c r="I16" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J16" s="7"/>
+      <x:c r="J16" s="7" t="n"/>
       <x:c r="K16" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L16" s="7"/>
-      <x:c r="M16" s="7"/>
+      <x:c r="L16" s="7" t="n"/>
+      <x:c r="M16" s="7" t="n"/>
       <x:c r="N16" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Randomization date from SDTM.DM.RFSTDTC or randomization source record.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O16" s="7"/>
-      <x:c r="P16" s="7"/>
+      <x:c r="O16" s="7" t="n"/>
+      <x:c r="P16" s="7" t="n"/>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="7" t="n">
@@ -1834,20 +1846,20 @@
       <x:c r="F17" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G17" s="7"/>
-      <x:c r="H17" s="7"/>
+      <x:c r="G17" s="7" t="n"/>
+      <x:c r="H17" s="7" t="n"/>
       <x:c r="I17" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J17" s="7"/>
+      <x:c r="J17" s="7" t="n"/>
       <x:c r="K17" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L17" s="7"/>
+      <x:c r="L17" s="7" t="n"/>
       <x:c r="M17" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.TRTSDT</x:t>
@@ -1858,8 +1870,8 @@
           <x:t xml:space="preserve">First exposure start date from SDTM.EX.EXSTDTC.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O17" s="7"/>
-      <x:c r="P17" s="7"/>
+      <x:c r="O17" s="7" t="n"/>
+      <x:c r="P17" s="7" t="n"/>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="7" t="n">
@@ -1888,20 +1900,20 @@
       <x:c r="F18" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G18" s="7"/>
-      <x:c r="H18" s="7"/>
+      <x:c r="G18" s="7" t="n"/>
+      <x:c r="H18" s="7" t="n"/>
       <x:c r="I18" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J18" s="7"/>
+      <x:c r="J18" s="7" t="n"/>
       <x:c r="K18" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L18" s="7"/>
+      <x:c r="L18" s="7" t="n"/>
       <x:c r="M18" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.TRTEDT</x:t>
@@ -1912,8 +1924,8 @@
           <x:t xml:space="preserve">Last exposure end date from SDTM.EX.EXENDTC.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O18" s="7"/>
-      <x:c r="P18" s="7"/>
+      <x:c r="O18" s="7" t="n"/>
+      <x:c r="P18" s="7" t="n"/>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="7" t="n">
@@ -1942,20 +1954,20 @@
       <x:c r="F19" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G19" s="7"/>
-      <x:c r="H19" s="7"/>
+      <x:c r="G19" s="7" t="n"/>
+      <x:c r="H19" s="7" t="n"/>
       <x:c r="I19" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J19" s="7"/>
+      <x:c r="J19" s="7" t="n"/>
       <x:c r="K19" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L19" s="7"/>
+      <x:c r="L19" s="7" t="n"/>
       <x:c r="M19" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.TRTDURD</x:t>
@@ -1966,8 +1978,8 @@
           <x:t xml:space="preserve">Derived from ADSL.TRTSDT and ADSL.TRTEDT.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O19" s="7"/>
-      <x:c r="P19" s="7"/>
+      <x:c r="O19" s="7" t="n"/>
+      <x:c r="P19" s="7" t="n"/>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="7" t="n">
@@ -1996,8 +2008,8 @@
       <x:c r="F20" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G20" s="7"/>
-      <x:c r="H20" s="7"/>
+      <x:c r="G20" s="7" t="n"/>
+      <x:c r="H20" s="7" t="n"/>
       <x:c r="I20" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -2013,7 +2025,7 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L20" s="7"/>
+      <x:c r="L20" s="7" t="n"/>
       <x:c r="M20" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ITTFL</x:t>
@@ -2024,8 +2036,8 @@
           <x:t xml:space="preserve">Population flag from randomized subject records and protocol population rules.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O20" s="7"/>
-      <x:c r="P20" s="7"/>
+      <x:c r="O20" s="7" t="n"/>
+      <x:c r="P20" s="7" t="n"/>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="7" t="n">
@@ -2054,8 +2066,8 @@
       <x:c r="F21" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G21" s="7"/>
-      <x:c r="H21" s="7"/>
+      <x:c r="G21" s="7" t="n"/>
+      <x:c r="H21" s="7" t="n"/>
       <x:c r="I21" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -2071,7 +2083,7 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L21" s="7"/>
+      <x:c r="L21" s="7" t="n"/>
       <x:c r="M21" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.SAFFL</x:t>
@@ -2082,8 +2094,8 @@
           <x:t xml:space="preserve">Population flag from treated subject records using SDTM.EX exposure evidence.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O21" s="7"/>
-      <x:c r="P21" s="7"/>
+      <x:c r="O21" s="7" t="n"/>
+      <x:c r="P21" s="7" t="n"/>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="7" t="n">
@@ -2112,8 +2124,8 @@
       <x:c r="F22" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G22" s="7"/>
-      <x:c r="H22" s="7"/>
+      <x:c r="G22" s="7" t="n"/>
+      <x:c r="H22" s="7" t="n"/>
       <x:c r="I22" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -2129,15 +2141,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L22" s="7"/>
-      <x:c r="M22" s="7"/>
+      <x:c r="L22" s="7" t="n"/>
+      <x:c r="M22" s="7" t="n"/>
       <x:c r="N22" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol/per-protocol eligibility source records and protocol deviation review.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O22" s="7"/>
-      <x:c r="P22" s="7"/>
+      <x:c r="O22" s="7" t="n"/>
+      <x:c r="P22" s="7" t="n"/>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="7" t="n">
@@ -2166,8 +2178,8 @@
       <x:c r="F23" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G23" s="7"/>
-      <x:c r="H23" s="7"/>
+      <x:c r="G23" s="7" t="n"/>
+      <x:c r="H23" s="7" t="n"/>
       <x:c r="I23" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -2183,15 +2195,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L23" s="7"/>
-      <x:c r="M23" s="7"/>
+      <x:c r="L23" s="7" t="n"/>
+      <x:c r="M23" s="7" t="n"/>
       <x:c r="N23" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Death flag from SDTM.DM.DTHFL and disposition/death records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O23" s="7"/>
-      <x:c r="P23" s="7"/>
+      <x:c r="O23" s="7" t="n"/>
+      <x:c r="P23" s="7" t="n"/>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="7" t="n">
@@ -2220,32 +2232,30 @@
       <x:c r="F24" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G24" s="7"/>
-      <x:c r="H24" s="7"/>
+      <x:c r="G24" s="7" t="n"/>
+      <x:c r="H24" s="7" t="n"/>
       <x:c r="I24" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J24" s="7"/>
+      <x:c r="J24" s="7" t="n"/>
       <x:c r="K24" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L24" s="7"/>
+      <x:c r="L24" s="7" t="n"/>
       <x:c r="M24" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.DTHDT</x:t>
         </x:is>
       </x:c>
-      <x:c r="N24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Death date from SDTM.DM.DTHDTC or disposition/death records.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O24" s="7"/>
-      <x:c r="P24" s="7"/>
+      <x:c r="N24" s="7" t="str">
+        <x:v>Earliest complete SDTM.AE.AEDTHDTC is preferred; otherwise the earliest DS death week is anchored to randomization.</x:v>
+      </x:c>
+      <x:c r="O24" s="7" t="n"/>
+      <x:c r="P24" s="7" t="n"/>
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="7" t="n">
@@ -2274,28 +2284,28 @@
       <x:c r="F25" s="7" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G25" s="7"/>
-      <x:c r="H25" s="7"/>
+      <x:c r="G25" s="7" t="n"/>
+      <x:c r="H25" s="7" t="n"/>
       <x:c r="I25" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J25" s="7"/>
+      <x:c r="J25" s="7" t="n"/>
       <x:c r="K25" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L25" s="7"/>
-      <x:c r="M25" s="7"/>
+      <x:c r="L25" s="7" t="n"/>
+      <x:c r="M25" s="7" t="n"/>
       <x:c r="N25" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Death cause from disposition/death source records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O25" s="7"/>
-      <x:c r="P25" s="7"/>
+      <x:c r="O25" s="7" t="n"/>
+      <x:c r="P25" s="7" t="n"/>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="7" t="n">
@@ -2324,32 +2334,30 @@
       <x:c r="F26" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G26" s="7"/>
-      <x:c r="H26" s="7"/>
+      <x:c r="G26" s="7" t="n"/>
+      <x:c r="H26" s="7" t="n"/>
       <x:c r="I26" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J26" s="7"/>
+      <x:c r="J26" s="7" t="n"/>
       <x:c r="K26" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L26" s="7"/>
+      <x:c r="L26" s="7" t="n"/>
       <x:c r="M26" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.LSTALVDT</x:t>
         </x:is>
       </x:c>
-      <x:c r="N26" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Last known alive date from maximum non-death contact/assessment date across SDTM source domains.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O26" s="7"/>
-      <x:c r="P26" s="7"/>
+      <x:c r="N26" s="7" t="str">
+        <x:v>Maximum dated observed contact or assessment across DS, EX, VS, LB, LS, PN, and SV, capped at DTHDT for deceased subjects.</x:v>
+      </x:c>
+      <x:c r="O26" s="7" t="n"/>
+      <x:c r="P26" s="7" t="n"/>
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="7" t="n">
@@ -2378,20 +2386,20 @@
       <x:c r="F27" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G27" s="7"/>
-      <x:c r="H27" s="7"/>
+      <x:c r="G27" s="7" t="n"/>
+      <x:c r="H27" s="7" t="n"/>
       <x:c r="I27" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J27" s="7"/>
+      <x:c r="J27" s="7" t="n"/>
       <x:c r="K27" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L27" s="7"/>
+      <x:c r="L27" s="7" t="n"/>
       <x:c r="M27" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ECOGBL</x:t>
@@ -2402,8 +2410,8 @@
           <x:t xml:space="preserve">Baseline ECOG from SDTM.QS/VS assessment source before treatment start.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O27" s="7"/>
-      <x:c r="P27" s="7"/>
+      <x:c r="O27" s="7" t="n"/>
+      <x:c r="P27" s="7" t="n"/>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
       <x:c r="A28" s="7" t="n">
@@ -2432,8 +2440,8 @@
       <x:c r="F28" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G28" s="7"/>
-      <x:c r="H28" s="7"/>
+      <x:c r="G28" s="7" t="n"/>
+      <x:c r="H28" s="7" t="n"/>
       <x:c r="I28" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -2449,7 +2457,7 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L28" s="7"/>
+      <x:c r="L28" s="7" t="n"/>
       <x:c r="M28" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.MEASDISF</x:t>
@@ -2460,8 +2468,8 @@
           <x:t xml:space="preserve">Measurable disease flag from baseline tumor/response source assessments.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O28" s="7"/>
-      <x:c r="P28" s="7"/>
+      <x:c r="O28" s="7" t="n"/>
+      <x:c r="P28" s="7" t="n"/>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
       <x:c r="A29" s="7" t="n">
@@ -2490,8 +2498,8 @@
       <x:c r="F29" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G29" s="7"/>
-      <x:c r="H29" s="7"/>
+      <x:c r="G29" s="7" t="n"/>
+      <x:c r="H29" s="7" t="n"/>
       <x:c r="I29" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -2507,15 +2515,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L29" s="7"/>
-      <x:c r="M29" s="7"/>
+      <x:c r="L29" s="7" t="n"/>
+      <x:c r="M29" s="7" t="n"/>
       <x:c r="N29" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Visceral disease flag from baseline lesion source assessments.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O29" s="7"/>
-      <x:c r="P29" s="7"/>
+      <x:c r="O29" s="7" t="n"/>
+      <x:c r="P29" s="7" t="n"/>
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
       <x:c r="A30" s="7" t="n">
@@ -2544,8 +2552,8 @@
       <x:c r="F30" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G30" s="7"/>
-      <x:c r="H30" s="7"/>
+      <x:c r="G30" s="7" t="n"/>
+      <x:c r="H30" s="7" t="n"/>
       <x:c r="I30" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -2561,19 +2569,17 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L30" s="7"/>
+      <x:c r="L30" s="7" t="n"/>
       <x:c r="M30" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.PAINBL</x:t>
         </x:is>
       </x:c>
-      <x:c r="N30" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline pain score from pain assessment source before treatment start.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O30" s="7"/>
-      <x:c r="P30" s="7"/>
+      <x:c r="N30" s="7" t="str">
+        <x:v>Y when a component-specific 7-day pre-treatment diary has at least 5 non-discordant days and median pain intensity &gt;=2 or mean analgesic score &gt;=10; otherwise N.</x:v>
+      </x:c>
+      <x:c r="O30" s="7" t="n"/>
+      <x:c r="P30" s="7" t="n"/>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
       <x:c r="A31" s="7" t="n">
@@ -2602,28 +2608,28 @@
       <x:c r="F31" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G31" s="7"/>
-      <x:c r="H31" s="7"/>
+      <x:c r="G31" s="7" t="n"/>
+      <x:c r="H31" s="7" t="n"/>
       <x:c r="I31" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J31" s="7"/>
+      <x:c r="J31" s="7" t="n"/>
       <x:c r="K31" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L31" s="7"/>
-      <x:c r="M31" s="7"/>
+      <x:c r="L31" s="7" t="n"/>
+      <x:c r="M31" s="7" t="n"/>
       <x:c r="N31" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Baseline PSA from SDTM.LB prostate-specific antigen records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O31" s="7"/>
-      <x:c r="P31" s="7"/>
+      <x:c r="O31" s="7" t="n"/>
+      <x:c r="P31" s="7" t="n"/>
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="7" t="n">
@@ -2652,28 +2658,28 @@
       <x:c r="F32" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G32" s="7"/>
-      <x:c r="H32" s="7"/>
+      <x:c r="G32" s="7" t="n"/>
+      <x:c r="H32" s="7" t="n"/>
       <x:c r="I32" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J32" s="7"/>
+      <x:c r="J32" s="7" t="n"/>
       <x:c r="K32" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L32" s="7"/>
-      <x:c r="M32" s="7"/>
+      <x:c r="L32" s="7" t="n"/>
+      <x:c r="M32" s="7" t="n"/>
       <x:c r="N32" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Baseline alkaline phosphatase from SDTM.LB records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O32" s="7"/>
-      <x:c r="P32" s="7"/>
+      <x:c r="O32" s="7" t="n"/>
+      <x:c r="P32" s="7" t="n"/>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="7" t="n">
@@ -2702,28 +2708,28 @@
       <x:c r="F33" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G33" s="7"/>
-      <x:c r="H33" s="7"/>
+      <x:c r="G33" s="7" t="n"/>
+      <x:c r="H33" s="7" t="n"/>
       <x:c r="I33" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J33" s="7"/>
+      <x:c r="J33" s="7" t="n"/>
       <x:c r="K33" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L33" s="7"/>
-      <x:c r="M33" s="7"/>
+      <x:c r="L33" s="7" t="n"/>
+      <x:c r="M33" s="7" t="n"/>
       <x:c r="N33" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Not collected in the public SDTM.LB release; left missing with a blank imputation flag (ADRG §5.1).</x:t>
         </x:is>
       </x:c>
-      <x:c r="O33" s="7"/>
-      <x:c r="P33" s="7"/>
+      <x:c r="O33" s="7" t="n"/>
+      <x:c r="P33" s="7" t="n"/>
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="7" t="n">
@@ -2752,28 +2758,28 @@
       <x:c r="F34" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G34" s="7"/>
-      <x:c r="H34" s="7"/>
+      <x:c r="G34" s="7" t="n"/>
+      <x:c r="H34" s="7" t="n"/>
       <x:c r="I34" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J34" s="7"/>
+      <x:c r="J34" s="7" t="n"/>
       <x:c r="K34" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L34" s="7"/>
-      <x:c r="M34" s="7"/>
+      <x:c r="L34" s="7" t="n"/>
+      <x:c r="M34" s="7" t="n"/>
       <x:c r="N34" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Not collected in the public SDTM.LB release; left missing with a blank imputation flag (ADRG §5.1).</x:t>
         </x:is>
       </x:c>
-      <x:c r="O34" s="7"/>
-      <x:c r="P34" s="7"/>
+      <x:c r="O34" s="7" t="n"/>
+      <x:c r="P34" s="7" t="n"/>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="7" t="n">
@@ -2802,28 +2808,28 @@
       <x:c r="F35" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G35" s="7"/>
-      <x:c r="H35" s="7"/>
+      <x:c r="G35" s="7" t="n"/>
+      <x:c r="H35" s="7" t="n"/>
       <x:c r="I35" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J35" s="7"/>
+      <x:c r="J35" s="7" t="n"/>
       <x:c r="K35" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L35" s="7"/>
-      <x:c r="M35" s="7"/>
+      <x:c r="L35" s="7" t="n"/>
+      <x:c r="M35" s="7" t="n"/>
       <x:c r="N35" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Baseline hemoglobin from SDTM.LB records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O35" s="7"/>
-      <x:c r="P35" s="7"/>
+      <x:c r="O35" s="7" t="n"/>
+      <x:c r="P35" s="7" t="n"/>
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
       <x:c r="A36" s="7" t="n">
@@ -2852,28 +2858,28 @@
       <x:c r="F36" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G36" s="7"/>
-      <x:c r="H36" s="7"/>
+      <x:c r="G36" s="7" t="n"/>
+      <x:c r="H36" s="7" t="n"/>
       <x:c r="I36" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J36" s="7"/>
+      <x:c r="J36" s="7" t="n"/>
       <x:c r="K36" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L36" s="7"/>
-      <x:c r="M36" s="7"/>
+      <x:c r="L36" s="7" t="n"/>
+      <x:c r="M36" s="7" t="n"/>
       <x:c r="N36" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Investigator-assessed progression source records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O36" s="7"/>
-      <x:c r="P36" s="7"/>
+      <x:c r="O36" s="7" t="n"/>
+      <x:c r="P36" s="7" t="n"/>
     </x:row>
     <x:row r="37" ht="42" customHeight="1">
       <x:c r="A37" s="7" t="n">
@@ -2902,8 +2908,8 @@
       <x:c r="F37" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G37" s="7"/>
-      <x:c r="H37" s="7"/>
+      <x:c r="G37" s="7" t="n"/>
+      <x:c r="H37" s="7" t="n"/>
       <x:c r="I37" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -2919,15 +2925,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L37" s="7"/>
-      <x:c r="M37" s="7"/>
+      <x:c r="L37" s="7" t="n"/>
+      <x:c r="M37" s="7" t="n"/>
       <x:c r="N37" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Investigator-assessed response source records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O37" s="7"/>
-      <x:c r="P37" s="7"/>
+      <x:c r="O37" s="7" t="n"/>
+      <x:c r="P37" s="7" t="n"/>
     </x:row>
     <x:row r="38" ht="42" customHeight="1">
       <x:c r="A38" s="7" t="n">
@@ -2943,10 +2949,8 @@
           <x:t xml:space="preserve">ECOGBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="D38" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline ECOG Imputed Flag</x:t>
-        </x:is>
+      <x:c r="D38" s="7" t="str">
+        <x:v>Baseline ECOG Imputation Flag</x:v>
       </x:c>
       <x:c r="E38" s="7" t="inlineStr">
         <x:is>
@@ -2956,8 +2960,8 @@
       <x:c r="F38" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G38" s="7"/>
-      <x:c r="H38" s="7"/>
+      <x:c r="G38" s="7" t="n"/>
+      <x:c r="H38" s="7" t="n"/>
       <x:c r="I38" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -2973,19 +2977,17 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L38" s="7"/>
+      <x:c r="L38" s="7" t="n"/>
       <x:c r="M38" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ECOGBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="N38" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imputation flag derived from ECOGBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O38" s="7"/>
-      <x:c r="P38" s="7"/>
+      <x:c r="N38" s="7" t="str">
+        <x:v>Set to N because the corresponding observed source baseline is not imputed.</x:v>
+      </x:c>
+      <x:c r="O38" s="7" t="n"/>
+      <x:c r="P38" s="7" t="n"/>
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
       <x:c r="A39" s="7" t="n">
@@ -3001,10 +3003,8 @@
           <x:t xml:space="preserve">PSABLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="D39" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline PSA Imputed Flag</x:t>
-        </x:is>
+      <x:c r="D39" s="7" t="str">
+        <x:v>Baseline PSA Imputation Flag</x:v>
       </x:c>
       <x:c r="E39" s="7" t="inlineStr">
         <x:is>
@@ -3014,8 +3014,8 @@
       <x:c r="F39" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G39" s="7"/>
-      <x:c r="H39" s="7"/>
+      <x:c r="G39" s="7" t="n"/>
+      <x:c r="H39" s="7" t="n"/>
       <x:c r="I39" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -3031,19 +3031,17 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L39" s="7"/>
+      <x:c r="L39" s="7" t="n"/>
       <x:c r="M39" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.PSABLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="N39" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imputation flag derived from PSABL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O39" s="7"/>
-      <x:c r="P39" s="7"/>
+      <x:c r="N39" s="7" t="str">
+        <x:v>Set to N because the corresponding observed source baseline is not imputed.</x:v>
+      </x:c>
+      <x:c r="O39" s="7" t="n"/>
+      <x:c r="P39" s="7" t="n"/>
     </x:row>
     <x:row r="40" ht="42" customHeight="1">
       <x:c r="A40" s="7" t="n">
@@ -3059,10 +3057,8 @@
           <x:t xml:space="preserve">ALPBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="D40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline ALP Imputed Flag</x:t>
-        </x:is>
+      <x:c r="D40" s="7" t="str">
+        <x:v>Baseline ALP Imputation Flag</x:v>
       </x:c>
       <x:c r="E40" s="7" t="inlineStr">
         <x:is>
@@ -3072,8 +3068,8 @@
       <x:c r="F40" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G40" s="7"/>
-      <x:c r="H40" s="7"/>
+      <x:c r="G40" s="7" t="n"/>
+      <x:c r="H40" s="7" t="n"/>
       <x:c r="I40" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -3089,19 +3085,17 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L40" s="7"/>
+      <x:c r="L40" s="7" t="n"/>
       <x:c r="M40" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ALPBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="N40" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imputation flag derived from ALPBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O40" s="7"/>
-      <x:c r="P40" s="7"/>
+      <x:c r="N40" s="7" t="str">
+        <x:v>Set to N because the corresponding observed source baseline is not imputed.</x:v>
+      </x:c>
+      <x:c r="O40" s="7" t="n"/>
+      <x:c r="P40" s="7" t="n"/>
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
       <x:c r="A41" s="7" t="n">
@@ -3117,10 +3111,8 @@
           <x:t xml:space="preserve">HGBBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="D41" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline Hemoglobin Imputed Flag</x:t>
-        </x:is>
+      <x:c r="D41" s="7" t="str">
+        <x:v>Baseline Hemoglobin Imputation Flag</x:v>
       </x:c>
       <x:c r="E41" s="7" t="inlineStr">
         <x:is>
@@ -3130,8 +3122,8 @@
       <x:c r="F41" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G41" s="7"/>
-      <x:c r="H41" s="7"/>
+      <x:c r="G41" s="7" t="n"/>
+      <x:c r="H41" s="7" t="n"/>
       <x:c r="I41" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -3147,19 +3139,17 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L41" s="7"/>
+      <x:c r="L41" s="7" t="n"/>
       <x:c r="M41" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.HGBBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="N41" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imputation flag derived from HGBBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O41" s="7"/>
-      <x:c r="P41" s="7"/>
+      <x:c r="N41" s="7" t="str">
+        <x:v>Set to N because the corresponding observed source baseline is not imputed.</x:v>
+      </x:c>
+      <x:c r="O41" s="7" t="n"/>
+      <x:c r="P41" s="7" t="n"/>
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
       <x:c r="A42" s="7" t="n">
@@ -3175,10 +3165,8 @@
           <x:t xml:space="preserve">ALBBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="D42" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline Albumin Imputed Flag</x:t>
-        </x:is>
+      <x:c r="D42" s="7" t="str">
+        <x:v>Baseline Albumin Imputation Flag</x:v>
       </x:c>
       <x:c r="E42" s="7" t="inlineStr">
         <x:is>
@@ -3188,8 +3176,8 @@
       <x:c r="F42" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G42" s="7"/>
-      <x:c r="H42" s="7"/>
+      <x:c r="G42" s="7" t="n"/>
+      <x:c r="H42" s="7" t="n"/>
       <x:c r="I42" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -3205,19 +3193,17 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L42" s="7"/>
+      <x:c r="L42" s="7" t="n"/>
       <x:c r="M42" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ALBBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="N42" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imputation flag derived from ALBBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O42" s="7"/>
-      <x:c r="P42" s="7"/>
+      <x:c r="N42" s="7" t="str">
+        <x:v>Blank because the source analyte is unavailable and no imputation is performed.</x:v>
+      </x:c>
+      <x:c r="O42" s="7" t="n"/>
+      <x:c r="P42" s="7" t="n"/>
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
       <x:c r="A43" s="7" t="n">
@@ -3233,10 +3219,8 @@
           <x:t xml:space="preserve">LDHBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="D43" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline LDH Imputed Flag</x:t>
-        </x:is>
+      <x:c r="D43" s="7" t="str">
+        <x:v>Baseline LDH Imputation Flag</x:v>
       </x:c>
       <x:c r="E43" s="7" t="inlineStr">
         <x:is>
@@ -3246,8 +3230,8 @@
       <x:c r="F43" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G43" s="7"/>
-      <x:c r="H43" s="7"/>
+      <x:c r="G43" s="7" t="n"/>
+      <x:c r="H43" s="7" t="n"/>
       <x:c r="I43" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -3263,19 +3247,17 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L43" s="7"/>
+      <x:c r="L43" s="7" t="n"/>
       <x:c r="M43" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.LDHBLIF</x:t>
         </x:is>
       </x:c>
-      <x:c r="N43" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imputation flag derived from LDHBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O43" s="7"/>
-      <x:c r="P43" s="7"/>
+      <x:c r="N43" s="7" t="str">
+        <x:v>Blank because the source analyte is unavailable and no imputation is performed.</x:v>
+      </x:c>
+      <x:c r="O43" s="7" t="n"/>
+      <x:c r="P43" s="7" t="n"/>
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="7" t="n">
@@ -3304,28 +3286,28 @@
       <x:c r="F44" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G44" s="7"/>
-      <x:c r="H44" s="7"/>
+      <x:c r="G44" s="7" t="n"/>
+      <x:c r="H44" s="7" t="n"/>
       <x:c r="I44" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J44" s="7"/>
+      <x:c r="J44" s="7" t="n"/>
       <x:c r="K44" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol</x:t>
         </x:is>
       </x:c>
-      <x:c r="L44" s="7"/>
-      <x:c r="M44" s="7"/>
+      <x:c r="L44" s="7" t="n"/>
+      <x:c r="M44" s="7" t="n"/>
       <x:c r="N44" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol identifier from config/study_config.yaml and SDTM study domain records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O44" s="7"/>
-      <x:c r="P44" s="7"/>
+      <x:c r="O44" s="7" t="n"/>
+      <x:c r="P44" s="7" t="n"/>
     </x:row>
     <x:row r="45" ht="42" customHeight="1">
       <x:c r="A45" s="7" t="n">
@@ -3354,28 +3336,28 @@
       <x:c r="F45" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G45" s="7"/>
-      <x:c r="H45" s="7"/>
+      <x:c r="G45" s="7" t="n"/>
+      <x:c r="H45" s="7" t="n"/>
       <x:c r="I45" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J45" s="7"/>
+      <x:c r="J45" s="7" t="n"/>
       <x:c r="K45" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L45" s="7"/>
-      <x:c r="M45" s="7"/>
+      <x:c r="L45" s="7" t="n"/>
+      <x:c r="M45" s="7" t="n"/>
       <x:c r="N45" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.USUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O45" s="7"/>
-      <x:c r="P45" s="7"/>
+      <x:c r="O45" s="7" t="n"/>
+      <x:c r="P45" s="7" t="n"/>
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
       <x:c r="A46" s="7" t="n">
@@ -3404,28 +3386,28 @@
       <x:c r="F46" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G46" s="7"/>
-      <x:c r="H46" s="7"/>
+      <x:c r="G46" s="7" t="n"/>
+      <x:c r="H46" s="7" t="n"/>
       <x:c r="I46" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J46" s="7"/>
+      <x:c r="J46" s="7" t="n"/>
       <x:c r="K46" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L46" s="7"/>
-      <x:c r="M46" s="7"/>
+      <x:c r="L46" s="7" t="n"/>
+      <x:c r="M46" s="7" t="n"/>
       <x:c r="N46" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.SUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O46" s="7"/>
-      <x:c r="P46" s="7"/>
+      <x:c r="O46" s="7" t="n"/>
+      <x:c r="P46" s="7" t="n"/>
     </x:row>
     <x:row r="47" ht="42" customHeight="1">
       <x:c r="A47" s="7" t="n">
@@ -3454,8 +3436,8 @@
       <x:c r="F47" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G47" s="7"/>
-      <x:c r="H47" s="7"/>
+      <x:c r="G47" s="7" t="n"/>
+      <x:c r="H47" s="7" t="n"/>
       <x:c r="I47" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -3471,15 +3453,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L47" s="7"/>
-      <x:c r="M47" s="7"/>
+      <x:c r="L47" s="7" t="n"/>
+      <x:c r="M47" s="7" t="n"/>
       <x:c r="N47" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Randomized/planned treatment assignment from SDTM.DM.ARM and config/study_config.yaml treatment map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O47" s="7"/>
-      <x:c r="P47" s="7"/>
+      <x:c r="O47" s="7" t="n"/>
+      <x:c r="P47" s="7" t="n"/>
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
       <x:c r="A48" s="7" t="n">
@@ -3508,8 +3490,8 @@
       <x:c r="F48" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G48" s="7"/>
-      <x:c r="H48" s="7"/>
+      <x:c r="G48" s="7" t="n"/>
+      <x:c r="H48" s="7" t="n"/>
       <x:c r="I48" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -3525,15 +3507,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L48" s="7"/>
-      <x:c r="M48" s="7"/>
+      <x:c r="L48" s="7" t="n"/>
+      <x:c r="M48" s="7" t="n"/>
       <x:c r="N48" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Numeric planned treatment assignment from config/study_config.yaml treatment map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O48" s="7"/>
-      <x:c r="P48" s="7"/>
+      <x:c r="O48" s="7" t="n"/>
+      <x:c r="P48" s="7" t="n"/>
     </x:row>
     <x:row r="49" ht="42" customHeight="1">
       <x:c r="A49" s="7" t="n">
@@ -3562,28 +3544,28 @@
       <x:c r="F49" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G49" s="7"/>
-      <x:c r="H49" s="7"/>
+      <x:c r="G49" s="7" t="n"/>
+      <x:c r="H49" s="7" t="n"/>
       <x:c r="I49" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J49" s="7"/>
+      <x:c r="J49" s="7" t="n"/>
       <x:c r="K49" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L49" s="7"/>
-      <x:c r="M49" s="7"/>
+      <x:c r="L49" s="7" t="n"/>
+      <x:c r="M49" s="7" t="n"/>
       <x:c r="N49" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Treatment start date inherited from ADSL.TRTSDT unless defined directly for ADSL.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O49" s="7"/>
-      <x:c r="P49" s="7"/>
+      <x:c r="O49" s="7" t="n"/>
+      <x:c r="P49" s="7" t="n"/>
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
       <x:c r="A50" s="7" t="n">
@@ -3612,8 +3594,8 @@
       <x:c r="F50" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G50" s="7"/>
-      <x:c r="H50" s="7"/>
+      <x:c r="G50" s="7" t="n"/>
+      <x:c r="H50" s="7" t="n"/>
       <x:c r="I50" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -3629,15 +3611,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L50" s="7"/>
-      <x:c r="M50" s="7"/>
+      <x:c r="L50" s="7" t="n"/>
+      <x:c r="M50" s="7" t="n"/>
       <x:c r="N50" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter code from dataset-specific parameter derivation and source test/category.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O50" s="7"/>
-      <x:c r="P50" s="7"/>
+      <x:c r="O50" s="7" t="n"/>
+      <x:c r="P50" s="7" t="n"/>
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
       <x:c r="A51" s="7" t="n">
@@ -3666,28 +3648,28 @@
       <x:c r="F51" s="7" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G51" s="7"/>
-      <x:c r="H51" s="7"/>
+      <x:c r="G51" s="7" t="n"/>
+      <x:c r="H51" s="7" t="n"/>
       <x:c r="I51" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J51" s="7"/>
+      <x:c r="J51" s="7" t="n"/>
       <x:c r="K51" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L51" s="7"/>
-      <x:c r="M51" s="7"/>
+      <x:c r="L51" s="7" t="n"/>
+      <x:c r="M51" s="7" t="n"/>
       <x:c r="N51" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter label from dataset-specific parameter derivation and source test/category.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O51" s="7"/>
-      <x:c r="P51" s="7"/>
+      <x:c r="O51" s="7" t="n"/>
+      <x:c r="P51" s="7" t="n"/>
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
       <x:c r="A52" s="7" t="n">
@@ -3716,28 +3698,28 @@
       <x:c r="F52" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G52" s="7"/>
-      <x:c r="H52" s="7"/>
+      <x:c r="G52" s="7" t="n"/>
+      <x:c r="H52" s="7" t="n"/>
       <x:c r="I52" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J52" s="7"/>
+      <x:c r="J52" s="7" t="n"/>
       <x:c r="K52" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L52" s="7"/>
-      <x:c r="M52" s="7"/>
+      <x:c r="L52" s="7" t="n"/>
+      <x:c r="M52" s="7" t="n"/>
       <x:c r="N52" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter category from dataset-specific parameter map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O52" s="7"/>
-      <x:c r="P52" s="7"/>
+      <x:c r="O52" s="7" t="n"/>
+      <x:c r="P52" s="7" t="n"/>
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
       <x:c r="A53" s="7" t="n">
@@ -3766,32 +3748,30 @@
       <x:c r="F53" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G53" s="7"/>
-      <x:c r="H53" s="7"/>
+      <x:c r="G53" s="7" t="n"/>
+      <x:c r="H53" s="7" t="n"/>
       <x:c r="I53" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J53" s="7"/>
+      <x:c r="J53" s="7" t="n"/>
       <x:c r="K53" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L53" s="7"/>
+      <x:c r="L53" s="7" t="n"/>
       <x:c r="M53" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADEX_AVAL</x:t>
         </x:is>
       </x:c>
-      <x:c r="N53" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Numeric exposure analysis value from SDTM.EX dose/duration fields by PARAMCD.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O53" s="7"/>
-      <x:c r="P53" s="7"/>
+      <x:c r="N53" s="7" t="str">
+        <x:v>Parameter-specific value from qualifying primary IV SDTM.EX records: EXDOSE2, EXCUMD2, EXPDOSE, consistent EXTRINT, or derived count/flag as documented in the method.</x:v>
+      </x:c>
+      <x:c r="O53" s="7" t="n"/>
+      <x:c r="P53" s="7" t="n"/>
     </x:row>
     <x:row r="54" ht="42" customHeight="1">
       <x:c r="A54" s="7" t="n">
@@ -3820,32 +3800,30 @@
       <x:c r="F54" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G54" s="7"/>
-      <x:c r="H54" s="7"/>
+      <x:c r="G54" s="7" t="n"/>
+      <x:c r="H54" s="7" t="n"/>
       <x:c r="I54" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J54" s="7"/>
+      <x:c r="J54" s="7" t="n"/>
       <x:c r="K54" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L54" s="7"/>
+      <x:c r="L54" s="7" t="n"/>
       <x:c r="M54" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADEX_AVALC</x:t>
         </x:is>
       </x:c>
-      <x:c r="N54" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Character exposure analysis value from SDTM.EX dose/duration fields by PARAMCD.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O54" s="7"/>
-      <x:c r="P54" s="7"/>
+      <x:c r="N54" s="7" t="str">
+        <x:v>Character representation or category corresponding to the parameter-specific ADEX analysis value.</x:v>
+      </x:c>
+      <x:c r="O54" s="7" t="n"/>
+      <x:c r="P54" s="7" t="n"/>
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
       <x:c r="A55" s="7" t="n">
@@ -3874,28 +3852,28 @@
       <x:c r="F55" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G55" s="7"/>
-      <x:c r="H55" s="7"/>
+      <x:c r="G55" s="7" t="n"/>
+      <x:c r="H55" s="7" t="n"/>
       <x:c r="I55" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J55" s="7"/>
+      <x:c r="J55" s="7" t="n"/>
       <x:c r="K55" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L55" s="7"/>
-      <x:c r="M55" s="7"/>
+      <x:c r="L55" s="7" t="n"/>
+      <x:c r="M55" s="7" t="n"/>
       <x:c r="N55" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis visit derived from source visit/date and dataset-specific visit window rules.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O55" s="7"/>
-      <x:c r="P55" s="7"/>
+      <x:c r="O55" s="7" t="n"/>
+      <x:c r="P55" s="7" t="n"/>
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
       <x:c r="A56" s="7" t="n">
@@ -3924,28 +3902,28 @@
       <x:c r="F56" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G56" s="7"/>
-      <x:c r="H56" s="7"/>
+      <x:c r="G56" s="7" t="n"/>
+      <x:c r="H56" s="7" t="n"/>
       <x:c r="I56" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J56" s="7"/>
+      <x:c r="J56" s="7" t="n"/>
       <x:c r="K56" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol</x:t>
         </x:is>
       </x:c>
-      <x:c r="L56" s="7"/>
-      <x:c r="M56" s="7"/>
+      <x:c r="L56" s="7" t="n"/>
+      <x:c r="M56" s="7" t="n"/>
       <x:c r="N56" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol identifier from config/study_config.yaml and SDTM study domain records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O56" s="7"/>
-      <x:c r="P56" s="7"/>
+      <x:c r="O56" s="7" t="n"/>
+      <x:c r="P56" s="7" t="n"/>
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
       <x:c r="A57" s="7" t="n">
@@ -3974,28 +3952,28 @@
       <x:c r="F57" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G57" s="7"/>
-      <x:c r="H57" s="7"/>
+      <x:c r="G57" s="7" t="n"/>
+      <x:c r="H57" s="7" t="n"/>
       <x:c r="I57" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J57" s="7"/>
+      <x:c r="J57" s="7" t="n"/>
       <x:c r="K57" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L57" s="7"/>
-      <x:c r="M57" s="7"/>
+      <x:c r="L57" s="7" t="n"/>
+      <x:c r="M57" s="7" t="n"/>
       <x:c r="N57" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.USUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O57" s="7"/>
-      <x:c r="P57" s="7"/>
+      <x:c r="O57" s="7" t="n"/>
+      <x:c r="P57" s="7" t="n"/>
     </x:row>
     <x:row r="58" ht="42" customHeight="1">
       <x:c r="A58" s="7" t="n">
@@ -4024,28 +4002,28 @@
       <x:c r="F58" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G58" s="7"/>
-      <x:c r="H58" s="7"/>
+      <x:c r="G58" s="7" t="n"/>
+      <x:c r="H58" s="7" t="n"/>
       <x:c r="I58" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J58" s="7"/>
+      <x:c r="J58" s="7" t="n"/>
       <x:c r="K58" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L58" s="7"/>
-      <x:c r="M58" s="7"/>
+      <x:c r="L58" s="7" t="n"/>
+      <x:c r="M58" s="7" t="n"/>
       <x:c r="N58" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O58" s="7"/>
-      <x:c r="P58" s="7"/>
+      <x:c r="O58" s="7" t="n"/>
+      <x:c r="P58" s="7" t="n"/>
     </x:row>
     <x:row r="59" ht="42" customHeight="1">
       <x:c r="A59" s="7" t="n">
@@ -4074,28 +4052,28 @@
       <x:c r="F59" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G59" s="7"/>
-      <x:c r="H59" s="7"/>
+      <x:c r="G59" s="7" t="n"/>
+      <x:c r="H59" s="7" t="n"/>
       <x:c r="I59" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J59" s="7"/>
+      <x:c r="J59" s="7" t="n"/>
       <x:c r="K59" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L59" s="7"/>
-      <x:c r="M59" s="7"/>
+      <x:c r="L59" s="7" t="n"/>
+      <x:c r="M59" s="7" t="n"/>
       <x:c r="N59" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O59" s="7"/>
-      <x:c r="P59" s="7"/>
+      <x:c r="O59" s="7" t="n"/>
+      <x:c r="P59" s="7" t="n"/>
     </x:row>
     <x:row r="60" ht="42" customHeight="1">
       <x:c r="A60" s="7" t="n">
@@ -4124,28 +4102,28 @@
       <x:c r="F60" s="7" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G60" s="7"/>
-      <x:c r="H60" s="7"/>
+      <x:c r="G60" s="7" t="n"/>
+      <x:c r="H60" s="7" t="n"/>
       <x:c r="I60" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J60" s="7"/>
+      <x:c r="J60" s="7" t="n"/>
       <x:c r="K60" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L60" s="7"/>
-      <x:c r="M60" s="7"/>
+      <x:c r="L60" s="7" t="n"/>
+      <x:c r="M60" s="7" t="n"/>
       <x:c r="N60" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O60" s="7"/>
-      <x:c r="P60" s="7"/>
+      <x:c r="O60" s="7" t="n"/>
+      <x:c r="P60" s="7" t="n"/>
     </x:row>
     <x:row r="61" ht="42" customHeight="1">
       <x:c r="A61" s="7" t="n">
@@ -4174,20 +4152,20 @@
       <x:c r="F61" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G61" s="7"/>
-      <x:c r="H61" s="7"/>
+      <x:c r="G61" s="7" t="n"/>
+      <x:c r="H61" s="7" t="n"/>
       <x:c r="I61" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J61" s="7"/>
+      <x:c r="J61" s="7" t="n"/>
       <x:c r="K61" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L61" s="7"/>
+      <x:c r="L61" s="7" t="n"/>
       <x:c r="M61" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADCM_ASTDT</x:t>
@@ -4198,8 +4176,8 @@
           <x:t xml:space="preserve">Analysis start date derived from source start date.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O61" s="7"/>
-      <x:c r="P61" s="7"/>
+      <x:c r="O61" s="7" t="n"/>
+      <x:c r="P61" s="7" t="n"/>
     </x:row>
     <x:row r="62" ht="42" customHeight="1">
       <x:c r="A62" s="7" t="n">
@@ -4228,20 +4206,20 @@
       <x:c r="F62" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G62" s="7"/>
-      <x:c r="H62" s="7"/>
+      <x:c r="G62" s="7" t="n"/>
+      <x:c r="H62" s="7" t="n"/>
       <x:c r="I62" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J62" s="7"/>
+      <x:c r="J62" s="7" t="n"/>
       <x:c r="K62" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L62" s="7"/>
+      <x:c r="L62" s="7" t="n"/>
       <x:c r="M62" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADCM_AENDT</x:t>
@@ -4252,8 +4230,8 @@
           <x:t xml:space="preserve">Analysis end date derived from source end date.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O62" s="7"/>
-      <x:c r="P62" s="7"/>
+      <x:c r="O62" s="7" t="n"/>
+      <x:c r="P62" s="7" t="n"/>
     </x:row>
     <x:row r="63" ht="42" customHeight="1">
       <x:c r="A63" s="7" t="n">
@@ -4282,28 +4260,28 @@
       <x:c r="F63" s="7" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G63" s="7"/>
-      <x:c r="H63" s="7"/>
+      <x:c r="G63" s="7" t="n"/>
+      <x:c r="H63" s="7" t="n"/>
       <x:c r="I63" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J63" s="7"/>
+      <x:c r="J63" s="7" t="n"/>
       <x:c r="K63" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L63" s="7"/>
-      <x:c r="M63" s="7"/>
+      <x:c r="L63" s="7" t="n"/>
+      <x:c r="M63" s="7" t="n"/>
       <x:c r="N63" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O63" s="7"/>
-      <x:c r="P63" s="7"/>
+      <x:c r="O63" s="7" t="n"/>
+      <x:c r="P63" s="7" t="n"/>
     </x:row>
     <x:row r="64" ht="42" customHeight="1">
       <x:c r="A64" s="7" t="n">
@@ -4332,20 +4310,20 @@
       <x:c r="F64" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G64" s="7"/>
-      <x:c r="H64" s="7"/>
+      <x:c r="G64" s="7" t="n"/>
+      <x:c r="H64" s="7" t="n"/>
       <x:c r="I64" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J64" s="7"/>
+      <x:c r="J64" s="7" t="n"/>
       <x:c r="K64" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L64" s="7"/>
+      <x:c r="L64" s="7" t="n"/>
       <x:c r="M64" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADCM_ASTDY</x:t>
@@ -4356,8 +4334,8 @@
           <x:t xml:space="preserve">Analysis start relative day derived from ASTDT and ADSL.TRTSDT.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O64" s="7"/>
-      <x:c r="P64" s="7"/>
+      <x:c r="O64" s="7" t="n"/>
+      <x:c r="P64" s="7" t="n"/>
     </x:row>
     <x:row r="65" ht="42" customHeight="1">
       <x:c r="A65" s="7" t="n">
@@ -4386,8 +4364,8 @@
       <x:c r="F65" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G65" s="7"/>
-      <x:c r="H65" s="7"/>
+      <x:c r="G65" s="7" t="n"/>
+      <x:c r="H65" s="7" t="n"/>
       <x:c r="I65" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -4403,15 +4381,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L65" s="7"/>
-      <x:c r="M65" s="7"/>
+      <x:c r="L65" s="7" t="n"/>
+      <x:c r="M65" s="7" t="n"/>
       <x:c r="N65" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O65" s="7"/>
-      <x:c r="P65" s="7"/>
+      <x:c r="O65" s="7" t="n"/>
+      <x:c r="P65" s="7" t="n"/>
     </x:row>
     <x:row r="66" ht="42" customHeight="1">
       <x:c r="A66" s="7" t="n">
@@ -4440,8 +4418,8 @@
       <x:c r="F66" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G66" s="7"/>
-      <x:c r="H66" s="7"/>
+      <x:c r="G66" s="7" t="n"/>
+      <x:c r="H66" s="7" t="n"/>
       <x:c r="I66" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -4457,15 +4435,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L66" s="7"/>
-      <x:c r="M66" s="7"/>
+      <x:c r="L66" s="7" t="n"/>
+      <x:c r="M66" s="7" t="n"/>
       <x:c r="N66" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O66" s="7"/>
-      <x:c r="P66" s="7"/>
+      <x:c r="O66" s="7" t="n"/>
+      <x:c r="P66" s="7" t="n"/>
     </x:row>
     <x:row r="67" ht="42" customHeight="1">
       <x:c r="A67" s="7" t="n">
@@ -4494,8 +4472,8 @@
       <x:c r="F67" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G67" s="7"/>
-      <x:c r="H67" s="7"/>
+      <x:c r="G67" s="7" t="n"/>
+      <x:c r="H67" s="7" t="n"/>
       <x:c r="I67" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -4511,15 +4489,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L67" s="7"/>
-      <x:c r="M67" s="7"/>
+      <x:c r="L67" s="7" t="n"/>
+      <x:c r="M67" s="7" t="n"/>
       <x:c r="N67" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O67" s="7"/>
-      <x:c r="P67" s="7"/>
+      <x:c r="O67" s="7" t="n"/>
+      <x:c r="P67" s="7" t="n"/>
     </x:row>
     <x:row r="68" ht="42" customHeight="1">
       <x:c r="A68" s="7" t="n">
@@ -4548,28 +4526,28 @@
       <x:c r="F68" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G68" s="7"/>
-      <x:c r="H68" s="7"/>
+      <x:c r="G68" s="7" t="n"/>
+      <x:c r="H68" s="7" t="n"/>
       <x:c r="I68" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J68" s="7"/>
+      <x:c r="J68" s="7" t="n"/>
       <x:c r="K68" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L68" s="7"/>
-      <x:c r="M68" s="7"/>
+      <x:c r="L68" s="7" t="n"/>
+      <x:c r="M68" s="7" t="n"/>
       <x:c r="N68" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O68" s="7"/>
-      <x:c r="P68" s="7"/>
+      <x:c r="O68" s="7" t="n"/>
+      <x:c r="P68" s="7" t="n"/>
     </x:row>
     <x:row r="69" ht="42" customHeight="1">
       <x:c r="A69" s="7" t="n">
@@ -4598,8 +4576,8 @@
       <x:c r="F69" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G69" s="7"/>
-      <x:c r="H69" s="7"/>
+      <x:c r="G69" s="7" t="n"/>
+      <x:c r="H69" s="7" t="n"/>
       <x:c r="I69" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -4615,15 +4593,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L69" s="7"/>
-      <x:c r="M69" s="7"/>
+      <x:c r="L69" s="7" t="n"/>
+      <x:c r="M69" s="7" t="n"/>
       <x:c r="N69" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O69" s="7"/>
-      <x:c r="P69" s="7"/>
+      <x:c r="O69" s="7" t="n"/>
+      <x:c r="P69" s="7" t="n"/>
     </x:row>
     <x:row r="70" ht="42" customHeight="1">
       <x:c r="A70" s="7" t="n">
@@ -4652,8 +4630,8 @@
       <x:c r="F70" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G70" s="7"/>
-      <x:c r="H70" s="7"/>
+      <x:c r="G70" s="7" t="n"/>
+      <x:c r="H70" s="7" t="n"/>
       <x:c r="I70" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -4669,15 +4647,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L70" s="7"/>
-      <x:c r="M70" s="7"/>
+      <x:c r="L70" s="7" t="n"/>
+      <x:c r="M70" s="7" t="n"/>
       <x:c r="N70" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.CM plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O70" s="7"/>
-      <x:c r="P70" s="7"/>
+      <x:c r="O70" s="7" t="n"/>
+      <x:c r="P70" s="7" t="n"/>
     </x:row>
     <x:row r="71" ht="42" customHeight="1">
       <x:c r="A71" s="7" t="n">
@@ -4706,28 +4684,28 @@
       <x:c r="F71" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G71" s="7"/>
-      <x:c r="H71" s="7"/>
+      <x:c r="G71" s="7" t="n"/>
+      <x:c r="H71" s="7" t="n"/>
       <x:c r="I71" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J71" s="7"/>
+      <x:c r="J71" s="7" t="n"/>
       <x:c r="K71" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol</x:t>
         </x:is>
       </x:c>
-      <x:c r="L71" s="7"/>
-      <x:c r="M71" s="7"/>
+      <x:c r="L71" s="7" t="n"/>
+      <x:c r="M71" s="7" t="n"/>
       <x:c r="N71" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol identifier from config/study_config.yaml and SDTM study domain records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O71" s="7"/>
-      <x:c r="P71" s="7"/>
+      <x:c r="O71" s="7" t="n"/>
+      <x:c r="P71" s="7" t="n"/>
     </x:row>
     <x:row r="72" ht="42" customHeight="1">
       <x:c r="A72" s="7" t="n">
@@ -4756,28 +4734,28 @@
       <x:c r="F72" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G72" s="7"/>
-      <x:c r="H72" s="7"/>
+      <x:c r="G72" s="7" t="n"/>
+      <x:c r="H72" s="7" t="n"/>
       <x:c r="I72" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J72" s="7"/>
+      <x:c r="J72" s="7" t="n"/>
       <x:c r="K72" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L72" s="7"/>
-      <x:c r="M72" s="7"/>
+      <x:c r="L72" s="7" t="n"/>
+      <x:c r="M72" s="7" t="n"/>
       <x:c r="N72" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.USUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O72" s="7"/>
-      <x:c r="P72" s="7"/>
+      <x:c r="O72" s="7" t="n"/>
+      <x:c r="P72" s="7" t="n"/>
     </x:row>
     <x:row r="73" ht="42" customHeight="1">
       <x:c r="A73" s="7" t="n">
@@ -4806,28 +4784,28 @@
       <x:c r="F73" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G73" s="7"/>
-      <x:c r="H73" s="7"/>
+      <x:c r="G73" s="7" t="n"/>
+      <x:c r="H73" s="7" t="n"/>
       <x:c r="I73" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J73" s="7"/>
+      <x:c r="J73" s="7" t="n"/>
       <x:c r="K73" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L73" s="7"/>
-      <x:c r="M73" s="7"/>
+      <x:c r="L73" s="7" t="n"/>
+      <x:c r="M73" s="7" t="n"/>
       <x:c r="N73" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O73" s="7"/>
-      <x:c r="P73" s="7"/>
+      <x:c r="O73" s="7" t="n"/>
+      <x:c r="P73" s="7" t="n"/>
     </x:row>
     <x:row r="74" ht="42" customHeight="1">
       <x:c r="A74" s="7" t="n">
@@ -4856,28 +4834,28 @@
       <x:c r="F74" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G74" s="7"/>
-      <x:c r="H74" s="7"/>
+      <x:c r="G74" s="7" t="n"/>
+      <x:c r="H74" s="7" t="n"/>
       <x:c r="I74" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J74" s="7"/>
+      <x:c r="J74" s="7" t="n"/>
       <x:c r="K74" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L74" s="7"/>
-      <x:c r="M74" s="7"/>
+      <x:c r="L74" s="7" t="n"/>
+      <x:c r="M74" s="7" t="n"/>
       <x:c r="N74" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O74" s="7"/>
-      <x:c r="P74" s="7"/>
+      <x:c r="O74" s="7" t="n"/>
+      <x:c r="P74" s="7" t="n"/>
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
       <x:c r="A75" s="7" t="n">
@@ -4906,28 +4884,28 @@
       <x:c r="F75" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G75" s="7"/>
-      <x:c r="H75" s="7"/>
+      <x:c r="G75" s="7" t="n"/>
+      <x:c r="H75" s="7" t="n"/>
       <x:c r="I75" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J75" s="7"/>
+      <x:c r="J75" s="7" t="n"/>
       <x:c r="K75" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L75" s="7"/>
-      <x:c r="M75" s="7"/>
+      <x:c r="L75" s="7" t="n"/>
+      <x:c r="M75" s="7" t="n"/>
       <x:c r="N75" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O75" s="7"/>
-      <x:c r="P75" s="7"/>
+      <x:c r="O75" s="7" t="n"/>
+      <x:c r="P75" s="7" t="n"/>
     </x:row>
     <x:row r="76" ht="42" customHeight="1">
       <x:c r="A76" s="7" t="n">
@@ -4956,28 +4934,28 @@
       <x:c r="F76" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G76" s="7"/>
-      <x:c r="H76" s="7"/>
+      <x:c r="G76" s="7" t="n"/>
+      <x:c r="H76" s="7" t="n"/>
       <x:c r="I76" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J76" s="7"/>
+      <x:c r="J76" s="7" t="n"/>
       <x:c r="K76" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L76" s="7"/>
-      <x:c r="M76" s="7"/>
+      <x:c r="L76" s="7" t="n"/>
+      <x:c r="M76" s="7" t="n"/>
       <x:c r="N76" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O76" s="7"/>
-      <x:c r="P76" s="7"/>
+      <x:c r="O76" s="7" t="n"/>
+      <x:c r="P76" s="7" t="n"/>
     </x:row>
     <x:row r="77" ht="42" customHeight="1">
       <x:c r="A77" s="7" t="n">
@@ -5006,20 +4984,20 @@
       <x:c r="F77" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G77" s="7"/>
-      <x:c r="H77" s="7"/>
+      <x:c r="G77" s="7" t="n"/>
+      <x:c r="H77" s="7" t="n"/>
       <x:c r="I77" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J77" s="7"/>
+      <x:c r="J77" s="7" t="n"/>
       <x:c r="K77" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L77" s="7"/>
+      <x:c r="L77" s="7" t="n"/>
       <x:c r="M77" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADAE_ATOXGR</x:t>
@@ -5030,8 +5008,8 @@
           <x:t xml:space="preserve">Numeric toxicity grade derived from SDTM.AE toxicity grade/severity source fields.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O77" s="7"/>
-      <x:c r="P77" s="7"/>
+      <x:c r="O77" s="7" t="n"/>
+      <x:c r="P77" s="7" t="n"/>
     </x:row>
     <x:row r="78" ht="42" customHeight="1">
       <x:c r="A78" s="7" t="n">
@@ -5060,8 +5038,8 @@
       <x:c r="F78" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G78" s="7"/>
-      <x:c r="H78" s="7"/>
+      <x:c r="G78" s="7" t="n"/>
+      <x:c r="H78" s="7" t="n"/>
       <x:c r="I78" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -5077,15 +5055,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L78" s="7"/>
-      <x:c r="M78" s="7"/>
+      <x:c r="L78" s="7" t="n"/>
+      <x:c r="M78" s="7" t="n"/>
       <x:c r="N78" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O78" s="7"/>
-      <x:c r="P78" s="7"/>
+      <x:c r="O78" s="7" t="n"/>
+      <x:c r="P78" s="7" t="n"/>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
       <x:c r="A79" s="7" t="n">
@@ -5114,28 +5092,28 @@
       <x:c r="F79" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G79" s="7"/>
-      <x:c r="H79" s="7"/>
+      <x:c r="G79" s="7" t="n"/>
+      <x:c r="H79" s="7" t="n"/>
       <x:c r="I79" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J79" s="7"/>
+      <x:c r="J79" s="7" t="n"/>
       <x:c r="K79" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L79" s="7"/>
-      <x:c r="M79" s="7"/>
+      <x:c r="L79" s="7" t="n"/>
+      <x:c r="M79" s="7" t="n"/>
       <x:c r="N79" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O79" s="7"/>
-      <x:c r="P79" s="7"/>
+      <x:c r="O79" s="7" t="n"/>
+      <x:c r="P79" s="7" t="n"/>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="7" t="n">
@@ -5164,28 +5142,28 @@
       <x:c r="F80" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G80" s="7"/>
-      <x:c r="H80" s="7"/>
+      <x:c r="G80" s="7" t="n"/>
+      <x:c r="H80" s="7" t="n"/>
       <x:c r="I80" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J80" s="7"/>
+      <x:c r="J80" s="7" t="n"/>
       <x:c r="K80" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L80" s="7"/>
-      <x:c r="M80" s="7"/>
+      <x:c r="L80" s="7" t="n"/>
+      <x:c r="M80" s="7" t="n"/>
       <x:c r="N80" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis start date derived from source start date.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O80" s="7"/>
-      <x:c r="P80" s="7"/>
+      <x:c r="O80" s="7" t="n"/>
+      <x:c r="P80" s="7" t="n"/>
     </x:row>
     <x:row r="81" ht="42" customHeight="1">
       <x:c r="A81" s="7" t="n">
@@ -5214,28 +5192,28 @@
       <x:c r="F81" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G81" s="7"/>
-      <x:c r="H81" s="7"/>
+      <x:c r="G81" s="7" t="n"/>
+      <x:c r="H81" s="7" t="n"/>
       <x:c r="I81" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J81" s="7"/>
+      <x:c r="J81" s="7" t="n"/>
       <x:c r="K81" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L81" s="7"/>
-      <x:c r="M81" s="7"/>
+      <x:c r="L81" s="7" t="n"/>
+      <x:c r="M81" s="7" t="n"/>
       <x:c r="N81" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis end date derived from source end date.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O81" s="7"/>
-      <x:c r="P81" s="7"/>
+      <x:c r="O81" s="7" t="n"/>
+      <x:c r="P81" s="7" t="n"/>
     </x:row>
     <x:row r="82" ht="42" customHeight="1">
       <x:c r="A82" s="7" t="n">
@@ -5264,28 +5242,28 @@
       <x:c r="F82" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G82" s="7"/>
-      <x:c r="H82" s="7"/>
+      <x:c r="G82" s="7" t="n"/>
+      <x:c r="H82" s="7" t="n"/>
       <x:c r="I82" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J82" s="7"/>
+      <x:c r="J82" s="7" t="n"/>
       <x:c r="K82" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L82" s="7"/>
-      <x:c r="M82" s="7"/>
+      <x:c r="L82" s="7" t="n"/>
+      <x:c r="M82" s="7" t="n"/>
       <x:c r="N82" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis start relative day derived from ASTDT and ADSL.TRTSDT.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O82" s="7"/>
-      <x:c r="P82" s="7"/>
+      <x:c r="O82" s="7" t="n"/>
+      <x:c r="P82" s="7" t="n"/>
     </x:row>
     <x:row r="83" ht="42" customHeight="1">
       <x:c r="A83" s="7" t="n">
@@ -5314,28 +5292,28 @@
       <x:c r="F83" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G83" s="7"/>
-      <x:c r="H83" s="7"/>
+      <x:c r="G83" s="7" t="n"/>
+      <x:c r="H83" s="7" t="n"/>
       <x:c r="I83" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J83" s="7"/>
+      <x:c r="J83" s="7" t="n"/>
       <x:c r="K83" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L83" s="7"/>
-      <x:c r="M83" s="7"/>
+      <x:c r="L83" s="7" t="n"/>
+      <x:c r="M83" s="7" t="n"/>
       <x:c r="N83" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis end relative day derived from AENDT and ADSL.TRTSDT.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O83" s="7"/>
-      <x:c r="P83" s="7"/>
+      <x:c r="O83" s="7" t="n"/>
+      <x:c r="P83" s="7" t="n"/>
     </x:row>
     <x:row r="84" ht="42" customHeight="1">
       <x:c r="A84" s="7" t="n">
@@ -5364,28 +5342,28 @@
       <x:c r="F84" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G84" s="7"/>
-      <x:c r="H84" s="7"/>
+      <x:c r="G84" s="7" t="n"/>
+      <x:c r="H84" s="7" t="n"/>
       <x:c r="I84" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J84" s="7"/>
+      <x:c r="J84" s="7" t="n"/>
       <x:c r="K84" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L84" s="7"/>
-      <x:c r="M84" s="7"/>
+      <x:c r="L84" s="7" t="n"/>
+      <x:c r="M84" s="7" t="n"/>
       <x:c r="N84" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O84" s="7"/>
-      <x:c r="P84" s="7"/>
+      <x:c r="O84" s="7" t="n"/>
+      <x:c r="P84" s="7" t="n"/>
     </x:row>
     <x:row r="85" ht="42" customHeight="1">
       <x:c r="A85" s="7" t="n">
@@ -5414,28 +5392,28 @@
       <x:c r="F85" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G85" s="7"/>
-      <x:c r="H85" s="7"/>
+      <x:c r="G85" s="7" t="n"/>
+      <x:c r="H85" s="7" t="n"/>
       <x:c r="I85" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J85" s="7"/>
+      <x:c r="J85" s="7" t="n"/>
       <x:c r="K85" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L85" s="7"/>
-      <x:c r="M85" s="7"/>
+      <x:c r="L85" s="7" t="n"/>
+      <x:c r="M85" s="7" t="n"/>
       <x:c r="N85" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O85" s="7"/>
-      <x:c r="P85" s="7"/>
+      <x:c r="O85" s="7" t="n"/>
+      <x:c r="P85" s="7" t="n"/>
     </x:row>
     <x:row r="86" ht="42" customHeight="1">
       <x:c r="A86" s="7" t="n">
@@ -5464,28 +5442,28 @@
       <x:c r="F86" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G86" s="7"/>
-      <x:c r="H86" s="7"/>
+      <x:c r="G86" s="7" t="n"/>
+      <x:c r="H86" s="7" t="n"/>
       <x:c r="I86" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J86" s="7"/>
+      <x:c r="J86" s="7" t="n"/>
       <x:c r="K86" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L86" s="7"/>
-      <x:c r="M86" s="7"/>
+      <x:c r="L86" s="7" t="n"/>
+      <x:c r="M86" s="7" t="n"/>
       <x:c r="N86" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O86" s="7"/>
-      <x:c r="P86" s="7"/>
+      <x:c r="O86" s="7" t="n"/>
+      <x:c r="P86" s="7" t="n"/>
     </x:row>
     <x:row r="87" ht="42" customHeight="1">
       <x:c r="A87" s="7" t="n">
@@ -5514,28 +5492,28 @@
       <x:c r="F87" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G87" s="7"/>
-      <x:c r="H87" s="7"/>
+      <x:c r="G87" s="7" t="n"/>
+      <x:c r="H87" s="7" t="n"/>
       <x:c r="I87" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J87" s="7"/>
+      <x:c r="J87" s="7" t="n"/>
       <x:c r="K87" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L87" s="7"/>
-      <x:c r="M87" s="7"/>
+      <x:c r="L87" s="7" t="n"/>
+      <x:c r="M87" s="7" t="n"/>
       <x:c r="N87" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O87" s="7"/>
-      <x:c r="P87" s="7"/>
+      <x:c r="O87" s="7" t="n"/>
+      <x:c r="P87" s="7" t="n"/>
     </x:row>
     <x:row r="88" ht="42" customHeight="1">
       <x:c r="A88" s="7" t="n">
@@ -5564,28 +5542,28 @@
       <x:c r="F88" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G88" s="7"/>
-      <x:c r="H88" s="7"/>
+      <x:c r="G88" s="7" t="n"/>
+      <x:c r="H88" s="7" t="n"/>
       <x:c r="I88" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J88" s="7"/>
+      <x:c r="J88" s="7" t="n"/>
       <x:c r="K88" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L88" s="7"/>
-      <x:c r="M88" s="7"/>
+      <x:c r="L88" s="7" t="n"/>
+      <x:c r="M88" s="7" t="n"/>
       <x:c r="N88" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O88" s="7"/>
-      <x:c r="P88" s="7"/>
+      <x:c r="O88" s="7" t="n"/>
+      <x:c r="P88" s="7" t="n"/>
     </x:row>
     <x:row r="89" ht="42" customHeight="1">
       <x:c r="A89" s="7" t="n">
@@ -5614,28 +5592,28 @@
       <x:c r="F89" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G89" s="7"/>
-      <x:c r="H89" s="7"/>
+      <x:c r="G89" s="7" t="n"/>
+      <x:c r="H89" s="7" t="n"/>
       <x:c r="I89" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J89" s="7"/>
+      <x:c r="J89" s="7" t="n"/>
       <x:c r="K89" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L89" s="7"/>
-      <x:c r="M89" s="7"/>
+      <x:c r="L89" s="7" t="n"/>
+      <x:c r="M89" s="7" t="n"/>
       <x:c r="N89" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O89" s="7"/>
-      <x:c r="P89" s="7"/>
+      <x:c r="O89" s="7" t="n"/>
+      <x:c r="P89" s="7" t="n"/>
     </x:row>
     <x:row r="90" ht="42" customHeight="1">
       <x:c r="A90" s="7" t="n">
@@ -5664,28 +5642,28 @@
       <x:c r="F90" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G90" s="7"/>
-      <x:c r="H90" s="7"/>
+      <x:c r="G90" s="7" t="n"/>
+      <x:c r="H90" s="7" t="n"/>
       <x:c r="I90" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J90" s="7"/>
+      <x:c r="J90" s="7" t="n"/>
       <x:c r="K90" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L90" s="7"/>
-      <x:c r="M90" s="7"/>
+      <x:c r="L90" s="7" t="n"/>
+      <x:c r="M90" s="7" t="n"/>
       <x:c r="N90" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O90" s="7"/>
-      <x:c r="P90" s="7"/>
+      <x:c r="O90" s="7" t="n"/>
+      <x:c r="P90" s="7" t="n"/>
     </x:row>
     <x:row r="91" ht="42" customHeight="1">
       <x:c r="A91" s="7" t="n">
@@ -5714,28 +5692,28 @@
       <x:c r="F91" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G91" s="7"/>
-      <x:c r="H91" s="7"/>
+      <x:c r="G91" s="7" t="n"/>
+      <x:c r="H91" s="7" t="n"/>
       <x:c r="I91" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J91" s="7"/>
+      <x:c r="J91" s="7" t="n"/>
       <x:c r="K91" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L91" s="7"/>
-      <x:c r="M91" s="7"/>
+      <x:c r="L91" s="7" t="n"/>
+      <x:c r="M91" s="7" t="n"/>
       <x:c r="N91" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O91" s="7"/>
-      <x:c r="P91" s="7"/>
+      <x:c r="O91" s="7" t="n"/>
+      <x:c r="P91" s="7" t="n"/>
     </x:row>
     <x:row r="92" ht="42" customHeight="1">
       <x:c r="A92" s="7" t="n">
@@ -5764,28 +5742,28 @@
       <x:c r="F92" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G92" s="7"/>
-      <x:c r="H92" s="7"/>
+      <x:c r="G92" s="7" t="n"/>
+      <x:c r="H92" s="7" t="n"/>
       <x:c r="I92" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J92" s="7"/>
+      <x:c r="J92" s="7" t="n"/>
       <x:c r="K92" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L92" s="7"/>
-      <x:c r="M92" s="7"/>
+      <x:c r="L92" s="7" t="n"/>
+      <x:c r="M92" s="7" t="n"/>
       <x:c r="N92" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O92" s="7"/>
-      <x:c r="P92" s="7"/>
+      <x:c r="O92" s="7" t="n"/>
+      <x:c r="P92" s="7" t="n"/>
     </x:row>
     <x:row r="93" ht="42" customHeight="1">
       <x:c r="A93" s="7" t="n">
@@ -5814,8 +5792,8 @@
       <x:c r="F93" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G93" s="7"/>
-      <x:c r="H93" s="7"/>
+      <x:c r="G93" s="7" t="n"/>
+      <x:c r="H93" s="7" t="n"/>
       <x:c r="I93" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -5831,15 +5809,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L93" s="7"/>
-      <x:c r="M93" s="7"/>
+      <x:c r="L93" s="7" t="n"/>
+      <x:c r="M93" s="7" t="n"/>
       <x:c r="N93" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O93" s="7"/>
-      <x:c r="P93" s="7"/>
+      <x:c r="O93" s="7" t="n"/>
+      <x:c r="P93" s="7" t="n"/>
     </x:row>
     <x:row r="94" ht="42" customHeight="1">
       <x:c r="A94" s="7" t="n">
@@ -5868,8 +5846,8 @@
       <x:c r="F94" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G94" s="7"/>
-      <x:c r="H94" s="7"/>
+      <x:c r="G94" s="7" t="n"/>
+      <x:c r="H94" s="7" t="n"/>
       <x:c r="I94" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -5885,15 +5863,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L94" s="7"/>
-      <x:c r="M94" s="7"/>
+      <x:c r="L94" s="7" t="n"/>
+      <x:c r="M94" s="7" t="n"/>
       <x:c r="N94" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Treatment-emergent flag derived from ADAE.ASTDT and ADSL.TRTSDT.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O94" s="7"/>
-      <x:c r="P94" s="7"/>
+      <x:c r="O94" s="7" t="n"/>
+      <x:c r="P94" s="7" t="n"/>
     </x:row>
     <x:row r="95" ht="42" customHeight="1">
       <x:c r="A95" s="7" t="n">
@@ -5922,28 +5900,28 @@
       <x:c r="F95" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G95" s="7"/>
-      <x:c r="H95" s="7"/>
+      <x:c r="G95" s="7" t="n"/>
+      <x:c r="H95" s="7" t="n"/>
       <x:c r="I95" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J95" s="7"/>
+      <x:c r="J95" s="7" t="n"/>
       <x:c r="K95" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L95" s="7"/>
-      <x:c r="M95" s="7"/>
+      <x:c r="L95" s="7" t="n"/>
+      <x:c r="M95" s="7" t="n"/>
       <x:c r="N95" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Adverse event duration derived from ADAE.ASTDT and ADAE.AENDT.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O95" s="7"/>
-      <x:c r="P95" s="7"/>
+      <x:c r="O95" s="7" t="n"/>
+      <x:c r="P95" s="7" t="n"/>
     </x:row>
     <x:row r="96" ht="42" customHeight="1">
       <x:c r="A96" s="7" t="n">
@@ -5972,28 +5950,28 @@
       <x:c r="F96" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G96" s="7"/>
-      <x:c r="H96" s="7"/>
+      <x:c r="G96" s="7" t="n"/>
+      <x:c r="H96" s="7" t="n"/>
       <x:c r="I96" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J96" s="7"/>
+      <x:c r="J96" s="7" t="n"/>
       <x:c r="K96" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L96" s="7"/>
-      <x:c r="M96" s="7"/>
+      <x:c r="L96" s="7" t="n"/>
+      <x:c r="M96" s="7" t="n"/>
       <x:c r="N96" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Duration unit assigned by adverse-event derivation rule.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O96" s="7"/>
-      <x:c r="P96" s="7"/>
+      <x:c r="O96" s="7" t="n"/>
+      <x:c r="P96" s="7" t="n"/>
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
       <x:c r="A97" s="7" t="n">
@@ -6022,28 +6000,28 @@
       <x:c r="F97" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G97" s="7"/>
-      <x:c r="H97" s="7"/>
+      <x:c r="G97" s="7" t="n"/>
+      <x:c r="H97" s="7" t="n"/>
       <x:c r="I97" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J97" s="7"/>
+      <x:c r="J97" s="7" t="n"/>
       <x:c r="K97" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L97" s="7"/>
-      <x:c r="M97" s="7"/>
+      <x:c r="L97" s="7" t="n"/>
+      <x:c r="M97" s="7" t="n"/>
       <x:c r="N97" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.AE/SUPPAE plus ADSL treatment and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O97" s="7"/>
-      <x:c r="P97" s="7"/>
+      <x:c r="O97" s="7" t="n"/>
+      <x:c r="P97" s="7" t="n"/>
     </x:row>
     <x:row r="98" ht="42" customHeight="1">
       <x:c r="A98" s="7" t="n">
@@ -6072,8 +6050,8 @@
       <x:c r="F98" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G98" s="7"/>
-      <x:c r="H98" s="7"/>
+      <x:c r="G98" s="7" t="n"/>
+      <x:c r="H98" s="7" t="n"/>
       <x:c r="I98" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -6089,15 +6067,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L98" s="7"/>
-      <x:c r="M98" s="7"/>
+      <x:c r="L98" s="7" t="n"/>
+      <x:c r="M98" s="7" t="n"/>
       <x:c r="N98" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Actual treatment assignment inherited from ADSL.TRT01A.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O98" s="7"/>
-      <x:c r="P98" s="7"/>
+      <x:c r="O98" s="7" t="n"/>
+      <x:c r="P98" s="7" t="n"/>
     </x:row>
     <x:row r="99" ht="42" customHeight="1">
       <x:c r="A99" s="7" t="n">
@@ -6126,8 +6104,8 @@
       <x:c r="F99" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G99" s="7"/>
-      <x:c r="H99" s="7"/>
+      <x:c r="G99" s="7" t="n"/>
+      <x:c r="H99" s="7" t="n"/>
       <x:c r="I99" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -6143,15 +6121,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L99" s="7"/>
-      <x:c r="M99" s="7"/>
+      <x:c r="L99" s="7" t="n"/>
+      <x:c r="M99" s="7" t="n"/>
       <x:c r="N99" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Numeric actual treatment assignment inherited from ADSL.TRT01AN.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O99" s="7"/>
-      <x:c r="P99" s="7"/>
+      <x:c r="O99" s="7" t="n"/>
+      <x:c r="P99" s="7" t="n"/>
     </x:row>
     <x:row r="100" ht="42" customHeight="1">
       <x:c r="A100" s="7" t="n">
@@ -6180,28 +6158,28 @@
       <x:c r="F100" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G100" s="7"/>
-      <x:c r="H100" s="7"/>
+      <x:c r="G100" s="7" t="n"/>
+      <x:c r="H100" s="7" t="n"/>
       <x:c r="I100" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J100" s="7"/>
+      <x:c r="J100" s="7" t="n"/>
       <x:c r="K100" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol</x:t>
         </x:is>
       </x:c>
-      <x:c r="L100" s="7"/>
-      <x:c r="M100" s="7"/>
+      <x:c r="L100" s="7" t="n"/>
+      <x:c r="M100" s="7" t="n"/>
       <x:c r="N100" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol identifier from config/study_config.yaml and SDTM study domain records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O100" s="7"/>
-      <x:c r="P100" s="7"/>
+      <x:c r="O100" s="7" t="n"/>
+      <x:c r="P100" s="7" t="n"/>
     </x:row>
     <x:row r="101" ht="42" customHeight="1">
       <x:c r="A101" s="7" t="n">
@@ -6230,28 +6208,28 @@
       <x:c r="F101" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G101" s="7"/>
-      <x:c r="H101" s="7"/>
+      <x:c r="G101" s="7" t="n"/>
+      <x:c r="H101" s="7" t="n"/>
       <x:c r="I101" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J101" s="7"/>
+      <x:c r="J101" s="7" t="n"/>
       <x:c r="K101" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L101" s="7"/>
-      <x:c r="M101" s="7"/>
+      <x:c r="L101" s="7" t="n"/>
+      <x:c r="M101" s="7" t="n"/>
       <x:c r="N101" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.USUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O101" s="7"/>
-      <x:c r="P101" s="7"/>
+      <x:c r="O101" s="7" t="n"/>
+      <x:c r="P101" s="7" t="n"/>
     </x:row>
     <x:row r="102" ht="42" customHeight="1">
       <x:c r="A102" s="7" t="n">
@@ -6280,28 +6258,28 @@
       <x:c r="F102" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G102" s="7"/>
-      <x:c r="H102" s="7"/>
+      <x:c r="G102" s="7" t="n"/>
+      <x:c r="H102" s="7" t="n"/>
       <x:c r="I102" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J102" s="7"/>
+      <x:c r="J102" s="7" t="n"/>
       <x:c r="K102" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L102" s="7"/>
-      <x:c r="M102" s="7"/>
+      <x:c r="L102" s="7" t="n"/>
+      <x:c r="M102" s="7" t="n"/>
       <x:c r="N102" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.SUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O102" s="7"/>
-      <x:c r="P102" s="7"/>
+      <x:c r="O102" s="7" t="n"/>
+      <x:c r="P102" s="7" t="n"/>
     </x:row>
     <x:row r="103" ht="42" customHeight="1">
       <x:c r="A103" s="7" t="n">
@@ -6330,8 +6308,8 @@
       <x:c r="F103" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G103" s="7"/>
-      <x:c r="H103" s="7"/>
+      <x:c r="G103" s="7" t="n"/>
+      <x:c r="H103" s="7" t="n"/>
       <x:c r="I103" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -6347,15 +6325,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L103" s="7"/>
-      <x:c r="M103" s="7"/>
+      <x:c r="L103" s="7" t="n"/>
+      <x:c r="M103" s="7" t="n"/>
       <x:c r="N103" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Randomized/planned treatment assignment from SDTM.DM.ARM and config/study_config.yaml treatment map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O103" s="7"/>
-      <x:c r="P103" s="7"/>
+      <x:c r="O103" s="7" t="n"/>
+      <x:c r="P103" s="7" t="n"/>
     </x:row>
     <x:row r="104" ht="42" customHeight="1">
       <x:c r="A104" s="7" t="n">
@@ -6384,28 +6362,28 @@
       <x:c r="F104" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G104" s="7"/>
-      <x:c r="H104" s="7"/>
+      <x:c r="G104" s="7" t="n"/>
+      <x:c r="H104" s="7" t="n"/>
       <x:c r="I104" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J104" s="7"/>
+      <x:c r="J104" s="7" t="n"/>
       <x:c r="K104" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L104" s="7"/>
-      <x:c r="M104" s="7"/>
+      <x:c r="L104" s="7" t="n"/>
+      <x:c r="M104" s="7" t="n"/>
       <x:c r="N104" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Treatment start date inherited from ADSL.TRTSDT unless defined directly for ADSL.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O104" s="7"/>
-      <x:c r="P104" s="7"/>
+      <x:c r="O104" s="7" t="n"/>
+      <x:c r="P104" s="7" t="n"/>
     </x:row>
     <x:row r="105" ht="42" customHeight="1">
       <x:c r="A105" s="7" t="n">
@@ -6434,8 +6412,8 @@
       <x:c r="F105" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G105" s="7"/>
-      <x:c r="H105" s="7"/>
+      <x:c r="G105" s="7" t="n"/>
+      <x:c r="H105" s="7" t="n"/>
       <x:c r="I105" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -6451,15 +6429,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L105" s="7"/>
-      <x:c r="M105" s="7"/>
+      <x:c r="L105" s="7" t="n"/>
+      <x:c r="M105" s="7" t="n"/>
       <x:c r="N105" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter code from dataset-specific parameter derivation and source test/category.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O105" s="7"/>
-      <x:c r="P105" s="7"/>
+      <x:c r="O105" s="7" t="n"/>
+      <x:c r="P105" s="7" t="n"/>
     </x:row>
     <x:row r="106" ht="42" customHeight="1">
       <x:c r="A106" s="7" t="n">
@@ -6488,28 +6466,28 @@
       <x:c r="F106" s="7" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G106" s="7"/>
-      <x:c r="H106" s="7"/>
+      <x:c r="G106" s="7" t="n"/>
+      <x:c r="H106" s="7" t="n"/>
       <x:c r="I106" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J106" s="7"/>
+      <x:c r="J106" s="7" t="n"/>
       <x:c r="K106" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L106" s="7"/>
-      <x:c r="M106" s="7"/>
+      <x:c r="L106" s="7" t="n"/>
+      <x:c r="M106" s="7" t="n"/>
       <x:c r="N106" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter label from dataset-specific parameter derivation and source test/category.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O106" s="7"/>
-      <x:c r="P106" s="7"/>
+      <x:c r="O106" s="7" t="n"/>
+      <x:c r="P106" s="7" t="n"/>
     </x:row>
     <x:row r="107" ht="42" customHeight="1">
       <x:c r="A107" s="7" t="n">
@@ -6538,28 +6516,28 @@
       <x:c r="F107" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G107" s="7"/>
-      <x:c r="H107" s="7"/>
+      <x:c r="G107" s="7" t="n"/>
+      <x:c r="H107" s="7" t="n"/>
       <x:c r="I107" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J107" s="7"/>
+      <x:c r="J107" s="7" t="n"/>
       <x:c r="K107" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L107" s="7"/>
-      <x:c r="M107" s="7"/>
+      <x:c r="L107" s="7" t="n"/>
+      <x:c r="M107" s="7" t="n"/>
       <x:c r="N107" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Numeric parameter ordering from dataset-specific parameter map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O107" s="7"/>
-      <x:c r="P107" s="7"/>
+      <x:c r="O107" s="7" t="n"/>
+      <x:c r="P107" s="7" t="n"/>
     </x:row>
     <x:row r="108" ht="42" customHeight="1">
       <x:c r="A108" s="7" t="n">
@@ -6588,28 +6566,26 @@
       <x:c r="F108" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G108" s="7"/>
-      <x:c r="H108" s="7"/>
+      <x:c r="G108" s="7" t="n"/>
+      <x:c r="H108" s="7" t="n"/>
       <x:c r="I108" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J108" s="7"/>
-      <x:c r="K108" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collected</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L108" s="7"/>
-      <x:c r="M108" s="7"/>
-      <x:c r="N108" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Analysis parameter category from dataset-specific parameter map.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O108" s="7"/>
-      <x:c r="P108" s="7"/>
+      <x:c r="J108" s="7" t="n"/>
+      <x:c r="K108" s="7" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="L108" s="7" t="n"/>
+      <x:c r="M108" s="7" t="str">
+        <x:v>MT.ADLB_PARCAT1</x:v>
+      </x:c>
+      <x:c r="N108" s="7" t="str">
+        <x:v>Assigned TUMOR MARKER for PSA; otherwise carried from SDTM.LB.LBCAT.</x:v>
+      </x:c>
+      <x:c r="O108" s="7" t="n"/>
+      <x:c r="P108" s="7" t="n"/>
     </x:row>
     <x:row r="109" ht="42" customHeight="1">
       <x:c r="A109" s="7" t="n">
@@ -6638,20 +6614,20 @@
       <x:c r="F109" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G109" s="7"/>
-      <x:c r="H109" s="7"/>
+      <x:c r="G109" s="7" t="n"/>
+      <x:c r="H109" s="7" t="n"/>
       <x:c r="I109" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J109" s="7"/>
+      <x:c r="J109" s="7" t="n"/>
       <x:c r="K109" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L109" s="7"/>
+      <x:c r="L109" s="7" t="n"/>
       <x:c r="M109" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADLB_AVAL</x:t>
@@ -6662,8 +6638,8 @@
           <x:t xml:space="preserve">Numeric lab analysis value from SDTM.LB.LBSTRESN.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O109" s="7"/>
-      <x:c r="P109" s="7"/>
+      <x:c r="O109" s="7" t="n"/>
+      <x:c r="P109" s="7" t="n"/>
     </x:row>
     <x:row r="110" ht="42" customHeight="1">
       <x:c r="A110" s="7" t="n">
@@ -6692,20 +6668,20 @@
       <x:c r="F110" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G110" s="7"/>
-      <x:c r="H110" s="7"/>
+      <x:c r="G110" s="7" t="n"/>
+      <x:c r="H110" s="7" t="n"/>
       <x:c r="I110" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J110" s="7"/>
+      <x:c r="J110" s="7" t="n"/>
       <x:c r="K110" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L110" s="7"/>
+      <x:c r="L110" s="7" t="n"/>
       <x:c r="M110" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADLB_AVALC</x:t>
@@ -6716,8 +6692,8 @@
           <x:t xml:space="preserve">Character lab analysis value from SDTM.LB.LBSTRESC.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O110" s="7"/>
-      <x:c r="P110" s="7"/>
+      <x:c r="O110" s="7" t="n"/>
+      <x:c r="P110" s="7" t="n"/>
     </x:row>
     <x:row r="111" ht="42" customHeight="1">
       <x:c r="A111" s="7" t="n">
@@ -6746,28 +6722,28 @@
       <x:c r="F111" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G111" s="7"/>
-      <x:c r="H111" s="7"/>
+      <x:c r="G111" s="7" t="n"/>
+      <x:c r="H111" s="7" t="n"/>
       <x:c r="I111" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J111" s="7"/>
+      <x:c r="J111" s="7" t="n"/>
       <x:c r="K111" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L111" s="7"/>
-      <x:c r="M111" s="7"/>
+      <x:c r="L111" s="7" t="n"/>
+      <x:c r="M111" s="7" t="n"/>
       <x:c r="N111" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O111" s="7"/>
-      <x:c r="P111" s="7"/>
+      <x:c r="O111" s="7" t="n"/>
+      <x:c r="P111" s="7" t="n"/>
     </x:row>
     <x:row r="112" ht="42" customHeight="1">
       <x:c r="A112" s="7" t="n">
@@ -6796,28 +6772,28 @@
       <x:c r="F112" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G112" s="7"/>
-      <x:c r="H112" s="7"/>
+      <x:c r="G112" s="7" t="n"/>
+      <x:c r="H112" s="7" t="n"/>
       <x:c r="I112" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J112" s="7"/>
+      <x:c r="J112" s="7" t="n"/>
       <x:c r="K112" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L112" s="7"/>
-      <x:c r="M112" s="7"/>
+      <x:c r="L112" s="7" t="n"/>
+      <x:c r="M112" s="7" t="n"/>
       <x:c r="N112" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O112" s="7"/>
-      <x:c r="P112" s="7"/>
+      <x:c r="O112" s="7" t="n"/>
+      <x:c r="P112" s="7" t="n"/>
     </x:row>
     <x:row r="113" ht="42" customHeight="1">
       <x:c r="A113" s="7" t="n">
@@ -6846,28 +6822,28 @@
       <x:c r="F113" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G113" s="7"/>
-      <x:c r="H113" s="7"/>
+      <x:c r="G113" s="7" t="n"/>
+      <x:c r="H113" s="7" t="n"/>
       <x:c r="I113" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J113" s="7"/>
+      <x:c r="J113" s="7" t="n"/>
       <x:c r="K113" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L113" s="7"/>
-      <x:c r="M113" s="7"/>
+      <x:c r="L113" s="7" t="n"/>
+      <x:c r="M113" s="7" t="n"/>
       <x:c r="N113" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O113" s="7"/>
-      <x:c r="P113" s="7"/>
+      <x:c r="O113" s="7" t="n"/>
+      <x:c r="P113" s="7" t="n"/>
     </x:row>
     <x:row r="114" ht="42" customHeight="1">
       <x:c r="A114" s="7" t="n">
@@ -6896,28 +6872,28 @@
       <x:c r="F114" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G114" s="7"/>
-      <x:c r="H114" s="7"/>
+      <x:c r="G114" s="7" t="n"/>
+      <x:c r="H114" s="7" t="n"/>
       <x:c r="I114" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J114" s="7"/>
+      <x:c r="J114" s="7" t="n"/>
       <x:c r="K114" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L114" s="7"/>
-      <x:c r="M114" s="7"/>
+      <x:c r="L114" s="7" t="n"/>
+      <x:c r="M114" s="7" t="n"/>
       <x:c r="N114" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis visit derived from source visit/date and dataset-specific visit window rules.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O114" s="7"/>
-      <x:c r="P114" s="7"/>
+      <x:c r="O114" s="7" t="n"/>
+      <x:c r="P114" s="7" t="n"/>
     </x:row>
     <x:row r="115" ht="42" customHeight="1">
       <x:c r="A115" s="7" t="n">
@@ -6946,28 +6922,28 @@
       <x:c r="F115" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G115" s="7"/>
-      <x:c r="H115" s="7"/>
+      <x:c r="G115" s="7" t="n"/>
+      <x:c r="H115" s="7" t="n"/>
       <x:c r="I115" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J115" s="7"/>
+      <x:c r="J115" s="7" t="n"/>
       <x:c r="K115" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L115" s="7"/>
-      <x:c r="M115" s="7"/>
+      <x:c r="L115" s="7" t="n"/>
+      <x:c r="M115" s="7" t="n"/>
       <x:c r="N115" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Numeric analysis visit derived from AVISIT and dataset-specific visit ordering.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O115" s="7"/>
-      <x:c r="P115" s="7"/>
+      <x:c r="O115" s="7" t="n"/>
+      <x:c r="P115" s="7" t="n"/>
     </x:row>
     <x:row r="116" ht="42" customHeight="1">
       <x:c r="A116" s="7" t="n">
@@ -6996,28 +6972,28 @@
       <x:c r="F116" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G116" s="7"/>
-      <x:c r="H116" s="7"/>
+      <x:c r="G116" s="7" t="n"/>
+      <x:c r="H116" s="7" t="n"/>
       <x:c r="I116" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J116" s="7"/>
+      <x:c r="J116" s="7" t="n"/>
       <x:c r="K116" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L116" s="7"/>
-      <x:c r="M116" s="7"/>
+      <x:c r="L116" s="7" t="n"/>
+      <x:c r="M116" s="7" t="n"/>
       <x:c r="N116" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O116" s="7"/>
-      <x:c r="P116" s="7"/>
+      <x:c r="O116" s="7" t="n"/>
+      <x:c r="P116" s="7" t="n"/>
     </x:row>
     <x:row r="117" ht="42" customHeight="1">
       <x:c r="A117" s="7" t="n">
@@ -7046,32 +7022,26 @@
       <x:c r="F117" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G117" s="7"/>
-      <x:c r="H117" s="7"/>
+      <x:c r="G117" s="7" t="n"/>
+      <x:c r="H117" s="7" t="n"/>
       <x:c r="I117" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J117" s="7"/>
-      <x:c r="K117" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Derived</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L117" s="7"/>
-      <x:c r="M117" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MT.ADLB_ATOXGR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N117" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Analysis toxicity grade derived from SDTM.LB result, normal range, and grading rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O117" s="7"/>
-      <x:c r="P117" s="7"/>
+      <x:c r="J117" s="7" t="n"/>
+      <x:c r="K117" s="7" t="str">
+        <x:v>Predecessor</x:v>
+      </x:c>
+      <x:c r="L117" s="7" t="n"/>
+      <x:c r="M117" s="7" t="str">
+        <x:v>MT.ADLB_ATOXGR</x:v>
+      </x:c>
+      <x:c r="N117" s="7" t="str">
+        <x:v>SDTM.LB.LBTOXGR converted to numeric; no new grading algorithm is applied.</x:v>
+      </x:c>
+      <x:c r="O117" s="7" t="n"/>
+      <x:c r="P117" s="7" t="n"/>
     </x:row>
     <x:row r="118" ht="42" customHeight="1">
       <x:c r="A118" s="7" t="n">
@@ -7100,32 +7070,30 @@
       <x:c r="F118" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G118" s="7"/>
-      <x:c r="H118" s="7"/>
+      <x:c r="G118" s="7" t="n"/>
+      <x:c r="H118" s="7" t="n"/>
       <x:c r="I118" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J118" s="7"/>
+      <x:c r="J118" s="7" t="n"/>
       <x:c r="K118" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L118" s="7"/>
+      <x:c r="L118" s="7" t="n"/>
       <x:c r="M118" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADLB_BASE</x:t>
         </x:is>
       </x:c>
-      <x:c r="N118" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline numeric value selected from pre-treatment ADLB.AVAL records.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O118" s="7"/>
-      <x:c r="P118" s="7"/>
+      <x:c r="N118" s="7" t="str">
+        <x:v>Numeric value from the deterministic SDTM.LB.LBBLFL=Y record selected by date and LBSEQ within subject and parameter.</x:v>
+      </x:c>
+      <x:c r="O118" s="7" t="n"/>
+      <x:c r="P118" s="7" t="n"/>
     </x:row>
     <x:row r="119" ht="42" customHeight="1">
       <x:c r="A119" s="7" t="n">
@@ -7154,32 +7122,30 @@
       <x:c r="F119" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G119" s="7"/>
-      <x:c r="H119" s="7"/>
+      <x:c r="G119" s="7" t="n"/>
+      <x:c r="H119" s="7" t="n"/>
       <x:c r="I119" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J119" s="7"/>
+      <x:c r="J119" s="7" t="n"/>
       <x:c r="K119" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L119" s="7"/>
+      <x:c r="L119" s="7" t="n"/>
       <x:c r="M119" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADLB_BASEC</x:t>
         </x:is>
       </x:c>
-      <x:c r="N119" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline character value selected from pre-treatment ADLB.AVALC records.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O119" s="7"/>
-      <x:c r="P119" s="7"/>
+      <x:c r="N119" s="7" t="str">
+        <x:v>Character value from the same deterministic SDTM.LB.LBBLFL=Y record used for BASE.</x:v>
+      </x:c>
+      <x:c r="O119" s="7" t="n"/>
+      <x:c r="P119" s="7" t="n"/>
     </x:row>
     <x:row r="120" ht="42" customHeight="1">
       <x:c r="A120" s="7" t="n">
@@ -7208,28 +7174,28 @@
       <x:c r="F120" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G120" s="7"/>
-      <x:c r="H120" s="7"/>
+      <x:c r="G120" s="7" t="n"/>
+      <x:c r="H120" s="7" t="n"/>
       <x:c r="I120" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J120" s="7"/>
+      <x:c r="J120" s="7" t="n"/>
       <x:c r="K120" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L120" s="7"/>
-      <x:c r="M120" s="7"/>
+      <x:c r="L120" s="7" t="n"/>
+      <x:c r="M120" s="7" t="n"/>
       <x:c r="N120" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Baseline toxicity grade selected from pre-treatment records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O120" s="7"/>
-      <x:c r="P120" s="7"/>
+      <x:c r="O120" s="7" t="n"/>
+      <x:c r="P120" s="7" t="n"/>
     </x:row>
     <x:row r="121" ht="42" customHeight="1">
       <x:c r="A121" s="7" t="n">
@@ -7258,20 +7224,20 @@
       <x:c r="F121" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G121" s="7"/>
-      <x:c r="H121" s="7"/>
+      <x:c r="G121" s="7" t="n"/>
+      <x:c r="H121" s="7" t="n"/>
       <x:c r="I121" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J121" s="7"/>
+      <x:c r="J121" s="7" t="n"/>
       <x:c r="K121" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L121" s="7"/>
+      <x:c r="L121" s="7" t="n"/>
       <x:c r="M121" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADLB_CHG</x:t>
@@ -7282,8 +7248,8 @@
           <x:t xml:space="preserve">Change from baseline derived as ADLB.AVAL minus ADLB.BASE.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O121" s="7"/>
-      <x:c r="P121" s="7"/>
+      <x:c r="O121" s="7" t="n"/>
+      <x:c r="P121" s="7" t="n"/>
     </x:row>
     <x:row r="122" ht="42" customHeight="1">
       <x:c r="A122" s="7" t="n">
@@ -7312,20 +7278,20 @@
       <x:c r="F122" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G122" s="7"/>
-      <x:c r="H122" s="7"/>
+      <x:c r="G122" s="7" t="n"/>
+      <x:c r="H122" s="7" t="n"/>
       <x:c r="I122" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J122" s="7"/>
+      <x:c r="J122" s="7" t="n"/>
       <x:c r="K122" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L122" s="7"/>
+      <x:c r="L122" s="7" t="n"/>
       <x:c r="M122" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADLB_PCHG</x:t>
@@ -7336,8 +7302,8 @@
           <x:t xml:space="preserve">Percent change from baseline derived as ADLB.CHG divided by ADLB.BASE.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O122" s="7"/>
-      <x:c r="P122" s="7"/>
+      <x:c r="O122" s="7" t="n"/>
+      <x:c r="P122" s="7" t="n"/>
     </x:row>
     <x:row r="123" ht="42" customHeight="1">
       <x:c r="A123" s="7" t="n">
@@ -7366,8 +7332,8 @@
       <x:c r="F123" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G123" s="7"/>
-      <x:c r="H123" s="7"/>
+      <x:c r="G123" s="7" t="n"/>
+      <x:c r="H123" s="7" t="n"/>
       <x:c r="I123" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -7383,15 +7349,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L123" s="7"/>
-      <x:c r="M123" s="7"/>
+      <x:c r="L123" s="7" t="n"/>
+      <x:c r="M123" s="7" t="n"/>
       <x:c r="N123" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis inclusion flag derived from dataset-specific record-selection rules.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O123" s="7"/>
-      <x:c r="P123" s="7"/>
+      <x:c r="O123" s="7" t="n"/>
+      <x:c r="P123" s="7" t="n"/>
     </x:row>
     <x:row r="124" ht="42" customHeight="1">
       <x:c r="A124" s="7" t="n">
@@ -7420,8 +7386,8 @@
       <x:c r="F124" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G124" s="7"/>
-      <x:c r="H124" s="7"/>
+      <x:c r="G124" s="7" t="n"/>
+      <x:c r="H124" s="7" t="n"/>
       <x:c r="I124" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -7437,19 +7403,17 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L124" s="7"/>
+      <x:c r="L124" s="7" t="n"/>
       <x:c r="M124" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADLB_BASEFL</x:t>
         </x:is>
       </x:c>
-      <x:c r="N124" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline flag derived from pre-treatment record-selection rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O124" s="7"/>
-      <x:c r="P124" s="7"/>
+      <x:c r="N124" s="7" t="str">
+        <x:v>Y only on the SDTM.LB record selected as baseline from LBBLFL=Y; N otherwise.</x:v>
+      </x:c>
+      <x:c r="O124" s="7" t="n"/>
+      <x:c r="P124" s="7" t="n"/>
     </x:row>
     <x:row r="125" ht="42" customHeight="1">
       <x:c r="A125" s="7" t="n">
@@ -7478,28 +7442,28 @@
       <x:c r="F125" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G125" s="7"/>
-      <x:c r="H125" s="7"/>
+      <x:c r="G125" s="7" t="n"/>
+      <x:c r="H125" s="7" t="n"/>
       <x:c r="I125" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J125" s="7"/>
+      <x:c r="J125" s="7" t="n"/>
       <x:c r="K125" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L125" s="7"/>
-      <x:c r="M125" s="7"/>
+      <x:c r="L125" s="7" t="n"/>
+      <x:c r="M125" s="7" t="n"/>
       <x:c r="N125" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.LB plus ADSL treatment, baseline, and subject-level attributes.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O125" s="7"/>
-      <x:c r="P125" s="7"/>
+      <x:c r="O125" s="7" t="n"/>
+      <x:c r="P125" s="7" t="n"/>
     </x:row>
     <x:row r="126" ht="42" customHeight="1">
       <x:c r="A126" s="7" t="n">
@@ -7528,20 +7492,20 @@
       <x:c r="F126" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G126" s="7"/>
-      <x:c r="H126" s="7"/>
+      <x:c r="G126" s="7" t="n"/>
+      <x:c r="H126" s="7" t="n"/>
       <x:c r="I126" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J126" s="7"/>
+      <x:c r="J126" s="7" t="n"/>
       <x:c r="K126" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L126" s="7"/>
+      <x:c r="L126" s="7" t="n"/>
       <x:c r="M126" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADLB_ADT</x:t>
@@ -7552,8 +7516,8 @@
           <x:t xml:space="preserve">Analysis date from SDTM.LB.LBDTC.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O126" s="7"/>
-      <x:c r="P126" s="7"/>
+      <x:c r="O126" s="7" t="n"/>
+      <x:c r="P126" s="7" t="n"/>
     </x:row>
     <x:row r="127" ht="42" customHeight="1">
       <x:c r="A127" s="7" t="n">
@@ -7582,28 +7546,28 @@
       <x:c r="F127" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G127" s="7"/>
-      <x:c r="H127" s="7"/>
+      <x:c r="G127" s="7" t="n"/>
+      <x:c r="H127" s="7" t="n"/>
       <x:c r="I127" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J127" s="7"/>
+      <x:c r="J127" s="7" t="n"/>
       <x:c r="K127" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol</x:t>
         </x:is>
       </x:c>
-      <x:c r="L127" s="7"/>
-      <x:c r="M127" s="7"/>
+      <x:c r="L127" s="7" t="n"/>
+      <x:c r="M127" s="7" t="n"/>
       <x:c r="N127" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol identifier from config/study_config.yaml and SDTM study domain records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O127" s="7"/>
-      <x:c r="P127" s="7"/>
+      <x:c r="O127" s="7" t="n"/>
+      <x:c r="P127" s="7" t="n"/>
     </x:row>
     <x:row r="128" ht="42" customHeight="1">
       <x:c r="A128" s="7" t="n">
@@ -7632,28 +7596,28 @@
       <x:c r="F128" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G128" s="7"/>
-      <x:c r="H128" s="7"/>
+      <x:c r="G128" s="7" t="n"/>
+      <x:c r="H128" s="7" t="n"/>
       <x:c r="I128" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J128" s="7"/>
+      <x:c r="J128" s="7" t="n"/>
       <x:c r="K128" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L128" s="7"/>
-      <x:c r="M128" s="7"/>
+      <x:c r="L128" s="7" t="n"/>
+      <x:c r="M128" s="7" t="n"/>
       <x:c r="N128" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.USUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O128" s="7"/>
-      <x:c r="P128" s="7"/>
+      <x:c r="O128" s="7" t="n"/>
+      <x:c r="P128" s="7" t="n"/>
     </x:row>
     <x:row r="129" ht="42" customHeight="1">
       <x:c r="A129" s="7" t="n">
@@ -7682,28 +7646,28 @@
       <x:c r="F129" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G129" s="7"/>
-      <x:c r="H129" s="7"/>
+      <x:c r="G129" s="7" t="n"/>
+      <x:c r="H129" s="7" t="n"/>
       <x:c r="I129" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J129" s="7"/>
+      <x:c r="J129" s="7" t="n"/>
       <x:c r="K129" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L129" s="7"/>
-      <x:c r="M129" s="7"/>
+      <x:c r="L129" s="7" t="n"/>
+      <x:c r="M129" s="7" t="n"/>
       <x:c r="N129" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.SUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O129" s="7"/>
-      <x:c r="P129" s="7"/>
+      <x:c r="O129" s="7" t="n"/>
+      <x:c r="P129" s="7" t="n"/>
     </x:row>
     <x:row r="130" ht="42" customHeight="1">
       <x:c r="A130" s="7" t="n">
@@ -7732,8 +7696,8 @@
       <x:c r="F130" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G130" s="7"/>
-      <x:c r="H130" s="7"/>
+      <x:c r="G130" s="7" t="n"/>
+      <x:c r="H130" s="7" t="n"/>
       <x:c r="I130" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -7749,15 +7713,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L130" s="7"/>
-      <x:c r="M130" s="7"/>
+      <x:c r="L130" s="7" t="n"/>
+      <x:c r="M130" s="7" t="n"/>
       <x:c r="N130" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Randomized/planned treatment assignment from SDTM.DM.ARM and config/study_config.yaml treatment map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O130" s="7"/>
-      <x:c r="P130" s="7"/>
+      <x:c r="O130" s="7" t="n"/>
+      <x:c r="P130" s="7" t="n"/>
     </x:row>
     <x:row r="131" ht="42" customHeight="1">
       <x:c r="A131" s="7" t="n">
@@ -7786,28 +7750,28 @@
       <x:c r="F131" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G131" s="7"/>
-      <x:c r="H131" s="7"/>
+      <x:c r="G131" s="7" t="n"/>
+      <x:c r="H131" s="7" t="n"/>
       <x:c r="I131" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J131" s="7"/>
+      <x:c r="J131" s="7" t="n"/>
       <x:c r="K131" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L131" s="7"/>
-      <x:c r="M131" s="7"/>
+      <x:c r="L131" s="7" t="n"/>
+      <x:c r="M131" s="7" t="n"/>
       <x:c r="N131" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Treatment start date inherited from ADSL.TRTSDT unless defined directly for ADSL.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O131" s="7"/>
-      <x:c r="P131" s="7"/>
+      <x:c r="O131" s="7" t="n"/>
+      <x:c r="P131" s="7" t="n"/>
     </x:row>
     <x:row r="132" ht="42" customHeight="1">
       <x:c r="A132" s="7" t="n">
@@ -7836,8 +7800,8 @@
       <x:c r="F132" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G132" s="7"/>
-      <x:c r="H132" s="7"/>
+      <x:c r="G132" s="7" t="n"/>
+      <x:c r="H132" s="7" t="n"/>
       <x:c r="I132" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -7853,15 +7817,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L132" s="7"/>
-      <x:c r="M132" s="7"/>
+      <x:c r="L132" s="7" t="n"/>
+      <x:c r="M132" s="7" t="n"/>
       <x:c r="N132" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter code from dataset-specific parameter derivation and source test/category.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O132" s="7"/>
-      <x:c r="P132" s="7"/>
+      <x:c r="O132" s="7" t="n"/>
+      <x:c r="P132" s="7" t="n"/>
     </x:row>
     <x:row r="133" ht="42" customHeight="1">
       <x:c r="A133" s="7" t="n">
@@ -7890,28 +7854,28 @@
       <x:c r="F133" s="7" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G133" s="7"/>
-      <x:c r="H133" s="7"/>
+      <x:c r="G133" s="7" t="n"/>
+      <x:c r="H133" s="7" t="n"/>
       <x:c r="I133" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J133" s="7"/>
+      <x:c r="J133" s="7" t="n"/>
       <x:c r="K133" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L133" s="7"/>
-      <x:c r="M133" s="7"/>
+      <x:c r="L133" s="7" t="n"/>
+      <x:c r="M133" s="7" t="n"/>
       <x:c r="N133" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter label from dataset-specific parameter derivation and source test/category.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O133" s="7"/>
-      <x:c r="P133" s="7"/>
+      <x:c r="O133" s="7" t="n"/>
+      <x:c r="P133" s="7" t="n"/>
     </x:row>
     <x:row r="134" ht="42" customHeight="1">
       <x:c r="A134" s="7" t="n">
@@ -7940,32 +7904,30 @@
       <x:c r="F134" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G134" s="7"/>
-      <x:c r="H134" s="7"/>
+      <x:c r="G134" s="7" t="n"/>
+      <x:c r="H134" s="7" t="n"/>
       <x:c r="I134" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J134" s="7"/>
+      <x:c r="J134" s="7" t="n"/>
       <x:c r="K134" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L134" s="7"/>
+      <x:c r="L134" s="7" t="n"/>
       <x:c r="M134" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADRS_AVALC</x:t>
         </x:is>
       </x:c>
-      <x:c r="N134" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Character response result from response source assessments and response derivation rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O134" s="7"/>
-      <x:c r="P134" s="7"/>
+      <x:c r="N134" s="7" t="str">
+        <x:v>Parameter-specific result: lesion-derived RECIST v1.0, confirmed response, reconstructed PSA rule, exploratory bone 2+2 status, or separately typed disposition clinical progression.</x:v>
+      </x:c>
+      <x:c r="O134" s="7" t="n"/>
+      <x:c r="P134" s="7" t="n"/>
     </x:row>
     <x:row r="135" ht="42" customHeight="1">
       <x:c r="A135" s="7" t="n">
@@ -7994,28 +7956,28 @@
       <x:c r="F135" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G135" s="7"/>
-      <x:c r="H135" s="7"/>
+      <x:c r="G135" s="7" t="n"/>
+      <x:c r="H135" s="7" t="n"/>
       <x:c r="I135" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J135" s="7"/>
+      <x:c r="J135" s="7" t="n"/>
       <x:c r="K135" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L135" s="7"/>
-      <x:c r="M135" s="7"/>
+      <x:c r="L135" s="7" t="n"/>
+      <x:c r="M135" s="7" t="n"/>
       <x:c r="N135" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis date derived from the source assessment date.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O135" s="7"/>
-      <x:c r="P135" s="7"/>
+      <x:c r="O135" s="7" t="n"/>
+      <x:c r="P135" s="7" t="n"/>
     </x:row>
     <x:row r="136" ht="42" customHeight="1">
       <x:c r="A136" s="7" t="n">
@@ -8044,28 +8006,28 @@
       <x:c r="F136" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G136" s="7"/>
-      <x:c r="H136" s="7"/>
+      <x:c r="G136" s="7" t="n"/>
+      <x:c r="H136" s="7" t="n"/>
       <x:c r="I136" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J136" s="7"/>
+      <x:c r="J136" s="7" t="n"/>
       <x:c r="K136" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L136" s="7"/>
-      <x:c r="M136" s="7"/>
+      <x:c r="L136" s="7" t="n"/>
+      <x:c r="M136" s="7" t="n"/>
       <x:c r="N136" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis relative day derived from ADT and ADSL.TRTSDT.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O136" s="7"/>
-      <x:c r="P136" s="7"/>
+      <x:c r="O136" s="7" t="n"/>
+      <x:c r="P136" s="7" t="n"/>
     </x:row>
     <x:row r="137" ht="42" customHeight="1">
       <x:c r="A137" s="7" t="n">
@@ -8094,28 +8056,28 @@
       <x:c r="F137" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G137" s="7"/>
-      <x:c r="H137" s="7"/>
+      <x:c r="G137" s="7" t="n"/>
+      <x:c r="H137" s="7" t="n"/>
       <x:c r="I137" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J137" s="7"/>
+      <x:c r="J137" s="7" t="n"/>
       <x:c r="K137" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L137" s="7"/>
-      <x:c r="M137" s="7"/>
+      <x:c r="L137" s="7" t="n"/>
+      <x:c r="M137" s="7" t="n"/>
       <x:c r="N137" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis visit derived from source visit/date and dataset-specific visit window rules.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O137" s="7"/>
-      <x:c r="P137" s="7"/>
+      <x:c r="O137" s="7" t="n"/>
+      <x:c r="P137" s="7" t="n"/>
     </x:row>
     <x:row r="138" ht="42" customHeight="1">
       <x:c r="A138" s="7" t="n">
@@ -8144,8 +8106,8 @@
       <x:c r="F138" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G138" s="7"/>
-      <x:c r="H138" s="7"/>
+      <x:c r="G138" s="7" t="n"/>
+      <x:c r="H138" s="7" t="n"/>
       <x:c r="I138" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
@@ -8161,15 +8123,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L138" s="7"/>
-      <x:c r="M138" s="7"/>
+      <x:c r="L138" s="7" t="n"/>
+      <x:c r="M138" s="7" t="n"/>
       <x:c r="N138" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis inclusion flag derived from dataset-specific record-selection rules.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O138" s="7"/>
-      <x:c r="P138" s="7"/>
+      <x:c r="O138" s="7" t="n"/>
+      <x:c r="P138" s="7" t="n"/>
     </x:row>
     <x:row r="139" ht="42" customHeight="1">
       <x:c r="A139" s="7" t="n">
@@ -8198,20 +8160,20 @@
       <x:c r="F139" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G139" s="7"/>
-      <x:c r="H139" s="7"/>
+      <x:c r="G139" s="7" t="n"/>
+      <x:c r="H139" s="7" t="n"/>
       <x:c r="I139" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J139" s="7"/>
+      <x:c r="J139" s="7" t="n"/>
       <x:c r="K139" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L139" s="7"/>
+      <x:c r="L139" s="7" t="n"/>
       <x:c r="M139" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADRS_AVAL</x:t>
@@ -8222,8 +8184,8 @@
           <x:t xml:space="preserve">Numeric response category from ADRS.AVALC response ordering map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O139" s="7"/>
-      <x:c r="P139" s="7"/>
+      <x:c r="O139" s="7" t="n"/>
+      <x:c r="P139" s="7" t="n"/>
     </x:row>
     <x:row r="140" ht="42" customHeight="1">
       <x:c r="A140" s="7" t="n">
@@ -8252,28 +8214,28 @@
       <x:c r="F140" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G140" s="7"/>
-      <x:c r="H140" s="7"/>
+      <x:c r="G140" s="7" t="n"/>
+      <x:c r="H140" s="7" t="n"/>
       <x:c r="I140" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J140" s="7"/>
+      <x:c r="J140" s="7" t="n"/>
       <x:c r="K140" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol</x:t>
         </x:is>
       </x:c>
-      <x:c r="L140" s="7"/>
-      <x:c r="M140" s="7"/>
+      <x:c r="L140" s="7" t="n"/>
+      <x:c r="M140" s="7" t="n"/>
       <x:c r="N140" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Protocol identifier from config/study_config.yaml and SDTM study domain records.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O140" s="7"/>
-      <x:c r="P140" s="7"/>
+      <x:c r="O140" s="7" t="n"/>
+      <x:c r="P140" s="7" t="n"/>
     </x:row>
     <x:row r="141" ht="42" customHeight="1">
       <x:c r="A141" s="7" t="n">
@@ -8302,28 +8264,28 @@
       <x:c r="F141" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G141" s="7"/>
-      <x:c r="H141" s="7"/>
+      <x:c r="G141" s="7" t="n"/>
+      <x:c r="H141" s="7" t="n"/>
       <x:c r="I141" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J141" s="7"/>
+      <x:c r="J141" s="7" t="n"/>
       <x:c r="K141" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L141" s="7"/>
-      <x:c r="M141" s="7"/>
+      <x:c r="L141" s="7" t="n"/>
+      <x:c r="M141" s="7" t="n"/>
       <x:c r="N141" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.USUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O141" s="7"/>
-      <x:c r="P141" s="7"/>
+      <x:c r="O141" s="7" t="n"/>
+      <x:c r="P141" s="7" t="n"/>
     </x:row>
     <x:row r="142" ht="42" customHeight="1">
       <x:c r="A142" s="7" t="n">
@@ -8352,28 +8314,28 @@
       <x:c r="F142" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G142" s="7"/>
-      <x:c r="H142" s="7"/>
+      <x:c r="G142" s="7" t="n"/>
+      <x:c r="H142" s="7" t="n"/>
       <x:c r="I142" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J142" s="7"/>
+      <x:c r="J142" s="7" t="n"/>
       <x:c r="K142" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L142" s="7"/>
-      <x:c r="M142" s="7"/>
+      <x:c r="L142" s="7" t="n"/>
+      <x:c r="M142" s="7" t="n"/>
       <x:c r="N142" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.SUBJID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O142" s="7"/>
-      <x:c r="P142" s="7"/>
+      <x:c r="O142" s="7" t="n"/>
+      <x:c r="P142" s="7" t="n"/>
     </x:row>
     <x:row r="143" ht="42" customHeight="1">
       <x:c r="A143" s="7" t="n">
@@ -8402,28 +8364,28 @@
       <x:c r="F143" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G143" s="7"/>
-      <x:c r="H143" s="7"/>
+      <x:c r="G143" s="7" t="n"/>
+      <x:c r="H143" s="7" t="n"/>
       <x:c r="I143" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J143" s="7"/>
+      <x:c r="J143" s="7" t="n"/>
       <x:c r="K143" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L143" s="7"/>
-      <x:c r="M143" s="7"/>
+      <x:c r="L143" s="7" t="n"/>
+      <x:c r="M143" s="7" t="n"/>
       <x:c r="N143" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SDTM.DM.SITEID.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O143" s="7"/>
-      <x:c r="P143" s="7"/>
+      <x:c r="O143" s="7" t="n"/>
+      <x:c r="P143" s="7" t="n"/>
     </x:row>
     <x:row r="144" ht="42" customHeight="1">
       <x:c r="A144" s="7" t="n">
@@ -8452,8 +8414,8 @@
       <x:c r="F144" s="7" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G144" s="7"/>
-      <x:c r="H144" s="7"/>
+      <x:c r="G144" s="7" t="n"/>
+      <x:c r="H144" s="7" t="n"/>
       <x:c r="I144" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -8469,15 +8431,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L144" s="7"/>
-      <x:c r="M144" s="7"/>
+      <x:c r="L144" s="7" t="n"/>
+      <x:c r="M144" s="7" t="n"/>
       <x:c r="N144" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Randomized/planned treatment assignment from SDTM.DM.ARM and config/study_config.yaml treatment map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O144" s="7"/>
-      <x:c r="P144" s="7"/>
+      <x:c r="O144" s="7" t="n"/>
+      <x:c r="P144" s="7" t="n"/>
     </x:row>
     <x:row r="145" ht="42" customHeight="1">
       <x:c r="A145" s="7" t="n">
@@ -8506,8 +8468,8 @@
       <x:c r="F145" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G145" s="7"/>
-      <x:c r="H145" s="7"/>
+      <x:c r="G145" s="7" t="n"/>
+      <x:c r="H145" s="7" t="n"/>
       <x:c r="I145" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -8523,15 +8485,15 @@
           <x:t xml:space="preserve">Assigned</x:t>
         </x:is>
       </x:c>
-      <x:c r="L145" s="7"/>
-      <x:c r="M145" s="7"/>
+      <x:c r="L145" s="7" t="n"/>
+      <x:c r="M145" s="7" t="n"/>
       <x:c r="N145" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Numeric planned treatment assignment from config/study_config.yaml treatment map.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O145" s="7"/>
-      <x:c r="P145" s="7"/>
+      <x:c r="O145" s="7" t="n"/>
+      <x:c r="P145" s="7" t="n"/>
     </x:row>
     <x:row r="146" ht="42" customHeight="1">
       <x:c r="A146" s="7" t="n">
@@ -8560,8 +8522,8 @@
       <x:c r="F146" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G146" s="7"/>
-      <x:c r="H146" s="7"/>
+      <x:c r="G146" s="7" t="n"/>
+      <x:c r="H146" s="7" t="n"/>
       <x:c r="I146" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -8577,7 +8539,7 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L146" s="7"/>
+      <x:c r="L146" s="7" t="n"/>
       <x:c r="M146" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADTTE_ITTFL</x:t>
@@ -8588,8 +8550,8 @@
           <x:t xml:space="preserve">Inherited from ADSL.ITTFL.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O146" s="7"/>
-      <x:c r="P146" s="7"/>
+      <x:c r="O146" s="7" t="n"/>
+      <x:c r="P146" s="7" t="n"/>
     </x:row>
     <x:row r="147" ht="42" customHeight="1">
       <x:c r="A147" s="7" t="n">
@@ -8618,8 +8580,8 @@
       <x:c r="F147" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G147" s="7"/>
-      <x:c r="H147" s="7"/>
+      <x:c r="G147" s="7" t="n"/>
+      <x:c r="H147" s="7" t="n"/>
       <x:c r="I147" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -8635,7 +8597,7 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L147" s="7"/>
+      <x:c r="L147" s="7" t="n"/>
       <x:c r="M147" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADTTE_SAFFL</x:t>
@@ -8646,8 +8608,8 @@
           <x:t xml:space="preserve">Inherited from ADSL.SAFFL.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O147" s="7"/>
-      <x:c r="P147" s="7"/>
+      <x:c r="O147" s="7" t="n"/>
+      <x:c r="P147" s="7" t="n"/>
     </x:row>
     <x:row r="148" ht="42" customHeight="1">
       <x:c r="A148" s="7" t="n">
@@ -8676,8 +8638,8 @@
       <x:c r="F148" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G148" s="7"/>
-      <x:c r="H148" s="7"/>
+      <x:c r="G148" s="7" t="n"/>
+      <x:c r="H148" s="7" t="n"/>
       <x:c r="I148" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -8693,15 +8655,15 @@
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L148" s="7"/>
-      <x:c r="M148" s="7"/>
+      <x:c r="L148" s="7" t="n"/>
+      <x:c r="M148" s="7" t="n"/>
       <x:c r="N148" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter code from dataset-specific parameter derivation and source test/category.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O148" s="7"/>
-      <x:c r="P148" s="7"/>
+      <x:c r="O148" s="7" t="n"/>
+      <x:c r="P148" s="7" t="n"/>
     </x:row>
     <x:row r="149" ht="42" customHeight="1">
       <x:c r="A149" s="7" t="n">
@@ -8730,28 +8692,28 @@
       <x:c r="F149" s="7" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G149" s="7"/>
-      <x:c r="H149" s="7"/>
+      <x:c r="G149" s="7" t="n"/>
+      <x:c r="H149" s="7" t="n"/>
       <x:c r="I149" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J149" s="7"/>
+      <x:c r="J149" s="7" t="n"/>
       <x:c r="K149" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Collected</x:t>
         </x:is>
       </x:c>
-      <x:c r="L149" s="7"/>
-      <x:c r="M149" s="7"/>
+      <x:c r="L149" s="7" t="n"/>
+      <x:c r="M149" s="7" t="n"/>
       <x:c r="N149" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Analysis parameter label from dataset-specific parameter derivation and source test/category.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O149" s="7"/>
-      <x:c r="P149" s="7"/>
+      <x:c r="O149" s="7" t="n"/>
+      <x:c r="P149" s="7" t="n"/>
     </x:row>
     <x:row r="150" ht="42" customHeight="1">
       <x:c r="A150" s="7" t="n">
@@ -8780,20 +8742,20 @@
       <x:c r="F150" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G150" s="7"/>
-      <x:c r="H150" s="7"/>
+      <x:c r="G150" s="7" t="n"/>
+      <x:c r="H150" s="7" t="n"/>
       <x:c r="I150" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J150" s="7"/>
+      <x:c r="J150" s="7" t="n"/>
       <x:c r="K150" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L150" s="7"/>
+      <x:c r="L150" s="7" t="n"/>
       <x:c r="M150" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADTTE_PARAMN</x:t>
@@ -8804,8 +8766,8 @@
           <x:t xml:space="preserve">Numeric parameter ordering from ADTTE.PARAMCD.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O150" s="7"/>
-      <x:c r="P150" s="7"/>
+      <x:c r="O150" s="7" t="n"/>
+      <x:c r="P150" s="7" t="n"/>
     </x:row>
     <x:row r="151" ht="42" customHeight="1">
       <x:c r="A151" s="7" t="n">
@@ -8834,20 +8796,20 @@
       <x:c r="F151" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G151" s="7"/>
-      <x:c r="H151" s="7"/>
+      <x:c r="G151" s="7" t="n"/>
+      <x:c r="H151" s="7" t="n"/>
       <x:c r="I151" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J151" s="7"/>
+      <x:c r="J151" s="7" t="n"/>
       <x:c r="K151" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L151" s="7"/>
+      <x:c r="L151" s="7" t="n"/>
       <x:c r="M151" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADTTE_PARCAT1</x:t>
@@ -8858,8 +8820,8 @@
           <x:t xml:space="preserve">Time-to-event category from ADTTE.PARAMCD.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O151" s="7"/>
-      <x:c r="P151" s="7"/>
+      <x:c r="O151" s="7" t="n"/>
+      <x:c r="P151" s="7" t="n"/>
     </x:row>
     <x:row r="152" ht="42" customHeight="1">
       <x:c r="A152" s="7" t="n">
@@ -8888,28 +8850,26 @@
       <x:c r="F152" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G152" s="7"/>
-      <x:c r="H152" s="7"/>
+      <x:c r="G152" s="7" t="n"/>
+      <x:c r="H152" s="7" t="n"/>
       <x:c r="I152" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J152" s="7"/>
-      <x:c r="K152" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collected</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L152" s="7"/>
-      <x:c r="M152" s="7"/>
-      <x:c r="N152" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ADSL subject-level attributes plus SDTM.DS, SDTM.RS/LS, SDTM.AE, and death/progression source dates by PARAMCD.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O152" s="7"/>
-      <x:c r="P152" s="7"/>
+      <x:c r="J152" s="7" t="n"/>
+      <x:c r="K152" s="7" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="L152" s="7" t="n"/>
+      <x:c r="M152" s="7" t="str">
+        <x:v>MT.ADTTE_ADT</x:v>
+      </x:c>
+      <x:c r="N152" s="7" t="str">
+        <x:v>RANDDT for OS, PFS, TTPSA, TTUMOR, and TTPAIN; TRTSDT for TTSAE.</x:v>
+      </x:c>
+      <x:c r="O152" s="7" t="n"/>
+      <x:c r="P152" s="7" t="n"/>
     </x:row>
     <x:row r="153" ht="42" customHeight="1">
       <x:c r="A153" s="7" t="n">
@@ -8938,28 +8898,26 @@
       <x:c r="F153" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G153" s="7"/>
-      <x:c r="H153" s="7"/>
+      <x:c r="G153" s="7" t="n"/>
+      <x:c r="H153" s="7" t="n"/>
       <x:c r="I153" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J153" s="7"/>
-      <x:c r="K153" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collected</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L153" s="7"/>
-      <x:c r="M153" s="7"/>
-      <x:c r="N153" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Analysis date derived from the source assessment date.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O153" s="7"/>
-      <x:c r="P153" s="7"/>
+      <x:c r="J153" s="7" t="n"/>
+      <x:c r="K153" s="7" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="L153" s="7" t="n"/>
+      <x:c r="M153" s="7" t="str">
+        <x:v>MT.ADTTE_ADT</x:v>
+      </x:c>
+      <x:c r="N153" s="7" t="str">
+        <x:v>Parameter-specific eligible event date or censoring date, not earlier than its time origin and bounded by the analysis cutoff.</x:v>
+      </x:c>
+      <x:c r="O153" s="7" t="n"/>
+      <x:c r="P153" s="7" t="n"/>
     </x:row>
     <x:row r="154" ht="42" customHeight="1">
       <x:c r="A154" s="7" t="n">
@@ -8988,8 +8946,8 @@
       <x:c r="F154" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G154" s="7"/>
-      <x:c r="H154" s="7"/>
+      <x:c r="G154" s="7" t="n"/>
+      <x:c r="H154" s="7" t="n"/>
       <x:c r="I154" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
@@ -9005,7 +8963,7 @@
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L154" s="7"/>
+      <x:c r="L154" s="7" t="n"/>
       <x:c r="M154" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.CNSR_TTE</x:t>
@@ -9016,8 +8974,8 @@
           <x:t xml:space="preserve">Censoring indicator derived from event/censor source dates by ADTTE.PARAMCD.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O154" s="7"/>
-      <x:c r="P154" s="7"/>
+      <x:c r="O154" s="7" t="n"/>
+      <x:c r="P154" s="7" t="n"/>
     </x:row>
     <x:row r="155" ht="42" customHeight="1">
       <x:c r="A155" s="7" t="n">
@@ -9046,28 +9004,26 @@
       <x:c r="F155" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G155" s="7"/>
-      <x:c r="H155" s="7"/>
+      <x:c r="G155" s="7" t="n"/>
+      <x:c r="H155" s="7" t="n"/>
       <x:c r="I155" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J155" s="7"/>
-      <x:c r="K155" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collected</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L155" s="7"/>
-      <x:c r="M155" s="7"/>
-      <x:c r="N155" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ADSL subject-level attributes plus SDTM.DS, SDTM.RS/LS, SDTM.AE, and death/progression source dates by PARAMCD.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O155" s="7"/>
-      <x:c r="P155" s="7"/>
+      <x:c r="J155" s="7" t="n"/>
+      <x:c r="K155" s="7" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="L155" s="7" t="n"/>
+      <x:c r="M155" s="7" t="str">
+        <x:v>MT.ADTTE_ADT</x:v>
+      </x:c>
+      <x:c r="N155" s="7" t="str">
+        <x:v>Assigned from the eligible parameter-specific event component when CNSR=0.</x:v>
+      </x:c>
+      <x:c r="O155" s="7" t="n"/>
+      <x:c r="P155" s="7" t="n"/>
     </x:row>
     <x:row r="156" ht="42" customHeight="1">
       <x:c r="A156" s="7" t="n">
@@ -9096,28 +9052,26 @@
       <x:c r="F156" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G156" s="7"/>
-      <x:c r="H156" s="7"/>
+      <x:c r="G156" s="7" t="n"/>
+      <x:c r="H156" s="7" t="n"/>
       <x:c r="I156" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J156" s="7"/>
-      <x:c r="K156" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Collected</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L156" s="7"/>
-      <x:c r="M156" s="7"/>
-      <x:c r="N156" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ADSL subject-level attributes plus SDTM.DS, SDTM.RS/LS, SDTM.AE, and death/progression source dates by PARAMCD.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O156" s="7"/>
-      <x:c r="P156" s="7"/>
+      <x:c r="J156" s="7" t="n"/>
+      <x:c r="K156" s="7" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="L156" s="7" t="n"/>
+      <x:c r="M156" s="7" t="str">
+        <x:v>MT.ADTTE_ADT</x:v>
+      </x:c>
+      <x:c r="N156" s="7" t="str">
+        <x:v>Assigned from the parameter-specific censoring rule when CNSR=1.</x:v>
+      </x:c>
+      <x:c r="O156" s="7" t="n"/>
+      <x:c r="P156" s="7" t="n"/>
     </x:row>
     <x:row r="157" ht="42" customHeight="1">
       <x:c r="A157" s="7" t="n">
@@ -9146,20 +9100,20 @@
       <x:c r="F157" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G157" s="7"/>
-      <x:c r="H157" s="7"/>
+      <x:c r="G157" s="7" t="n"/>
+      <x:c r="H157" s="7" t="n"/>
       <x:c r="I157" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes</x:t>
         </x:is>
       </x:c>
-      <x:c r="J157" s="7"/>
+      <x:c r="J157" s="7" t="n"/>
       <x:c r="K157" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L157" s="7"/>
+      <x:c r="L157" s="7" t="n"/>
       <x:c r="M157" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.AVAL_TTE</x:t>
@@ -9170,8 +9124,8 @@
           <x:t xml:space="preserve">Time-to-event duration derived from ADTTE.STARTDT, ADTTE.ADT, and ADTTE.AVALU.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O157" s="7"/>
-      <x:c r="P157" s="7"/>
+      <x:c r="O157" s="7" t="n"/>
+      <x:c r="P157" s="7" t="n"/>
     </x:row>
     <x:row r="158" ht="42" customHeight="1">
       <x:c r="A158" s="7" t="n">
@@ -9200,20 +9154,20 @@
       <x:c r="F158" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G158" s="7"/>
-      <x:c r="H158" s="7"/>
+      <x:c r="G158" s="7" t="n"/>
+      <x:c r="H158" s="7" t="n"/>
       <x:c r="I158" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J158" s="7"/>
+      <x:c r="J158" s="7" t="n"/>
       <x:c r="K158" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L158" s="7"/>
+      <x:c r="L158" s="7" t="n"/>
       <x:c r="M158" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADTTE_AVALU</x:t>
@@ -9224,8 +9178,8 @@
           <x:t xml:space="preserve">Time-to-event unit assigned by ADTTE parameter derivation.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O158" s="7"/>
-      <x:c r="P158" s="7"/>
+      <x:c r="O158" s="7" t="n"/>
+      <x:c r="P158" s="7" t="n"/>
     </x:row>
     <x:row r="159" ht="42" customHeight="1">
       <x:c r="A159" s="7" t="n">
@@ -9254,20 +9208,20 @@
       <x:c r="F159" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G159" s="7"/>
-      <x:c r="H159" s="7"/>
+      <x:c r="G159" s="7" t="n"/>
+      <x:c r="H159" s="7" t="n"/>
       <x:c r="I159" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J159" s="7"/>
+      <x:c r="J159" s="7" t="n"/>
       <x:c r="K159" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L159" s="7"/>
+      <x:c r="L159" s="7" t="n"/>
       <x:c r="M159" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADEX_PARAMN</x:t>
@@ -9278,8 +9232,8 @@
           <x:t xml:space="preserve">Numeric parameter ordering from ADEX.PARAMCD.</x:t>
         </x:is>
       </x:c>
-      <x:c r="O159" s="7"/>
-      <x:c r="P159" s="7"/>
+      <x:c r="O159" s="7" t="n"/>
+      <x:c r="P159" s="7" t="n"/>
     </x:row>
     <x:row r="160" ht="42" customHeight="1">
       <x:c r="A160" s="8" t="n">
@@ -9308,32 +9262,106 @@
       <x:c r="F160" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G160" s="8"/>
-      <x:c r="H160" s="8"/>
+      <x:c r="G160" s="8" t="n"/>
+      <x:c r="H160" s="8" t="n"/>
       <x:c r="I160" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="J160" s="8"/>
+      <x:c r="J160" s="8" t="n"/>
       <x:c r="K160" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="L160" s="8"/>
+      <x:c r="L160" s="8" t="n"/>
       <x:c r="M160" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MT.ADEX_AVISITN</x:t>
         </x:is>
       </x:c>
-      <x:c r="N160" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Numeric analysis visit derived from ADEX.AVISIT and SDTM.EX sequence/date.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="O160" s="8"/>
-      <x:c r="P160" s="8"/>
+      <x:c r="N160" s="8" t="str">
+        <x:v>Cycle number from SDTM.EX.VISITNUM; ALL CYCLES summary records are assigned 0.</x:v>
+      </x:c>
+      <x:c r="O160" s="8" t="n"/>
+      <x:c r="P160" s="8" t="n"/>
+    </x:row>
+    <x:row r="161" ht="15" hidden="0" customHeight="1">
+      <x:c r="A161" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>ADCM</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>CMSEQ</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
+        <x:v>Concomitant Medication Sequence Number</x:v>
+      </x:c>
+      <x:c r="E161" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="F161" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G161"/>
+      <x:c r="H161"/>
+      <x:c r="I161" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="J161"/>
+      <x:c r="K161" t="str">
+        <x:v>Predecessor</x:v>
+      </x:c>
+      <x:c r="L161"/>
+      <x:c r="M161"/>
+      <x:c r="N161" t="str">
+        <x:v>SDTM.CM.CMSEQ.</x:v>
+      </x:c>
+      <x:c r="O161"/>
+      <x:c r="P161" t="str">
+        <x:v>Unique within subject in the source CM domain.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="15" hidden="0" customHeight="1">
+      <x:c r="A162" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>ADLB</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>LBSEQ</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
+        <x:v>Laboratory Test Sequence Number</x:v>
+      </x:c>
+      <x:c r="E162" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="F162" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G162"/>
+      <x:c r="H162"/>
+      <x:c r="I162" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="J162"/>
+      <x:c r="K162" t="str">
+        <x:v>Predecessor</x:v>
+      </x:c>
+      <x:c r="L162"/>
+      <x:c r="M162"/>
+      <x:c r="N162" t="str">
+        <x:v>SDTM.LB.LBSEQ; blank on derived Optimus parameter rows.</x:v>
+      </x:c>
+      <x:c r="O162"/>
+      <x:c r="P162" t="str">
+        <x:v>Source identifier for laboratory records; derived Optimus rows are keyed by parameter and visit.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9344,22 +9372,22 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="10" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="50" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="38" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8" customWidth="1"/>
+    <x:col min="2" max="2" width="10" customWidth="1"/>
+    <x:col min="3" max="3" width="16" customWidth="1"/>
+    <x:col min="4" max="4" width="34" customWidth="1"/>
+    <x:col min="5" max="5" width="34" customWidth="1"/>
+    <x:col min="6" max="6" width="12" customWidth="1"/>
+    <x:col min="7" max="7" width="9" customWidth="1"/>
+    <x:col min="8" max="8" width="13" customWidth="1"/>
+    <x:col min="9" max="9" width="12" customWidth="1"/>
+    <x:col min="10" max="10" width="12" customWidth="1"/>
+    <x:col min="11" max="11" width="16" customWidth="1"/>
+    <x:col min="12" max="12" width="14" customWidth="1"/>
+    <x:col min="13" max="13" width="10" customWidth="1"/>
+    <x:col min="14" max="14" width="20" customWidth="1"/>
+    <x:col min="15" max="15" width="50" customWidth="1"/>
+    <x:col min="16" max="16" width="38" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -9476,23 +9504,27 @@
       <x:c r="G2" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7"/>
+      <x:c r="H2" s="7" t="n"/>
+      <x:c r="I2" s="7" t="n"/>
       <x:c r="J2" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="K2" s="7"/>
+      <x:c r="K2" s="7" t="n"/>
       <x:c r="L2" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="M2" s="7"/>
-      <x:c r="N2" s="7"/>
-      <x:c r="O2" s="7"/>
-      <x:c r="P2" s="7"/>
+      <x:c r="M2" s="7" t="n"/>
+      <x:c r="N2" s="7" t="str">
+        <x:v>MT.ADLB_AVAL</x:v>
+      </x:c>
+      <x:c r="O2" s="7" t="str">
+        <x:v>SDTM.LB.LBSTRESN</x:v>
+      </x:c>
+      <x:c r="P2" s="7" t="n"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="7" t="n">
@@ -9526,23 +9558,27 @@
       <x:c r="G3" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H3" s="7"/>
-      <x:c r="I3" s="7"/>
+      <x:c r="H3" s="7" t="n"/>
+      <x:c r="I3" s="7" t="n"/>
       <x:c r="J3" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="K3" s="7"/>
+      <x:c r="K3" s="7" t="n"/>
       <x:c r="L3" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="M3" s="7"/>
-      <x:c r="N3" s="7"/>
-      <x:c r="O3" s="7"/>
-      <x:c r="P3" s="7"/>
+      <x:c r="M3" s="7" t="n"/>
+      <x:c r="N3" s="7" t="str">
+        <x:v>MT.ANCNADIR</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="str">
+        <x:v>ADLB.AVAL where PARAMCD=NEUT</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="n"/>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="7" t="n">
@@ -9576,23 +9612,27 @@
       <x:c r="G4" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H4" s="7"/>
-      <x:c r="I4" s="7"/>
+      <x:c r="H4" s="7" t="n"/>
+      <x:c r="I4" s="7" t="n"/>
       <x:c r="J4" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="K4" s="7"/>
+      <x:c r="K4" s="7" t="n"/>
       <x:c r="L4" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="M4" s="7"/>
-      <x:c r="N4" s="7"/>
-      <x:c r="O4" s="7"/>
-      <x:c r="P4" s="7"/>
+      <x:c r="M4" s="7" t="n"/>
+      <x:c r="N4" s="7" t="str">
+        <x:v>MT.ADLB_AVAL</x:v>
+      </x:c>
+      <x:c r="O4" s="7" t="str">
+        <x:v>SDTM.LB.LBSTRESN</x:v>
+      </x:c>
+      <x:c r="P4" s="7" t="n"/>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="7" t="n">
@@ -9613,10 +9653,8 @@
           <x:t xml:space="preserve">WC.ADEX.PARAMCD.EQ.RDI</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Relative Dose Intensity (%)</x:t>
-        </x:is>
+      <x:c r="E5" s="7" t="str">
+        <x:v>Source Relative Dose Intensity (%)</x:v>
       </x:c>
       <x:c r="F5" s="7" t="inlineStr">
         <x:is>
@@ -9626,23 +9664,25 @@
       <x:c r="G5" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H5" s="7"/>
-      <x:c r="I5" s="7"/>
+      <x:c r="H5" s="7" t="n"/>
+      <x:c r="I5" s="7" t="n"/>
       <x:c r="J5" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="K5" s="7"/>
-      <x:c r="L5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Derived</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M5" s="7"/>
-      <x:c r="N5" s="7"/>
-      <x:c r="O5" s="7"/>
-      <x:c r="P5" s="7"/>
+      <x:c r="K5" s="7" t="n"/>
+      <x:c r="L5" s="7" t="str">
+        <x:v>Predecessor</x:v>
+      </x:c>
+      <x:c r="M5" s="7" t="n"/>
+      <x:c r="N5" s="7" t="str">
+        <x:v>MT.RDI</x:v>
+      </x:c>
+      <x:c r="O5" s="7" t="str">
+        <x:v>SDTM.EX.EXTRINT</x:v>
+      </x:c>
+      <x:c r="P5" s="7" t="n"/>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -9676,23 +9716,27 @@
       <x:c r="G6" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H6" s="7"/>
-      <x:c r="I6" s="7"/>
+      <x:c r="H6" s="7" t="n"/>
+      <x:c r="I6" s="7" t="n"/>
       <x:c r="J6" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="K6" s="7"/>
+      <x:c r="K6" s="7" t="n"/>
       <x:c r="L6" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="M6" s="7"/>
-      <x:c r="N6" s="7"/>
-      <x:c r="O6" s="7"/>
-      <x:c r="P6" s="7"/>
+      <x:c r="M6" s="7" t="n"/>
+      <x:c r="N6" s="7" t="str">
+        <x:v>MT.NCYCLE</x:v>
+      </x:c>
+      <x:c r="O6" s="7" t="str">
+        <x:v>SDTM.EX.EXDOSE2 and VISITNUM</x:v>
+      </x:c>
+      <x:c r="P6" s="7" t="n"/>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="7" t="n">
@@ -9726,23 +9770,25 @@
       <x:c r="G7" s="7" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="7"/>
-      <x:c r="I7" s="7"/>
+      <x:c r="H7" s="7" t="n"/>
+      <x:c r="I7" s="7" t="n"/>
       <x:c r="J7" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="K7" s="7"/>
+      <x:c r="K7" s="7" t="n"/>
       <x:c r="L7" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="M7" s="7"/>
-      <x:c r="N7" s="7"/>
-      <x:c r="O7" s="7"/>
-      <x:c r="P7" s="7"/>
+      <x:c r="M7" s="7" t="n"/>
+      <x:c r="N7" s="7" t="str">
+        <x:v>MT.AVAL_TTE</x:v>
+      </x:c>
+      <x:c r="O7" s="7" t="n"/>
+      <x:c r="P7" s="7" t="n"/>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="8" t="n">
@@ -9776,23 +9822,185 @@
       <x:c r="G8" s="8" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H8" s="8"/>
-      <x:c r="I8" s="8"/>
+      <x:c r="H8" s="8" t="n"/>
+      <x:c r="I8" s="8" t="n"/>
       <x:c r="J8" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">No</x:t>
         </x:is>
       </x:c>
-      <x:c r="K8" s="8"/>
+      <x:c r="K8" s="8" t="n"/>
       <x:c r="L8" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Derived</x:t>
         </x:is>
       </x:c>
-      <x:c r="M8" s="8"/>
-      <x:c r="N8" s="8"/>
-      <x:c r="O8" s="8"/>
-      <x:c r="P8" s="8"/>
+      <x:c r="M8" s="8" t="n"/>
+      <x:c r="N8" s="8" t="str">
+        <x:v>MT.AVAL_TTE</x:v>
+      </x:c>
+      <x:c r="O8" s="8" t="n"/>
+      <x:c r="P8" s="8" t="n"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>ADTTE</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>AVAL</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>WC.ADTTE.PARAMCD.EQ.TTPSA</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>Time to PSA Progression (Days)</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="K9"/>
+      <x:c r="L9" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="M9"/>
+      <x:c r="N9" t="str">
+        <x:v>MT.AVAL_TTE</x:v>
+      </x:c>
+      <x:c r="O9"/>
+      <x:c r="P9" t="str">
+        <x:v>Reconstructed PSA progression rule.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>ADTTE</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>AVAL</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>WC.ADTTE.PARAMCD.EQ.TTUMOR</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>Time to RECIST Tumor Progression (Days)</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="M10"/>
+      <x:c r="N10" t="str">
+        <x:v>MT.AVAL_TTE</x:v>
+      </x:c>
+      <x:c r="O10"/>
+      <x:c r="P10" t="str">
+        <x:v>Lesion-derived RECIST v1.0 progression only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>ADTTE</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>AVAL</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>WC.ADTTE.PARAMCD.EQ.TTPAIN</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Time to Pain Progression (Days)</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="M11"/>
+      <x:c r="N11" t="str">
+        <x:v>MT.AVAL_TTE</x:v>
+      </x:c>
+      <x:c r="O11"/>
+      <x:c r="P11" t="str">
+        <x:v>Author-adopted F-042 Phase 2 pain rule.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>ADTTE</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>AVAL</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>WC.ADTTE.PARAMCD.EQ.TTSAE</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Time to First TE Serious AE (Days)</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="G12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="K12"/>
+      <x:c r="L12" t="str">
+        <x:v>Derived</x:v>
+      </x:c>
+      <x:c r="M12"/>
+      <x:c r="N12" t="str">
+        <x:v>MT.AVAL_TTE</x:v>
+      </x:c>
+      <x:c r="O12"/>
+      <x:c r="P12" t="str">
+        <x:v>Safety follow-up ends at the earliest of last known alive, 30 days after last dose, and the analysis cutoff.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9803,11 +10011,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="40" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="40" customWidth="1"/>
+    <x:col min="2" max="2" width="12" customWidth="1"/>
+    <x:col min="3" max="3" width="18" customWidth="1"/>
+    <x:col min="4" max="4" width="14" customWidth="1"/>
+    <x:col min="5" max="5" width="20" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -10108,71 +10316,128 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="7" t="str">
-        <x:v>WC.ADTTE.PARAMCD.EQ.TTPAIN</x:v>
-      </x:c>
-      <x:c r="B12" s="7" t="str">
+      <x:c r="A12" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WC.ADTTE.PARAMCD.EQ.TTPAIN</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADTTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PARAMCD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EQ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TTPAIN</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WC.ADRS.PARAMCD.EQ.PSARESP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PARAMCD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EQ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PSARESP</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="28" customHeight="1">
+      <x:c r="A14" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WC.ADRS.PARAMCD.EQ.OBJRESP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PARAMCD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EQ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">OBJRESP</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WC.ADEX.PARAMCD.EQ.RDIDL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADEX</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PARAMCD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EQ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RDIDL</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>WC.ADTTE.PARAMCD.EQ.TTSAE</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
         <x:v>ADTTE</x:v>
       </x:c>
-      <x:c r="C12" s="7" t="str">
+      <x:c r="C16" t="str">
         <x:v>PARAMCD</x:v>
       </x:c>
-      <x:c r="D12" s="7" t="str">
+      <x:c r="D16" t="str">
         <x:v>EQ</x:v>
       </x:c>
-      <x:c r="E12" s="7" t="str">
-        <x:v>TTPAIN</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="7" t="str">
-        <x:v>WC.ADRS.PARAMCD.EQ.PSARESP</x:v>
-      </x:c>
-      <x:c r="B13" s="7" t="str">
-        <x:v>ADRS</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="str">
-        <x:v>PARAMCD</x:v>
-      </x:c>
-      <x:c r="D13" s="7" t="str">
-        <x:v>EQ</x:v>
-      </x:c>
-      <x:c r="E13" s="7" t="str">
-        <x:v>PSARESP</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="7" t="str">
-        <x:v>WC.ADRS.PARAMCD.EQ.OBJRESP</x:v>
-      </x:c>
-      <x:c r="B14" s="7" t="str">
-        <x:v>ADRS</x:v>
-      </x:c>
-      <x:c r="C14" s="7" t="str">
-        <x:v>PARAMCD</x:v>
-      </x:c>
-      <x:c r="D14" s="7" t="str">
-        <x:v>EQ</x:v>
-      </x:c>
-      <x:c r="E14" s="7" t="str">
-        <x:v>OBJRESP</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="8" t="str">
-        <x:v>WC.ADEX.PARAMCD.EQ.RDIDL</x:v>
-      </x:c>
-      <x:c r="B15" s="8" t="str">
-        <x:v>ADEX</x:v>
-      </x:c>
-      <x:c r="C15" s="8" t="str">
-        <x:v>PARAMCD</x:v>
-      </x:c>
-      <x:c r="D15" s="8" t="str">
-        <x:v>EQ</x:v>
-      </x:c>
-      <x:c r="E15" s="8" t="str">
-        <x:v>RDIDL</x:v>
+      <x:c r="E16" t="str">
+        <x:v>TTSAE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10184,14 +10449,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="48" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" customWidth="1"/>
+    <x:col min="2" max="2" width="32" customWidth="1"/>
+    <x:col min="3" max="3" width="16" customWidth="1"/>
+    <x:col min="4" max="4" width="12" customWidth="1"/>
+    <x:col min="5" max="5" width="10" customWidth="1"/>
+    <x:col min="6" max="6" width="20" customWidth="1"/>
+    <x:col min="7" max="7" width="16" customWidth="1"/>
+    <x:col min="8" max="8" width="48" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -10407,7 +10672,7 @@
           <x:t xml:space="preserve">Treatment Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="7"/>
+      <x:c r="C6" s="7" t="n"/>
       <x:c r="D6" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10421,7 +10686,7 @@
           <x:t xml:space="preserve">CbzP</x:t>
         </x:is>
       </x:c>
-      <x:c r="G6" s="7"/>
+      <x:c r="G6" s="7" t="n"/>
       <x:c r="H6" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cabazitaxel + Prednisone</x:t>
@@ -10439,7 +10704,7 @@
           <x:t xml:space="preserve">Treatment Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="7"/>
+      <x:c r="C7" s="7" t="n"/>
       <x:c r="D7" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10453,7 +10718,7 @@
           <x:t xml:space="preserve">MP</x:t>
         </x:is>
       </x:c>
-      <x:c r="G7" s="7"/>
+      <x:c r="G7" s="7" t="n"/>
       <x:c r="H7" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mitoxantrone + Prednisone</x:t>
@@ -10471,7 +10736,7 @@
           <x:t xml:space="preserve">Treatment Numeric Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="7"/>
+      <x:c r="C8" s="7" t="n"/>
       <x:c r="D8" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">integer</x:t>
@@ -10485,7 +10750,7 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="G8" s="7"/>
+      <x:c r="G8" s="7" t="n"/>
       <x:c r="H8" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cabazitaxel + Prednisone</x:t>
@@ -10503,7 +10768,7 @@
           <x:t xml:space="preserve">Treatment Numeric Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C9" s="7"/>
+      <x:c r="C9" s="7" t="n"/>
       <x:c r="D9" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">integer</x:t>
@@ -10517,7 +10782,7 @@
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
-      <x:c r="G9" s="7"/>
+      <x:c r="G9" s="7" t="n"/>
       <x:c r="H9" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mitoxantrone + Prednisone</x:t>
@@ -10535,7 +10800,7 @@
           <x:t xml:space="preserve">Age Group Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="7"/>
+      <x:c r="C10" s="7" t="n"/>
       <x:c r="D10" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10549,7 +10814,7 @@
           <x:t xml:space="preserve">&lt;65</x:t>
         </x:is>
       </x:c>
-      <x:c r="G10" s="7"/>
+      <x:c r="G10" s="7" t="n"/>
       <x:c r="H10" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">&lt;65 Years</x:t>
@@ -10567,7 +10832,7 @@
           <x:t xml:space="preserve">Age Group Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="7"/>
+      <x:c r="C11" s="7" t="n"/>
       <x:c r="D11" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10581,7 +10846,7 @@
           <x:t xml:space="preserve">&gt;=65</x:t>
         </x:is>
       </x:c>
-      <x:c r="G11" s="7"/>
+      <x:c r="G11" s="7" t="n"/>
       <x:c r="H11" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">&gt;=65 Years</x:t>
@@ -10599,7 +10864,7 @@
           <x:t xml:space="preserve">Censoring Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="7"/>
+      <x:c r="C12" s="7" t="n"/>
       <x:c r="D12" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">integer</x:t>
@@ -10613,7 +10878,7 @@
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
-      <x:c r="G12" s="7"/>
+      <x:c r="G12" s="7" t="n"/>
       <x:c r="H12" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Event</x:t>
@@ -10631,7 +10896,7 @@
           <x:t xml:space="preserve">Censoring Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" s="7"/>
+      <x:c r="C13" s="7" t="n"/>
       <x:c r="D13" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">integer</x:t>
@@ -10645,7 +10910,7 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="G13" s="7"/>
+      <x:c r="G13" s="7" t="n"/>
       <x:c r="H13" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Censored</x:t>
@@ -10663,7 +10928,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" s="7"/>
+      <x:c r="C14" s="7" t="n"/>
       <x:c r="D14" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10677,7 +10942,7 @@
           <x:t xml:space="preserve">NREDDOSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G14" s="7"/>
+      <x:c r="G14" s="7" t="n"/>
       <x:c r="H14" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Number of Dose Reductions</x:t>
@@ -10695,7 +10960,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C15" s="7"/>
+      <x:c r="C15" s="7" t="n"/>
       <x:c r="D15" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10709,11 +10974,9 @@
           <x:t xml:space="preserve">RDI</x:t>
         </x:is>
       </x:c>
-      <x:c r="G15" s="7"/>
-      <x:c r="H15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Relative Dose Intensity (%)</x:t>
-        </x:is>
+      <x:c r="G15" s="7" t="n"/>
+      <x:c r="H15" s="7" t="str">
+        <x:v>Source Relative Dose Intensity (%)</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
@@ -10727,7 +10990,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C16" s="7"/>
+      <x:c r="C16" s="7" t="n"/>
       <x:c r="D16" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10741,7 +11004,7 @@
           <x:t xml:space="preserve">RDIDL</x:t>
         </x:is>
       </x:c>
-      <x:c r="G16" s="7"/>
+      <x:c r="G16" s="7" t="n"/>
       <x:c r="H16" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Relative Dose Intensity Category</x:t>
@@ -10759,7 +11022,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C17" s="7"/>
+      <x:c r="C17" s="7" t="n"/>
       <x:c r="D17" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10773,11 +11036,9 @@
           <x:t xml:space="preserve">PERFDOSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G17" s="7"/>
-      <x:c r="H17" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Actual Dose Administered (mg/m2)</x:t>
-        </x:is>
+      <x:c r="G17" s="7" t="n"/>
+      <x:c r="H17" s="7" t="str">
+        <x:v>IV Actual Dose Administered (mg/m2)</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
@@ -10791,7 +11052,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" s="7"/>
+      <x:c r="C18" s="7" t="n"/>
       <x:c r="D18" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10805,7 +11066,7 @@
           <x:t xml:space="preserve">ADJ</x:t>
         </x:is>
       </x:c>
-      <x:c r="G18" s="7"/>
+      <x:c r="G18" s="7" t="n"/>
       <x:c r="H18" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Dose Adjusted Flag</x:t>
@@ -10823,7 +11084,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C19" s="7"/>
+      <x:c r="C19" s="7" t="n"/>
       <x:c r="D19" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10837,7 +11098,7 @@
           <x:t xml:space="preserve">ADJAE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G19" s="7"/>
+      <x:c r="G19" s="7" t="n"/>
       <x:c r="H19" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Dose Adjusted due to AE Flag</x:t>
@@ -10855,7 +11116,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C20" s="7"/>
+      <x:c r="C20" s="7" t="n"/>
       <x:c r="D20" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10869,7 +11130,7 @@
           <x:t xml:space="preserve">ANCNADIR</x:t>
         </x:is>
       </x:c>
-      <x:c r="G20" s="7"/>
+      <x:c r="G20" s="7" t="n"/>
       <x:c r="H20" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Minimum post-baseline ANC value per cycle</x:t>
@@ -10887,7 +11148,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C21" s="7"/>
+      <x:c r="C21" s="7" t="n"/>
       <x:c r="D21" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10901,7 +11162,7 @@
           <x:t xml:space="preserve">ANCRECDY</x:t>
         </x:is>
       </x:c>
-      <x:c r="G21" s="7"/>
+      <x:c r="G21" s="7" t="n"/>
       <x:c r="H21" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Days from nadir to first ANC recovery</x:t>
@@ -10919,7 +11180,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C22" s="7"/>
+      <x:c r="C22" s="7" t="n"/>
       <x:c r="D22" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10933,7 +11194,7 @@
           <x:t xml:space="preserve">OS</x:t>
         </x:is>
       </x:c>
-      <x:c r="G22" s="7"/>
+      <x:c r="G22" s="7" t="n"/>
       <x:c r="H22" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Overall Survival</x:t>
@@ -10951,7 +11212,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C23" s="7"/>
+      <x:c r="C23" s="7" t="n"/>
       <x:c r="D23" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10965,7 +11226,7 @@
           <x:t xml:space="preserve">PFS</x:t>
         </x:is>
       </x:c>
-      <x:c r="G23" s="7"/>
+      <x:c r="G23" s="7" t="n"/>
       <x:c r="H23" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Progression-Free Survival</x:t>
@@ -10983,7 +11244,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C24" s="7"/>
+      <x:c r="C24" s="7" t="n"/>
       <x:c r="D24" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -10997,7 +11258,7 @@
           <x:t xml:space="preserve">TTPSA</x:t>
         </x:is>
       </x:c>
-      <x:c r="G24" s="7"/>
+      <x:c r="G24" s="7" t="n"/>
       <x:c r="H24" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Time to PSA Progression</x:t>
@@ -11015,7 +11276,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C25" s="7"/>
+      <x:c r="C25" s="7" t="n"/>
       <x:c r="D25" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11029,7 +11290,7 @@
           <x:t xml:space="preserve">TTUMOR</x:t>
         </x:is>
       </x:c>
-      <x:c r="G25" s="7"/>
+      <x:c r="G25" s="7" t="n"/>
       <x:c r="H25" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Time to Tumor Progression</x:t>
@@ -11047,7 +11308,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C26" s="7"/>
+      <x:c r="C26" s="7" t="n"/>
       <x:c r="D26" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11061,7 +11322,7 @@
           <x:t xml:space="preserve">TTPAIN</x:t>
         </x:is>
       </x:c>
-      <x:c r="G26" s="7"/>
+      <x:c r="G26" s="7" t="n"/>
       <x:c r="H26" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Time to Pain Progression</x:t>
@@ -11079,7 +11340,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C27" s="7"/>
+      <x:c r="C27" s="7" t="n"/>
       <x:c r="D27" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11093,7 +11354,7 @@
           <x:t xml:space="preserve">TTSAE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G27" s="7"/>
+      <x:c r="G27" s="7" t="n"/>
       <x:c r="H27" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Time to First Serious Adverse Event</x:t>
@@ -11111,7 +11372,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C28" s="7"/>
+      <x:c r="C28" s="7" t="n"/>
       <x:c r="D28" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11125,7 +11386,7 @@
           <x:t xml:space="preserve">ALP</x:t>
         </x:is>
       </x:c>
-      <x:c r="G28" s="7"/>
+      <x:c r="G28" s="7" t="n"/>
       <x:c r="H28" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ALKALINE PHOSPHATASE</x:t>
@@ -11143,7 +11404,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C29" s="7"/>
+      <x:c r="C29" s="7" t="n"/>
       <x:c r="D29" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11157,7 +11418,7 @@
           <x:t xml:space="preserve">ALT</x:t>
         </x:is>
       </x:c>
-      <x:c r="G29" s="7"/>
+      <x:c r="G29" s="7" t="n"/>
       <x:c r="H29" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ALANINE AMINOTRANSFERASE</x:t>
@@ -11175,7 +11436,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C30" s="7"/>
+      <x:c r="C30" s="7" t="n"/>
       <x:c r="D30" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11189,7 +11450,7 @@
           <x:t xml:space="preserve">AST</x:t>
         </x:is>
       </x:c>
-      <x:c r="G30" s="7"/>
+      <x:c r="G30" s="7" t="n"/>
       <x:c r="H30" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ASPARTATE AMINOTRANSFERASE</x:t>
@@ -11207,7 +11468,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C31" s="7"/>
+      <x:c r="C31" s="7" t="n"/>
       <x:c r="D31" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11221,7 +11482,7 @@
           <x:t xml:space="preserve">BASO</x:t>
         </x:is>
       </x:c>
-      <x:c r="G31" s="7"/>
+      <x:c r="G31" s="7" t="n"/>
       <x:c r="H31" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">BASOPHILS</x:t>
@@ -11239,7 +11500,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C32" s="7"/>
+      <x:c r="C32" s="7" t="n"/>
       <x:c r="D32" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11253,7 +11514,7 @@
           <x:t xml:space="preserve">BESTRESP</x:t>
         </x:is>
       </x:c>
-      <x:c r="G32" s="7"/>
+      <x:c r="G32" s="7" t="n"/>
       <x:c r="H32" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Best Overall Response (BOR)</x:t>
@@ -11271,7 +11532,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C33" s="7"/>
+      <x:c r="C33" s="7" t="n"/>
       <x:c r="D33" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11285,7 +11546,7 @@
           <x:t xml:space="preserve">BICARB</x:t>
         </x:is>
       </x:c>
-      <x:c r="G33" s="7"/>
+      <x:c r="G33" s="7" t="n"/>
       <x:c r="H33" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">BICARBONATE</x:t>
@@ -11303,7 +11564,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C34" s="7"/>
+      <x:c r="C34" s="7" t="n"/>
       <x:c r="D34" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11317,7 +11578,7 @@
           <x:t xml:space="preserve">BILI</x:t>
         </x:is>
       </x:c>
-      <x:c r="G34" s="7"/>
+      <x:c r="G34" s="7" t="n"/>
       <x:c r="H34" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">BILIRUBIN</x:t>
@@ -11335,7 +11596,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C35" s="7"/>
+      <x:c r="C35" s="7" t="n"/>
       <x:c r="D35" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11349,7 +11610,7 @@
           <x:t xml:space="preserve">BUN</x:t>
         </x:is>
       </x:c>
-      <x:c r="G35" s="7"/>
+      <x:c r="G35" s="7" t="n"/>
       <x:c r="H35" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">BLOOD UREA NITROGEN</x:t>
@@ -11367,7 +11628,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C36" s="7"/>
+      <x:c r="C36" s="7" t="n"/>
       <x:c r="D36" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11381,7 +11642,7 @@
           <x:t xml:space="preserve">CL</x:t>
         </x:is>
       </x:c>
-      <x:c r="G36" s="7"/>
+      <x:c r="G36" s="7" t="n"/>
       <x:c r="H36" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CHLORIDE</x:t>
@@ -11399,7 +11660,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C37" s="7"/>
+      <x:c r="C37" s="7" t="n"/>
       <x:c r="D37" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11413,7 +11674,7 @@
           <x:t xml:space="preserve">CREAT</x:t>
         </x:is>
       </x:c>
-      <x:c r="G37" s="7"/>
+      <x:c r="G37" s="7" t="n"/>
       <x:c r="H37" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CREATININE</x:t>
@@ -11431,7 +11692,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C38" s="7"/>
+      <x:c r="C38" s="7" t="n"/>
       <x:c r="D38" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11445,11 +11706,9 @@
           <x:t xml:space="preserve">CUMDOSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G38" s="7"/>
-      <x:c r="H38" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cumulative Actual Dose (mg/m2)</x:t>
-        </x:is>
+      <x:c r="G38" s="7" t="n"/>
+      <x:c r="H38" s="7" t="str">
+        <x:v>Cumulative IV Actual Dose (mg/m2)</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="30" customHeight="1">
@@ -11463,7 +11722,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C39" s="7"/>
+      <x:c r="C39" s="7" t="n"/>
       <x:c r="D39" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11477,7 +11736,7 @@
           <x:t xml:space="preserve">EOS</x:t>
         </x:is>
       </x:c>
-      <x:c r="G39" s="7"/>
+      <x:c r="G39" s="7" t="n"/>
       <x:c r="H39" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">EOSINOPHILS</x:t>
@@ -11495,7 +11754,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C40" s="7"/>
+      <x:c r="C40" s="7" t="n"/>
       <x:c r="D40" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11509,7 +11768,7 @@
           <x:t xml:space="preserve">GLUC</x:t>
         </x:is>
       </x:c>
-      <x:c r="G40" s="7"/>
+      <x:c r="G40" s="7" t="n"/>
       <x:c r="H40" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GLUCOSE</x:t>
@@ -11527,7 +11786,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C41" s="7"/>
+      <x:c r="C41" s="7" t="n"/>
       <x:c r="D41" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11541,7 +11800,7 @@
           <x:t xml:space="preserve">HGB</x:t>
         </x:is>
       </x:c>
-      <x:c r="G41" s="7"/>
+      <x:c r="G41" s="7" t="n"/>
       <x:c r="H41" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">HEMOGLOBIN</x:t>
@@ -11559,7 +11818,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C42" s="7"/>
+      <x:c r="C42" s="7" t="n"/>
       <x:c r="D42" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11573,7 +11832,7 @@
           <x:t xml:space="preserve">K</x:t>
         </x:is>
       </x:c>
-      <x:c r="G42" s="7"/>
+      <x:c r="G42" s="7" t="n"/>
       <x:c r="H42" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">POTASSIUM</x:t>
@@ -11591,7 +11850,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C43" s="7"/>
+      <x:c r="C43" s="7" t="n"/>
       <x:c r="D43" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11605,7 +11864,7 @@
           <x:t xml:space="preserve">LYM</x:t>
         </x:is>
       </x:c>
-      <x:c r="G43" s="7"/>
+      <x:c r="G43" s="7" t="n"/>
       <x:c r="H43" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LYMPHOCYTES</x:t>
@@ -11623,7 +11882,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C44" s="7"/>
+      <x:c r="C44" s="7" t="n"/>
       <x:c r="D44" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11637,7 +11896,7 @@
           <x:t xml:space="preserve">MONO</x:t>
         </x:is>
       </x:c>
-      <x:c r="G44" s="7"/>
+      <x:c r="G44" s="7" t="n"/>
       <x:c r="H44" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MONOCYTES</x:t>
@@ -11655,7 +11914,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C45" s="7"/>
+      <x:c r="C45" s="7" t="n"/>
       <x:c r="D45" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11669,7 +11928,7 @@
           <x:t xml:space="preserve">NCYCLE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G45" s="7"/>
+      <x:c r="G45" s="7" t="n"/>
       <x:c r="H45" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Number of Cycles Received</x:t>
@@ -11687,7 +11946,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C46" s="7"/>
+      <x:c r="C46" s="7" t="n"/>
       <x:c r="D46" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11701,7 +11960,7 @@
           <x:t xml:space="preserve">NDELDOSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G46" s="7"/>
+      <x:c r="G46" s="7" t="n"/>
       <x:c r="H46" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Number of Dose Delays</x:t>
@@ -11719,7 +11978,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C47" s="7"/>
+      <x:c r="C47" s="7" t="n"/>
       <x:c r="D47" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11733,7 +11992,7 @@
           <x:t xml:space="preserve">NEUT</x:t>
         </x:is>
       </x:c>
-      <x:c r="G47" s="7"/>
+      <x:c r="G47" s="7" t="n"/>
       <x:c r="H47" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">NEUTROPHILS</x:t>
@@ -11751,7 +12010,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C48" s="7"/>
+      <x:c r="C48" s="7" t="n"/>
       <x:c r="D48" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11765,7 +12024,7 @@
           <x:t xml:space="preserve">OBJRESP</x:t>
         </x:is>
       </x:c>
-      <x:c r="G48" s="7"/>
+      <x:c r="G48" s="7" t="n"/>
       <x:c r="H48" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Objective Response (confirmed CR/PR)</x:t>
@@ -11783,7 +12042,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C49" s="7"/>
+      <x:c r="C49" s="7" t="n"/>
       <x:c r="D49" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11797,7 +12056,7 @@
           <x:t xml:space="preserve">OVRLRESP</x:t>
         </x:is>
       </x:c>
-      <x:c r="G49" s="7"/>
+      <x:c r="G49" s="7" t="n"/>
       <x:c r="H49" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Overall Response per RECIST v1.0</x:t>
@@ -11815,7 +12074,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C50" s="7"/>
+      <x:c r="C50" s="7" t="n"/>
       <x:c r="D50" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11829,7 +12088,7 @@
           <x:t xml:space="preserve">PLAT</x:t>
         </x:is>
       </x:c>
-      <x:c r="G50" s="7"/>
+      <x:c r="G50" s="7" t="n"/>
       <x:c r="H50" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">PLATELETS</x:t>
@@ -11847,7 +12106,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C51" s="7"/>
+      <x:c r="C51" s="7" t="n"/>
       <x:c r="D51" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11861,11 +12120,9 @@
           <x:t xml:space="preserve">PLDOSE</x:t>
         </x:is>
       </x:c>
-      <x:c r="G51" s="7"/>
-      <x:c r="H51" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Planned Dose (mg/m2)</x:t>
-        </x:is>
+      <x:c r="G51" s="7" t="n"/>
+      <x:c r="H51" s="7" t="str">
+        <x:v>Initial Planned IV Dose (mg/m2)</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="30" customHeight="1">
@@ -11879,7 +12136,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C52" s="7"/>
+      <x:c r="C52" s="7" t="n"/>
       <x:c r="D52" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11893,7 +12150,7 @@
           <x:t xml:space="preserve">PSA</x:t>
         </x:is>
       </x:c>
-      <x:c r="G52" s="7"/>
+      <x:c r="G52" s="7" t="n"/>
       <x:c r="H52" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">PROSTATE SPECIFIC ANTIGEN</x:t>
@@ -11911,7 +12168,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C53" s="7"/>
+      <x:c r="C53" s="7" t="n"/>
       <x:c r="D53" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11925,7 +12182,7 @@
           <x:t xml:space="preserve">PSARESP</x:t>
         </x:is>
       </x:c>
-      <x:c r="G53" s="7"/>
+      <x:c r="G53" s="7" t="n"/>
       <x:c r="H53" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">PSA Response (&gt;=50% decline)</x:t>
@@ -11943,7 +12200,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C54" s="7"/>
+      <x:c r="C54" s="7" t="n"/>
       <x:c r="D54" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11957,11 +12214,9 @@
           <x:t xml:space="preserve">PSPROG</x:t>
         </x:is>
       </x:c>
-      <x:c r="G54" s="7"/>
-      <x:c r="H54" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PSA Progression (PCWG3)</x:t>
-        </x:is>
+      <x:c r="G54" s="7" t="n"/>
+      <x:c r="H54" s="7" t="str">
+        <x:v>PSA Progression (reconstructed rule)</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="30" customHeight="1">
@@ -11975,7 +12230,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C55" s="7"/>
+      <x:c r="C55" s="7" t="n"/>
       <x:c r="D55" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -11989,7 +12244,7 @@
           <x:t xml:space="preserve">RBC</x:t>
         </x:is>
       </x:c>
-      <x:c r="G55" s="7"/>
+      <x:c r="G55" s="7" t="n"/>
       <x:c r="H55" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ERYTHROCYTES</x:t>
@@ -12007,7 +12262,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C56" s="7"/>
+      <x:c r="C56" s="7" t="n"/>
       <x:c r="D56" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -12021,7 +12276,7 @@
           <x:t xml:space="preserve">SODIUM</x:t>
         </x:is>
       </x:c>
-      <x:c r="G56" s="7"/>
+      <x:c r="G56" s="7" t="n"/>
       <x:c r="H56" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SODIUM</x:t>
@@ -12039,7 +12294,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C57" s="7"/>
+      <x:c r="C57" s="7" t="n"/>
       <x:c r="D57" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -12053,7 +12308,7 @@
           <x:t xml:space="preserve">TESTO</x:t>
         </x:is>
       </x:c>
-      <x:c r="G57" s="7"/>
+      <x:c r="G57" s="7" t="n"/>
       <x:c r="H57" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TESTOSTERONE</x:t>
@@ -12071,7 +12326,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C58" s="7"/>
+      <x:c r="C58" s="7" t="n"/>
       <x:c r="D58" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -12085,7 +12340,7 @@
           <x:t xml:space="preserve">TESTOFR</x:t>
         </x:is>
       </x:c>
-      <x:c r="G58" s="7"/>
+      <x:c r="G58" s="7" t="n"/>
       <x:c r="H58" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TESTOSTERONE, FREE</x:t>
@@ -12103,7 +12358,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C59" s="7"/>
+      <x:c r="C59" s="7" t="n"/>
       <x:c r="D59" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -12117,7 +12372,7 @@
           <x:t xml:space="preserve">UREA</x:t>
         </x:is>
       </x:c>
-      <x:c r="G59" s="7"/>
+      <x:c r="G59" s="7" t="n"/>
       <x:c r="H59" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">UREA</x:t>
@@ -12135,7 +12390,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C60" s="7"/>
+      <x:c r="C60" s="7" t="n"/>
       <x:c r="D60" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -12149,7 +12404,7 @@
           <x:t xml:space="preserve">WBC</x:t>
         </x:is>
       </x:c>
-      <x:c r="G60" s="7"/>
+      <x:c r="G60" s="7" t="n"/>
       <x:c r="H60" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LEUKOCYTES</x:t>
@@ -12167,7 +12422,7 @@
           <x:t xml:space="preserve">Parameter Code Codelist</x:t>
         </x:is>
       </x:c>
-      <x:c r="C61" s="8"/>
+      <x:c r="C61" s="8" t="n"/>
       <x:c r="D61" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">text</x:t>
@@ -12181,11 +12436,31 @@
           <x:t xml:space="preserve">BSGRESP</x:t>
         </x:is>
       </x:c>
-      <x:c r="G61" s="8"/>
-      <x:c r="H61" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bone Scan Progression (PCWG3)</x:t>
-        </x:is>
+      <x:c r="G61" s="8" t="n"/>
+      <x:c r="H61" s="8" t="str">
+        <x:v>Exploratory Bone Progression (2+2)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" hidden="0" customHeight="1">
+      <x:c r="A62" t="str">
+        <x:v>CL.PARAMCD</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>Parameter Code Codelist</x:v>
+      </x:c>
+      <x:c r="C62"/>
+      <x:c r="D62" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="E62" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F62" t="str">
+        <x:v>CLINPROG</x:v>
+      </x:c>
+      <x:c r="G62"/>
+      <x:c r="H62" t="str">
+        <x:v>Disposition Clinical Progression</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12197,11 +12472,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" customWidth="1"/>
+    <x:col min="2" max="2" width="32" customWidth="1"/>
+    <x:col min="3" max="3" width="16" customWidth="1"/>
+    <x:col min="4" max="4" width="24" customWidth="1"/>
+    <x:col min="5" max="5" width="16" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -12240,14 +12515,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="78" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" customWidth="1"/>
+    <x:col min="2" max="2" width="30" customWidth="1"/>
+    <x:col min="3" max="3" width="16" customWidth="1"/>
+    <x:col min="4" max="4" width="78" customWidth="1"/>
+    <x:col min="5" max="5" width="24" customWidth="1"/>
+    <x:col min="6" max="6" width="42" customWidth="1"/>
+    <x:col min="7" max="7" width="24" customWidth="1"/>
+    <x:col min="8" max="8" width="12" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">
@@ -12313,10 +12588,10 @@
           <x:t xml:space="preserve">Date of first exposure to treatment, derived as the minimum of EXSTDTC from the EX SDTM dataset.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
+      <x:c r="E2" s="7" t="n"/>
+      <x:c r="F2" s="7" t="n"/>
+      <x:c r="G2" s="7" t="n"/>
+      <x:c r="H2" s="7" t="n"/>
     </x:row>
     <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="7" t="inlineStr">
@@ -12339,10 +12614,10 @@
           <x:t xml:space="preserve">Date of last exposure to treatment, derived as the maximum of EXENDTC from the EX SDTM dataset.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E3" s="7"/>
-      <x:c r="F3" s="7"/>
-      <x:c r="G3" s="7"/>
-      <x:c r="H3" s="7"/>
+      <x:c r="E3" s="7" t="n"/>
+      <x:c r="F3" s="7" t="n"/>
+      <x:c r="G3" s="7" t="n"/>
+      <x:c r="H3" s="7" t="n"/>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="7" t="inlineStr">
@@ -12365,10 +12640,10 @@
           <x:t xml:space="preserve">Treatment duration in days, calculated as: TRTEDT - TRTSDT + 1.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E4" s="7"/>
-      <x:c r="F4" s="7"/>
-      <x:c r="G4" s="7"/>
-      <x:c r="H4" s="7"/>
+      <x:c r="E4" s="7" t="n"/>
+      <x:c r="F4" s="7" t="n"/>
+      <x:c r="G4" s="7" t="n"/>
+      <x:c r="H4" s="7" t="n"/>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="7" t="inlineStr">
@@ -12391,10 +12666,10 @@
           <x:t xml:space="preserve">Intent-to-treat population flag, set to Y for all randomized subjects.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" s="7"/>
-      <x:c r="F5" s="7"/>
-      <x:c r="G5" s="7"/>
-      <x:c r="H5" s="7"/>
+      <x:c r="E5" s="7" t="n"/>
+      <x:c r="F5" s="7" t="n"/>
+      <x:c r="G5" s="7" t="n"/>
+      <x:c r="H5" s="7" t="n"/>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="7" t="inlineStr">
@@ -12417,10 +12692,10 @@
           <x:t xml:space="preserve">Safety population flag, set to Y for all subjects who received at least one dose of study treatment.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="7"/>
-      <x:c r="F6" s="7"/>
-      <x:c r="G6" s="7"/>
-      <x:c r="H6" s="7"/>
+      <x:c r="E6" s="7" t="n"/>
+      <x:c r="F6" s="7" t="n"/>
+      <x:c r="G6" s="7" t="n"/>
+      <x:c r="H6" s="7" t="n"/>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="7" t="inlineStr">
@@ -12443,10 +12718,10 @@
           <x:t xml:space="preserve">Baseline ECOG performance status, derived as the first non-missing value from VS where VSTESTCD = 'ECOG' and VSBLFL = 'Y'.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="7"/>
-      <x:c r="F7" s="7"/>
-      <x:c r="G7" s="7"/>
-      <x:c r="H7" s="7"/>
+      <x:c r="E7" s="7" t="n"/>
+      <x:c r="F7" s="7" t="n"/>
+      <x:c r="G7" s="7" t="n"/>
+      <x:c r="H7" s="7" t="n"/>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="7" t="inlineStr">
@@ -12469,10 +12744,10 @@
           <x:t xml:space="preserve">Baseline measurable disease flag, set to Y if target lesions are present at baseline in the LS SDTM dataset.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="7"/>
-      <x:c r="F8" s="7"/>
-      <x:c r="G8" s="7"/>
-      <x:c r="H8" s="7"/>
+      <x:c r="E8" s="7" t="n"/>
+      <x:c r="F8" s="7" t="n"/>
+      <x:c r="G8" s="7" t="n"/>
+      <x:c r="H8" s="7" t="n"/>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="7" t="inlineStr">
@@ -12490,15 +12765,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D9" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline pain assessment flag, set to Y if baseline pain intensity is &gt;= 2 or baseline analgesic score is &gt;= 10.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="7"/>
-      <x:c r="F9" s="7"/>
-      <x:c r="G9" s="7"/>
-      <x:c r="H9" s="7"/>
+      <x:c r="D9" s="7" t="str">
+        <x:v>Baseline pain flag from the 7 days ending on treatment start. Within each component and day, discordant duplicates are excluded. A component requires at least 5 valid days; PAINBL=Y for median pain intensity &gt;=2 or mean analgesic score &gt;=10, otherwise N.</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="n"/>
+      <x:c r="F9" s="7" t="n"/>
+      <x:c r="G9" s="7" t="n"/>
+      <x:c r="H9" s="7" t="n"/>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
       <x:c r="A10" s="7" t="inlineStr">
@@ -12516,15 +12789,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Relative Dose Intensity, calculated as (Actual cumulative dose administered / Planned cumulative dose) * 100.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="7"/>
-      <x:c r="F10" s="7"/>
-      <x:c r="G10" s="7"/>
-      <x:c r="H10" s="7"/>
+      <x:c r="D10" s="7" t="str">
+        <x:v>Source relative dose intensity carried from SDTM.EX.EXTRINT for the qualifying primary IV antineoplastic when repeated subject values are internally consistent; no dose-intensity formula is reconstructed.</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="n"/>
+      <x:c r="F10" s="7" t="n"/>
+      <x:c r="G10" s="7" t="n"/>
+      <x:c r="H10" s="7" t="n"/>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
       <x:c r="A11" s="7" t="inlineStr">
@@ -12547,10 +12818,10 @@
           <x:t xml:space="preserve">Relative Dose Intensity Category, classified as &gt;=85%, 65-&lt;85%, or &lt;65% based on RDI.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="7"/>
-      <x:c r="F11" s="7"/>
-      <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7"/>
+      <x:c r="E11" s="7" t="n"/>
+      <x:c r="F11" s="7" t="n"/>
+      <x:c r="G11" s="7" t="n"/>
+      <x:c r="H11" s="7" t="n"/>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
       <x:c r="A12" s="7" t="inlineStr">
@@ -12568,15 +12839,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Number of treatment cycles received, derived as the max of visit number from EX.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="7"/>
-      <x:c r="F12" s="7"/>
-      <x:c r="G12" s="7"/>
-      <x:c r="H12" s="7"/>
+      <x:c r="D12" s="7" t="str">
+        <x:v>Count of distinct SDTM.EX.VISITNUM cycles with a positive administered IV dose (EXDOSE2&gt;0) for the qualifying randomized antineoplastic.</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="n"/>
+      <x:c r="F12" s="7" t="n"/>
+      <x:c r="G12" s="7" t="n"/>
+      <x:c r="H12" s="7" t="n"/>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
       <x:c r="A13" s="7" t="inlineStr">
@@ -12599,10 +12868,10 @@
           <x:t xml:space="preserve">Minimum absolute neutrophil count (ANC) value observed post-baseline during Cycle 1.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="7"/>
-      <x:c r="F13" s="7"/>
-      <x:c r="G13" s="7"/>
-      <x:c r="H13" s="7"/>
+      <x:c r="E13" s="7" t="n"/>
+      <x:c r="F13" s="7" t="n"/>
+      <x:c r="G13" s="7" t="n"/>
+      <x:c r="H13" s="7" t="n"/>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
       <x:c r="A14" s="7" t="inlineStr">
@@ -12620,15 +12889,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D14" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Time-to-event duration in days, calculated as: ADT - STARTDT + 1.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="7"/>
-      <x:c r="F14" s="7"/>
-      <x:c r="G14" s="7"/>
-      <x:c r="H14" s="7"/>
+      <x:c r="D14" s="7" t="str">
+        <x:v>Inclusive duration in days: ADT - STARTDT + 1. Missing or pre-origin dates are hard validation failures; durations are never floored to one day.</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="n"/>
+      <x:c r="F14" s="7" t="n"/>
+      <x:c r="G14" s="7" t="n"/>
+      <x:c r="H14" s="7" t="n"/>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
       <x:c r="A15" s="7" t="inlineStr">
@@ -12646,15 +12913,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D15" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Censoring indicator, set to 0 if the event occurred, or 1 if censored.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="7"/>
-      <x:c r="F15" s="7"/>
-      <x:c r="G15" s="7"/>
-      <x:c r="H15" s="7"/>
+      <x:c r="D15" s="7" t="str">
+        <x:v>CNSR=0 for an eligible event under the parameter-specific rule and CNSR=1 otherwise. New anti-cancer therapy censors PFS only when it precedes the earliest eligible event.</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="n"/>
+      <x:c r="F15" s="7" t="n"/>
+      <x:c r="G15" s="7" t="n"/>
+      <x:c r="H15" s="7" t="n"/>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
       <x:c r="A16" s="7" t="inlineStr">
@@ -12672,15 +12937,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D16" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Death date derived from SDTM.DM.DTHDTC or disposition/death records.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" s="7"/>
-      <x:c r="F16" s="7"/>
-      <x:c r="G16" s="7"/>
-      <x:c r="H16" s="7"/>
+      <x:c r="D16" s="7" t="str">
+        <x:v>Earliest complete SDTM.AE.AEDTHDTC is preferred; otherwise the earliest DS death week is anchored to ADSL.RANDDT.</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="n"/>
+      <x:c r="F16" s="7" t="n"/>
+      <x:c r="G16" s="7" t="n"/>
+      <x:c r="H16" s="7" t="n"/>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="7" t="inlineStr">
@@ -12698,15 +12961,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D17" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Last known alive date derived as the maximum non-death contact or assessment date across source domains.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" s="7"/>
-      <x:c r="F17" s="7"/>
-      <x:c r="G17" s="7"/>
-      <x:c r="H17" s="7"/>
+      <x:c r="D17" s="7" t="str">
+        <x:v>Maximum dated observed contact or assessment across DS, EX, VS, LB, LS, PN, and SV, capped at DTHDT for deceased subjects.</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="n"/>
+      <x:c r="F17" s="7" t="n"/>
+      <x:c r="G17" s="7" t="n"/>
+      <x:c r="H17" s="7" t="n"/>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="7" t="inlineStr">
@@ -12724,15 +12985,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D18" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline ECOG imputation flag derived from ECOGBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" s="7"/>
-      <x:c r="F18" s="7"/>
-      <x:c r="G18" s="7"/>
-      <x:c r="H18" s="7"/>
+      <x:c r="D18" s="7" t="str">
+        <x:v>Set to N because observed baseline ECOG is not imputed.</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="n"/>
+      <x:c r="F18" s="7" t="n"/>
+      <x:c r="G18" s="7" t="n"/>
+      <x:c r="H18" s="7" t="n"/>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="7" t="inlineStr">
@@ -12750,15 +13009,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D19" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline PSA imputation flag derived from PSABL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="7"/>
-      <x:c r="F19" s="7"/>
-      <x:c r="G19" s="7"/>
-      <x:c r="H19" s="7"/>
+      <x:c r="D19" s="7" t="str">
+        <x:v>Set to N because observed baseline PSA is not imputed.</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="n"/>
+      <x:c r="F19" s="7" t="n"/>
+      <x:c r="G19" s="7" t="n"/>
+      <x:c r="H19" s="7" t="n"/>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
       <x:c r="A20" s="7" t="inlineStr">
@@ -12776,15 +13033,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D20" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline alkaline phosphatase imputation flag derived from ALPBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="7"/>
-      <x:c r="F20" s="7"/>
-      <x:c r="G20" s="7"/>
-      <x:c r="H20" s="7"/>
+      <x:c r="D20" s="7" t="str">
+        <x:v>Set to N because observed baseline alkaline phosphatase is not imputed.</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="n"/>
+      <x:c r="F20" s="7" t="n"/>
+      <x:c r="G20" s="7" t="n"/>
+      <x:c r="H20" s="7" t="n"/>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
       <x:c r="A21" s="7" t="inlineStr">
@@ -12802,15 +13057,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D21" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline hemoglobin imputation flag derived from HGBBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="7"/>
-      <x:c r="F21" s="7"/>
-      <x:c r="G21" s="7"/>
-      <x:c r="H21" s="7"/>
+      <x:c r="D21" s="7" t="str">
+        <x:v>Set to N because observed baseline hemoglobin is not imputed.</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="n"/>
+      <x:c r="F21" s="7" t="n"/>
+      <x:c r="G21" s="7" t="n"/>
+      <x:c r="H21" s="7" t="n"/>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
       <x:c r="A22" s="7" t="inlineStr">
@@ -12828,15 +13081,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D22" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline albumin imputation flag derived from ALBBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E22" s="7"/>
-      <x:c r="F22" s="7"/>
-      <x:c r="G22" s="7"/>
-      <x:c r="H22" s="7"/>
+      <x:c r="D22" s="7" t="str">
+        <x:v>Blank because baseline albumin is unavailable in the source release and is not imputed.</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="n"/>
+      <x:c r="F22" s="7" t="n"/>
+      <x:c r="G22" s="7" t="n"/>
+      <x:c r="H22" s="7" t="n"/>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
       <x:c r="A23" s="7" t="inlineStr">
@@ -12854,15 +13105,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D23" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline lactate dehydrogenase imputation flag derived from LDHBL source availability and baseline window rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E23" s="7"/>
-      <x:c r="F23" s="7"/>
-      <x:c r="G23" s="7"/>
-      <x:c r="H23" s="7"/>
+      <x:c r="D23" s="7" t="str">
+        <x:v>Blank because baseline lactate dehydrogenase is unavailable in the source release and is not imputed.</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="n"/>
+      <x:c r="F23" s="7" t="n"/>
+      <x:c r="G23" s="7" t="n"/>
+      <x:c r="H23" s="7" t="n"/>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
       <x:c r="A24" s="7" t="inlineStr">
@@ -12880,15 +13129,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D24" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Numeric exposure analysis value derived from SDTM.EX dose, duration, or cycle records according to ADEX.PARAMCD.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E24" s="7"/>
-      <x:c r="F24" s="7"/>
-      <x:c r="G24" s="7"/>
-      <x:c r="H24" s="7"/>
+      <x:c r="D24" s="7" t="str">
+        <x:v>Parameter-specific numeric value from qualifying primary IV SDTM.EX records: initial EXPDOSE, cumulative EXCUMD2, positive administered-cycle count, delay/reduction counts, consistent source EXTRINT, cycle EXDOSE2, or adjustment flag.</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="n"/>
+      <x:c r="F24" s="7" t="n"/>
+      <x:c r="G24" s="7" t="n"/>
+      <x:c r="H24" s="7" t="n"/>
     </x:row>
     <x:row r="25" ht="48" customHeight="1">
       <x:c r="A25" s="7" t="inlineStr">
@@ -12906,15 +13153,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D25" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Character exposure analysis value derived from SDTM.EX dose, duration, or cycle records according to ADEX.PARAMCD.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E25" s="7"/>
-      <x:c r="F25" s="7"/>
-      <x:c r="G25" s="7"/>
-      <x:c r="H25" s="7"/>
+      <x:c r="D25" s="7" t="str">
+        <x:v>Character representation or category corresponding to ADEX.AVAL and PARAMCD.</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="n"/>
+      <x:c r="F25" s="7" t="n"/>
+      <x:c r="G25" s="7" t="n"/>
+      <x:c r="H25" s="7" t="n"/>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
       <x:c r="A26" s="7" t="inlineStr">
@@ -12937,10 +13182,10 @@
           <x:t xml:space="preserve">Numeric ADEX parameter ordering derived from ADEX.PARAMCD.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E26" s="7"/>
-      <x:c r="F26" s="7"/>
-      <x:c r="G26" s="7"/>
-      <x:c r="H26" s="7"/>
+      <x:c r="E26" s="7" t="n"/>
+      <x:c r="F26" s="7" t="n"/>
+      <x:c r="G26" s="7" t="n"/>
+      <x:c r="H26" s="7" t="n"/>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
       <x:c r="A27" s="7" t="inlineStr">
@@ -12958,15 +13203,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D27" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Numeric ADEX analysis visit derived from ADEX.AVISIT and SDTM.EX date or sequence ordering.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E27" s="7"/>
-      <x:c r="F27" s="7"/>
-      <x:c r="G27" s="7"/>
-      <x:c r="H27" s="7"/>
+      <x:c r="D27" s="7" t="str">
+        <x:v>Cycle number from SDTM.EX.VISITNUM; summary records labelled ALL CYCLES are assigned AVISITN=0.</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="n"/>
+      <x:c r="F27" s="7" t="n"/>
+      <x:c r="G27" s="7" t="n"/>
+      <x:c r="H27" s="7" t="n"/>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
       <x:c r="A28" s="7" t="inlineStr">
@@ -12989,10 +13232,10 @@
           <x:t xml:space="preserve">Numeric adverse-event toxicity grade derived from SDTM.AE toxicity grade or severity source fields.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E28" s="7"/>
-      <x:c r="F28" s="7"/>
-      <x:c r="G28" s="7"/>
-      <x:c r="H28" s="7"/>
+      <x:c r="E28" s="7" t="n"/>
+      <x:c r="F28" s="7" t="n"/>
+      <x:c r="G28" s="7" t="n"/>
+      <x:c r="H28" s="7" t="n"/>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
       <x:c r="A29" s="7" t="inlineStr">
@@ -13015,10 +13258,10 @@
           <x:t xml:space="preserve">Numeric laboratory analysis value derived from SDTM.LB.LBSTRESN after parameter-specific unit standardization.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E29" s="7"/>
-      <x:c r="F29" s="7"/>
-      <x:c r="G29" s="7"/>
-      <x:c r="H29" s="7"/>
+      <x:c r="E29" s="7" t="n"/>
+      <x:c r="F29" s="7" t="n"/>
+      <x:c r="G29" s="7" t="n"/>
+      <x:c r="H29" s="7" t="n"/>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
       <x:c r="A30" s="7" t="inlineStr">
@@ -13041,10 +13284,10 @@
           <x:t xml:space="preserve">Character laboratory analysis value derived from SDTM.LB.LBSTRESC.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E30" s="7"/>
-      <x:c r="F30" s="7"/>
-      <x:c r="G30" s="7"/>
-      <x:c r="H30" s="7"/>
+      <x:c r="E30" s="7" t="n"/>
+      <x:c r="F30" s="7" t="n"/>
+      <x:c r="G30" s="7" t="n"/>
+      <x:c r="H30" s="7" t="n"/>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
       <x:c r="A31" s="7" t="inlineStr">
@@ -13062,15 +13305,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D31" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Analysis toxicity grade derived from laboratory result, normal range, and grading rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" s="7"/>
-      <x:c r="F31" s="7"/>
-      <x:c r="G31" s="7"/>
-      <x:c r="H31" s="7"/>
+      <x:c r="D31" s="7" t="str">
+        <x:v>Numeric carry-forward of SDTM.LB.LBTOXGR. No independent CTCAE grading algorithm is applied.</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="n"/>
+      <x:c r="F31" s="7" t="n"/>
+      <x:c r="G31" s="7" t="n"/>
+      <x:c r="H31" s="7" t="n"/>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
       <x:c r="A32" s="7" t="inlineStr">
@@ -13088,15 +13329,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D32" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline numeric value selected from the latest eligible pre-treatment ADLB.AVAL record.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E32" s="7"/>
-      <x:c r="F32" s="7"/>
-      <x:c r="G32" s="7"/>
-      <x:c r="H32" s="7"/>
+      <x:c r="D32" s="7" t="str">
+        <x:v>Numeric value from the deterministic SDTM.LB.LBBLFL=Y record selected by date and LBSEQ within subject and parameter.</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="n"/>
+      <x:c r="F32" s="7" t="n"/>
+      <x:c r="G32" s="7" t="n"/>
+      <x:c r="H32" s="7" t="n"/>
     </x:row>
     <x:row r="33" ht="48" customHeight="1">
       <x:c r="A33" s="7" t="inlineStr">
@@ -13114,15 +13353,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D33" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline character value selected from the latest eligible pre-treatment ADLB.AVALC record.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E33" s="7"/>
-      <x:c r="F33" s="7"/>
-      <x:c r="G33" s="7"/>
-      <x:c r="H33" s="7"/>
+      <x:c r="D33" s="7" t="str">
+        <x:v>Character value from the same deterministic SDTM.LB.LBBLFL=Y record used for BASE.</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="n"/>
+      <x:c r="F33" s="7" t="n"/>
+      <x:c r="G33" s="7" t="n"/>
+      <x:c r="H33" s="7" t="n"/>
     </x:row>
     <x:row r="34" ht="48" customHeight="1">
       <x:c r="A34" s="7" t="inlineStr">
@@ -13145,10 +13382,10 @@
           <x:t xml:space="preserve">Change from baseline calculated as ADLB.AVAL minus ADLB.BASE.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E34" s="7"/>
-      <x:c r="F34" s="7"/>
-      <x:c r="G34" s="7"/>
-      <x:c r="H34" s="7"/>
+      <x:c r="E34" s="7" t="n"/>
+      <x:c r="F34" s="7" t="n"/>
+      <x:c r="G34" s="7" t="n"/>
+      <x:c r="H34" s="7" t="n"/>
     </x:row>
     <x:row r="35" ht="48" customHeight="1">
       <x:c r="A35" s="7" t="inlineStr">
@@ -13171,10 +13408,10 @@
           <x:t xml:space="preserve">Percent change from baseline calculated as 100 times ADLB.CHG divided by ADLB.BASE.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E35" s="7"/>
-      <x:c r="F35" s="7"/>
-      <x:c r="G35" s="7"/>
-      <x:c r="H35" s="7"/>
+      <x:c r="E35" s="7" t="n"/>
+      <x:c r="F35" s="7" t="n"/>
+      <x:c r="G35" s="7" t="n"/>
+      <x:c r="H35" s="7" t="n"/>
     </x:row>
     <x:row r="36" ht="48" customHeight="1">
       <x:c r="A36" s="7" t="inlineStr">
@@ -13192,15 +13429,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D36" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline flag set on the selected eligible pre-treatment laboratory record.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E36" s="7"/>
-      <x:c r="F36" s="7"/>
-      <x:c r="G36" s="7"/>
-      <x:c r="H36" s="7"/>
+      <x:c r="D36" s="7" t="str">
+        <x:v>Y only on the SDTM.LB record selected as baseline from LBBLFL=Y; N otherwise.</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="n"/>
+      <x:c r="F36" s="7" t="n"/>
+      <x:c r="G36" s="7" t="n"/>
+      <x:c r="H36" s="7" t="n"/>
     </x:row>
     <x:row r="37" ht="48" customHeight="1">
       <x:c r="A37" s="7" t="inlineStr">
@@ -13223,10 +13458,10 @@
           <x:t xml:space="preserve">Analysis date derived from SDTM.LB.LBDTC.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E37" s="7"/>
-      <x:c r="F37" s="7"/>
-      <x:c r="G37" s="7"/>
-      <x:c r="H37" s="7"/>
+      <x:c r="E37" s="7" t="n"/>
+      <x:c r="F37" s="7" t="n"/>
+      <x:c r="G37" s="7" t="n"/>
+      <x:c r="H37" s="7" t="n"/>
     </x:row>
     <x:row r="38" ht="48" customHeight="1">
       <x:c r="A38" s="7" t="inlineStr">
@@ -13244,15 +13479,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D38" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Character response result derived from response source assessments and response derivation rules.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E38" s="7"/>
-      <x:c r="F38" s="7"/>
-      <x:c r="G38" s="7"/>
-      <x:c r="H38" s="7"/>
+      <x:c r="D38" s="7" t="str">
+        <x:v>Parameter-specific response result. OVRLRESP is lesion-derived RECIST v1.0; BESTRESP/OBJRESP use confirmed objective-response rules without an intervening PD; PSPROG is reconstructed with prior nadir; BSGRESP is exploratory; CLINPROG remains separately typed.</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="n"/>
+      <x:c r="F38" s="7" t="n"/>
+      <x:c r="G38" s="7" t="n"/>
+      <x:c r="H38" s="7" t="n"/>
     </x:row>
     <x:row r="39" ht="48" customHeight="1">
       <x:c r="A39" s="7" t="inlineStr">
@@ -13270,15 +13503,13 @@
           <x:t xml:space="preserve">Computation</x:t>
         </x:is>
       </x:c>
-      <x:c r="D39" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Numeric response category derived from ADRS.AVALC response ordering.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E39" s="7"/>
-      <x:c r="F39" s="7"/>
-      <x:c r="G39" s="7"/>
-      <x:c r="H39" s="7"/>
+      <x:c r="D39" s="7" t="str">
+        <x:v>Numeric category mapped from the parameter-specific ADRS.AVALC value.</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="n"/>
+      <x:c r="F39" s="7" t="n"/>
+      <x:c r="G39" s="7" t="n"/>
+      <x:c r="H39" s="7" t="n"/>
     </x:row>
     <x:row r="40" ht="48" customHeight="1">
       <x:c r="A40" s="7" t="inlineStr">
@@ -13301,10 +13532,10 @@
           <x:t xml:space="preserve">Intent-to-treat flag inherited from ADSL.ITTFL.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E40" s="7"/>
-      <x:c r="F40" s="7"/>
-      <x:c r="G40" s="7"/>
-      <x:c r="H40" s="7"/>
+      <x:c r="E40" s="7" t="n"/>
+      <x:c r="F40" s="7" t="n"/>
+      <x:c r="G40" s="7" t="n"/>
+      <x:c r="H40" s="7" t="n"/>
     </x:row>
     <x:row r="41" ht="48" customHeight="1">
       <x:c r="A41" s="7" t="inlineStr">
@@ -13327,10 +13558,10 @@
           <x:t xml:space="preserve">Safety population flag inherited from ADSL.SAFFL.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E41" s="7"/>
-      <x:c r="F41" s="7"/>
-      <x:c r="G41" s="7"/>
-      <x:c r="H41" s="7"/>
+      <x:c r="E41" s="7" t="n"/>
+      <x:c r="F41" s="7" t="n"/>
+      <x:c r="G41" s="7" t="n"/>
+      <x:c r="H41" s="7" t="n"/>
     </x:row>
     <x:row r="42" ht="48" customHeight="1">
       <x:c r="A42" s="7" t="inlineStr">
@@ -13353,10 +13584,10 @@
           <x:t xml:space="preserve">Numeric ADTTE parameter ordering derived from ADTTE.PARAMCD.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E42" s="7"/>
-      <x:c r="F42" s="7"/>
-      <x:c r="G42" s="7"/>
-      <x:c r="H42" s="7"/>
+      <x:c r="E42" s="7" t="n"/>
+      <x:c r="F42" s="7" t="n"/>
+      <x:c r="G42" s="7" t="n"/>
+      <x:c r="H42" s="7" t="n"/>
     </x:row>
     <x:row r="43" ht="48" customHeight="1">
       <x:c r="A43" s="7" t="inlineStr">
@@ -13379,10 +13610,10 @@
           <x:t xml:space="preserve">Time-to-event parameter category derived from ADTTE.PARAMCD.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E43" s="7"/>
-      <x:c r="F43" s="7"/>
-      <x:c r="G43" s="7"/>
-      <x:c r="H43" s="7"/>
+      <x:c r="E43" s="7" t="n"/>
+      <x:c r="F43" s="7" t="n"/>
+      <x:c r="G43" s="7" t="n"/>
+      <x:c r="H43" s="7" t="n"/>
     </x:row>
     <x:row r="44" ht="48" customHeight="1">
       <x:c r="A44" s="7" t="inlineStr">
@@ -13405,10 +13636,10 @@
           <x:t xml:space="preserve">Time-to-event unit assigned by ADTTE parameter derivation.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E44" s="7"/>
-      <x:c r="F44" s="7"/>
-      <x:c r="G44" s="7"/>
-      <x:c r="H44" s="7"/>
+      <x:c r="E44" s="7" t="n"/>
+      <x:c r="F44" s="7" t="n"/>
+      <x:c r="G44" s="7" t="n"/>
+      <x:c r="H44" s="7" t="n"/>
     </x:row>
     <x:row r="45" ht="48" customHeight="1">
       <x:c r="A45" s="7" t="inlineStr">
@@ -13431,10 +13662,10 @@
           <x:t xml:space="preserve">Analysis medication start date derived from SDTM.CM.CMSTDTC.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E45" s="7"/>
-      <x:c r="F45" s="7"/>
-      <x:c r="G45" s="7"/>
-      <x:c r="H45" s="7"/>
+      <x:c r="E45" s="7" t="n"/>
+      <x:c r="F45" s="7" t="n"/>
+      <x:c r="G45" s="7" t="n"/>
+      <x:c r="H45" s="7" t="n"/>
     </x:row>
     <x:row r="46" ht="48" customHeight="1">
       <x:c r="A46" s="7" t="inlineStr">
@@ -13457,10 +13688,10 @@
           <x:t xml:space="preserve">Analysis medication end date derived from SDTM.CM.CMENDTC.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E46" s="7"/>
-      <x:c r="F46" s="7"/>
-      <x:c r="G46" s="7"/>
-      <x:c r="H46" s="7"/>
+      <x:c r="E46" s="7" t="n"/>
+      <x:c r="F46" s="7" t="n"/>
+      <x:c r="G46" s="7" t="n"/>
+      <x:c r="H46" s="7" t="n"/>
     </x:row>
     <x:row r="47" ht="48" customHeight="1">
       <x:c r="A47" s="8" t="inlineStr">
@@ -13483,10 +13714,64 @@
           <x:t xml:space="preserve">Analysis medication start relative day derived from ADCM.ASTDT and ADSL.TRTSDT.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E47" s="8"/>
-      <x:c r="F47" s="8"/>
-      <x:c r="G47" s="8"/>
-      <x:c r="H47" s="8"/>
+      <x:c r="E47" s="8" t="n"/>
+      <x:c r="F47" s="8" t="n"/>
+      <x:c r="G47" s="8" t="n"/>
+      <x:c r="H47" s="8" t="n"/>
+    </x:row>
+    <x:row r="48" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A48" t="str">
+        <x:v>MT.TRT01A</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>Method for TRT01A/TRT01AN</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Computation</x:v>
+      </x:c>
+      <x:c r="D48" s="25" t="str">
+        <x:v>Actual treatment is derived from administered qualifying primary IV antineoplastic in SDTM.EX (cabazitaxel/XRP6258 or mitoxantrone). If no qualifying IV record exists, planned treatment is retained; TRT01AN maps CbzP=1 and MP=2.</x:v>
+      </x:c>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
+      <x:c r="G48"/>
+      <x:c r="H48"/>
+    </x:row>
+    <x:row r="49" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A49" t="str">
+        <x:v>MT.ADLB_PARCAT1</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>Method for ADLB PARCAT1</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Computation</x:v>
+      </x:c>
+      <x:c r="D49" s="25" t="str">
+        <x:v>PARCAT1 is assigned TUMOR MARKER for PARAMCD=PSA; otherwise it is carried from SDTM.LB.LBCAT.</x:v>
+      </x:c>
+      <x:c r="E49"/>
+      <x:c r="F49"/>
+      <x:c r="G49"/>
+      <x:c r="H49"/>
+    </x:row>
+    <x:row r="50" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A50" t="str">
+        <x:v>MT.ADTTE_ADT</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>Method for ADTTE event/censor date</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Computation</x:v>
+      </x:c>
+      <x:c r="D50" s="25" t="str">
+        <x:v>OS, PFS, TTPSA, TTUMOR, and TTPAIN start at randomization; TTSAE starts at first dose. All are bounded by the analysis cutoff. OS uses eligible death; PFS uses the earliest eligible lesion-derived RECIST, reconstructed PSA, governed F-042 pain, or death component unless earlier NACT censors; TTPSA, TTUMOR, and TTPAIN use their typed components; TTSAE uses the first treatment-emergent serious AE through the earliest of last known alive, 30 days after last dose, and the cutoff. Censor dates are parameter-specific and may not precede STARTDT.</x:v>
+      </x:c>
+      <x:c r="E50"/>
+      <x:c r="F50"/>
+      <x:c r="G50"/>
+      <x:c r="H50"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13497,10 +13782,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" customWidth="1"/>
+    <x:col min="2" max="2" width="70" customWidth="1"/>
+    <x:col min="3" max="3" width="28" customWidth="1"/>
+    <x:col min="4" max="4" width="12" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="1" customFormat="1" ht="32" customHeight="1">

--- a/08_submission_package/m5/datasets/tropic/analysis/adam/ADaM_spec.xlsx
+++ b/08_submission_package/m5/datasets/tropic/analysis/adam/ADaM_spec.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study" sheetId="1" r:id="R8417359375c7412e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" r:id="R157960e7de3e429c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables" sheetId="3" r:id="R7ba54f32b8544e54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValueLevel" sheetId="4" r:id="R342ecab52a594eef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WhereClauses" sheetId="5" r:id="Rb6c7b016bfba4d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelists" sheetId="6" r:id="R676e14af20e64810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionaries" sheetId="7" r:id="R339fe328673e42a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods" sheetId="8" r:id="R4f84911ab6864d73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comments" sheetId="9" r:id="R260fc5554cf64d02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="10" r:id="Rb45df35fb9364064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study" sheetId="1" r:id="Rc041649ab5554055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" r:id="Rcc20954077054d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables" sheetId="3" r:id="R2d217589ce264202"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValueLevel" sheetId="4" r:id="R717134b3794c4374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WhereClauses" sheetId="5" r:id="R3109866325c14908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelists" sheetId="6" r:id="R93ff3ae7674a4239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionaries" sheetId="7" r:id="Rb3c15e576fc749fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods" sheetId="8" r:id="R83a45a79b9d14a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comments" sheetId="9" r:id="Rb5b31fd95c3d44df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="10" r:id="R449dfa3fdd8c48d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7368,15 +7368,11 @@
           <x:t xml:space="preserve">ADLB</x:t>
         </x:is>
       </x:c>
-      <x:c r="C124" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BASEFL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D124" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Baseline Record Flag</x:t>
-        </x:is>
+      <x:c r="C124" s="7" t="str">
+        <x:v>ABLFL</x:v>
+      </x:c>
+      <x:c r="D124" s="7" t="str">
+        <x:v>Baseline Record Flag</x:v>
       </x:c>
       <x:c r="E124" s="7" t="inlineStr">
         <x:is>
@@ -7404,13 +7400,11 @@
         </x:is>
       </x:c>
       <x:c r="L124" s="7" t="n"/>
-      <x:c r="M124" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MT.ADLB_BASEFL</x:t>
-        </x:is>
+      <x:c r="M124" s="7" t="str">
+        <x:v>MT.ADLB_ABLFL</x:v>
       </x:c>
       <x:c r="N124" s="7" t="str">
-        <x:v>Y only on the SDTM.LB record selected as baseline from LBBLFL=Y; N otherwise.</x:v>
+        <x:v>Y only on the deterministic SDTM.LB record selected as baseline from LBBLFL=Y; null otherwise.</x:v>
       </x:c>
       <x:c r="O124" s="7" t="n"/>
       <x:c r="P124" s="7" t="n"/>
@@ -13414,15 +13408,11 @@
       <x:c r="H35" s="7" t="n"/>
     </x:row>
     <x:row r="36" ht="48" customHeight="1">
-      <x:c r="A36" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MT.ADLB_BASEFL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B36" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Method for ADLB_BASEFL</x:t>
-        </x:is>
+      <x:c r="A36" s="7" t="str">
+        <x:v>MT.ADLB_ABLFL</x:v>
+      </x:c>
+      <x:c r="B36" s="7" t="str">
+        <x:v>Method for ADLB_ABLFL</x:v>
       </x:c>
       <x:c r="C36" s="7" t="inlineStr">
         <x:is>
@@ -13430,7 +13420,7 @@
         </x:is>
       </x:c>
       <x:c r="D36" s="7" t="str">
-        <x:v>Y only on the SDTM.LB record selected as baseline from LBBLFL=Y; N otherwise.</x:v>
+        <x:v>Y only on the deterministic SDTM.LB record selected as baseline from LBBLFL=Y; null otherwise.</x:v>
       </x:c>
       <x:c r="E36" s="7" t="n"/>
       <x:c r="F36" s="7" t="n"/>
